--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8428F4-BEEB-406D-BB9A-F1FACB59B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20925E4A-C6BA-4FB7-A98E-E3567DDA0245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4493" uniqueCount="486">
   <si>
     <t>Date</t>
   </si>
@@ -1493,12 +1493,15 @@
   <si>
     <t>OMNX598</t>
   </si>
+  <si>
+    <t>Shred</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1566,11 +1569,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1803,7 +1801,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1963,16 +1961,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -63079,7 +63074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96286940-14C8-42A2-8E24-DF88786D0349}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -63131,14 +63126,37 @@
         <v>164.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E4">
-        <f>SUM(E2:E2)</f>
-        <v>32.950000000000003</v>
-      </c>
-      <c r="G4">
-        <f>SUM(G2:G2)</f>
-        <v>164.75</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>46269</v>
+      </c>
+      <c r="B3">
+        <v>54750</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3">
+        <v>321</v>
+      </c>
+      <c r="E3">
+        <v>27.375</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>136.875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <f>SUM(E2:E3)</f>
+        <v>60.325000000000003</v>
+      </c>
+      <c r="G5">
+        <f>SUM(G2:G3)</f>
+        <v>301.625</v>
       </c>
     </row>
   </sheetData>
@@ -64105,52 +64123,65 @@
       <c r="H31" s="28">
         <v>195000</v>
       </c>
+      <c r="I31" s="44">
+        <v>263700</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="22"/>
       <c r="B32" s="23"/>
-      <c r="C32" s="65" t="s">
+      <c r="C32" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="23"/>
+      <c r="D32" s="41" t="s">
+        <v>66</v>
+      </c>
       <c r="E32" s="23"/>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="32"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
         <v>476</v>
       </c>
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="C33" s="67" t="s">
+      <c r="C33" s="66" t="s">
         <v>474</v>
       </c>
-      <c r="D33" s="66" t="s">
+      <c r="D33" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="E33" s="66" t="s">
+      <c r="E33" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="F33" s="66" t="s">
+      <c r="F33" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="G33" s="66" t="s">
+      <c r="G33" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="H33" s="66" t="s">
+      <c r="H33" s="65" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="42">
+        <v>253250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D34" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="31"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
         <v>478</v>
       </c>
@@ -64175,20 +64206,26 @@
       <c r="H35" s="28">
         <v>199230</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="44">
+        <v>259600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="22"/>
       <c r="B36" s="23"/>
-      <c r="C36" s="65" t="s">
+      <c r="C36" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="23"/>
+      <c r="D36" s="41" t="s">
+        <v>31</v>
+      </c>
       <c r="E36" s="23"/>
       <c r="F36" s="23"/>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="32"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>480</v>
       </c>
@@ -64213,20 +64250,26 @@
       <c r="H37" s="28">
         <v>165567</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="44">
+        <v>237900</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="22"/>
       <c r="B38" s="23"/>
-      <c r="C38" s="65" t="s">
+      <c r="C38" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="23"/>
+      <c r="D38" s="41" t="s">
+        <v>46</v>
+      </c>
       <c r="E38" s="23"/>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="32"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
         <v>481</v>
       </c>
@@ -64251,20 +64294,26 @@
       <c r="H39" s="28">
         <v>177869</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="44">
+        <v>249850</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="22"/>
       <c r="B40" s="23"/>
-      <c r="C40" s="65" t="s">
+      <c r="C40" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="23"/>
+      <c r="D40" s="41" t="s">
+        <v>485</v>
+      </c>
       <c r="E40" s="23"/>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>482</v>
       </c>
@@ -64289,20 +64338,26 @@
       <c r="H41" s="28">
         <v>182631</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="44">
+        <v>255150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="22"/>
       <c r="B42" s="23"/>
-      <c r="C42" s="65" t="s">
+      <c r="C42" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="23"/>
+      <c r="D42" s="41" t="s">
+        <v>485</v>
+      </c>
       <c r="E42" s="23"/>
       <c r="F42" s="23"/>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="32"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
         <v>483</v>
       </c>
@@ -64327,20 +64382,26 @@
       <c r="H43" s="28">
         <v>178839</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="44">
+        <v>248350</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="22"/>
       <c r="B44" s="23"/>
-      <c r="C44" s="65" t="s">
+      <c r="C44" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="23"/>
+      <c r="D44" s="41" t="s">
+        <v>485</v>
+      </c>
       <c r="E44" s="23"/>
       <c r="F44" s="23"/>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="32"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
         <v>484</v>
       </c>
@@ -64365,18 +64426,24 @@
       <c r="H45" s="28">
         <v>165920</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="44">
+        <v>238350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="22"/>
       <c r="B46" s="23"/>
-      <c r="C46" s="65" t="s">
+      <c r="C46" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="23"/>
+      <c r="D46" s="41" t="s">
+        <v>485</v>
+      </c>
       <c r="E46" s="23"/>
       <c r="F46" s="23"/>
       <c r="G46" s="23"/>
       <c r="H46" s="23"/>
+      <c r="I46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20925E4A-C6BA-4FB7-A98E-E3567DDA0245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6818C523-2462-471D-AE75-7F314D737D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4493" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4609" uniqueCount="541">
   <si>
     <t>Date</t>
   </si>
@@ -1496,6 +1496,171 @@
   <si>
     <t>Shred</t>
   </si>
+  <si>
+    <t>H145054</t>
+  </si>
+  <si>
+    <t>H145055</t>
+  </si>
+  <si>
+    <t>H145056</t>
+  </si>
+  <si>
+    <t>H145057</t>
+  </si>
+  <si>
+    <t>H145058</t>
+  </si>
+  <si>
+    <t>H145059</t>
+  </si>
+  <si>
+    <t>H145061</t>
+  </si>
+  <si>
+    <t>H145060</t>
+  </si>
+  <si>
+    <t>H145063</t>
+  </si>
+  <si>
+    <t>H145062</t>
+  </si>
+  <si>
+    <t>H145067</t>
+  </si>
+  <si>
+    <t>H145064</t>
+  </si>
+  <si>
+    <t>H145065</t>
+  </si>
+  <si>
+    <t>H145066</t>
+  </si>
+  <si>
+    <t>H145068</t>
+  </si>
+  <si>
+    <t>H145069</t>
+  </si>
+  <si>
+    <t>H145072</t>
+  </si>
+  <si>
+    <t>Manual Ticket 4126</t>
+  </si>
+  <si>
+    <t>H145073</t>
+  </si>
+  <si>
+    <t>Manual Ticket 4124</t>
+  </si>
+  <si>
+    <t>H145070</t>
+  </si>
+  <si>
+    <t>H145071</t>
+  </si>
+  <si>
+    <t>H145076</t>
+  </si>
+  <si>
+    <t>41B</t>
+  </si>
+  <si>
+    <t>H145074</t>
+  </si>
+  <si>
+    <t>H145077</t>
+  </si>
+  <si>
+    <t>H145075</t>
+  </si>
+  <si>
+    <t>H145078</t>
+  </si>
+  <si>
+    <t>Load contained NC material - shock and closed container</t>
+  </si>
+  <si>
+    <t>H145079</t>
+  </si>
+  <si>
+    <t>H145080</t>
+  </si>
+  <si>
+    <t>H145081</t>
+  </si>
+  <si>
+    <t>H145082</t>
+  </si>
+  <si>
+    <t>H145086</t>
+  </si>
+  <si>
+    <t>H145084</t>
+  </si>
+  <si>
+    <t>H145085</t>
+  </si>
+  <si>
+    <t>H145088</t>
+  </si>
+  <si>
+    <t>H145087</t>
+  </si>
+  <si>
+    <t>H145083</t>
+  </si>
+  <si>
+    <t>H145089</t>
+  </si>
+  <si>
+    <t>H145090</t>
+  </si>
+  <si>
+    <t>H145092</t>
+  </si>
+  <si>
+    <t>H145091</t>
+  </si>
+  <si>
+    <t>H145096</t>
+  </si>
+  <si>
+    <t>H145094</t>
+  </si>
+  <si>
+    <t>H145097</t>
+  </si>
+  <si>
+    <t>H145093</t>
+  </si>
+  <si>
+    <t>H145095</t>
+  </si>
+  <si>
+    <t>H145098</t>
+  </si>
+  <si>
+    <t>H145107</t>
+  </si>
+  <si>
+    <t>H145112</t>
+  </si>
+  <si>
+    <t>H145111</t>
+  </si>
+  <si>
+    <t>H145115</t>
+  </si>
+  <si>
+    <t>H145116</t>
+  </si>
+  <si>
+    <t>H145128</t>
+  </si>
 </sst>
 </file>
 
@@ -1946,6 +2111,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1960,15 +2134,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -49556,7 +49721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF6EBE6-8AD6-4D75-B294-66DBF263FABF}">
-  <dimension ref="A1:W229"/>
+  <dimension ref="A1:W280"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -63065,6 +63230,3024 @@
       </c>
       <c r="W229">
         <v>48180</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>47</v>
+      </c>
+      <c r="B230">
+        <v>1668367</v>
+      </c>
+      <c r="E230" t="s">
+        <v>113</v>
+      </c>
+      <c r="F230">
+        <v>47</v>
+      </c>
+      <c r="G230" t="s">
+        <v>486</v>
+      </c>
+      <c r="H230">
+        <v>75807</v>
+      </c>
+      <c r="I230">
+        <v>10011425</v>
+      </c>
+      <c r="J230" t="s">
+        <v>144</v>
+      </c>
+      <c r="M230">
+        <v>6720000</v>
+      </c>
+      <c r="N230" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O230" s="7">
+        <v>0.29312500000000002</v>
+      </c>
+      <c r="P230">
+        <v>353900</v>
+      </c>
+      <c r="Q230" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R230" s="7">
+        <v>0.30048611111111112</v>
+      </c>
+      <c r="S230">
+        <v>353902</v>
+      </c>
+      <c r="T230">
+        <v>0</v>
+      </c>
+      <c r="U230">
+        <v>77980</v>
+      </c>
+      <c r="V230">
+        <v>32860</v>
+      </c>
+      <c r="W230">
+        <v>45120</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>99268</v>
+      </c>
+      <c r="B231">
+        <v>1700793</v>
+      </c>
+      <c r="E231" t="s">
+        <v>113</v>
+      </c>
+      <c r="F231">
+        <v>99268</v>
+      </c>
+      <c r="G231" t="s">
+        <v>487</v>
+      </c>
+      <c r="H231">
+        <v>2202615</v>
+      </c>
+      <c r="I231">
+        <v>10012170</v>
+      </c>
+      <c r="J231">
+        <v>444</v>
+      </c>
+      <c r="M231">
+        <v>5000000</v>
+      </c>
+      <c r="N231" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O231" s="7">
+        <v>0.29600694444444442</v>
+      </c>
+      <c r="P231">
+        <v>353901</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R231" s="7">
+        <v>0.30342592592592593</v>
+      </c>
+      <c r="S231">
+        <v>353904</v>
+      </c>
+      <c r="T231">
+        <v>0</v>
+      </c>
+      <c r="U231">
+        <v>79700</v>
+      </c>
+      <c r="V231">
+        <v>29320</v>
+      </c>
+      <c r="W231">
+        <v>50380</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>530</v>
+      </c>
+      <c r="B232">
+        <v>1325989</v>
+      </c>
+      <c r="E232" t="s">
+        <v>113</v>
+      </c>
+      <c r="F232">
+        <v>530</v>
+      </c>
+      <c r="G232" t="s">
+        <v>488</v>
+      </c>
+      <c r="H232">
+        <v>8428641</v>
+      </c>
+      <c r="I232">
+        <v>10011509</v>
+      </c>
+      <c r="J232">
+        <v>503</v>
+      </c>
+      <c r="M232">
+        <v>99999999</v>
+      </c>
+      <c r="N232" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O232" s="7">
+        <v>0.30137731481481483</v>
+      </c>
+      <c r="P232">
+        <v>353903</v>
+      </c>
+      <c r="Q232" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R232" s="7">
+        <v>0.3109837962962963</v>
+      </c>
+      <c r="S232">
+        <v>353907</v>
+      </c>
+      <c r="T232">
+        <v>0</v>
+      </c>
+      <c r="U232">
+        <v>97500</v>
+      </c>
+      <c r="V232">
+        <v>33560</v>
+      </c>
+      <c r="W232">
+        <v>63940</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>495</v>
+      </c>
+      <c r="B233">
+        <v>1325993</v>
+      </c>
+      <c r="E233" t="s">
+        <v>113</v>
+      </c>
+      <c r="F233">
+        <v>495</v>
+      </c>
+      <c r="G233" t="s">
+        <v>489</v>
+      </c>
+      <c r="H233">
+        <v>8428643</v>
+      </c>
+      <c r="I233">
+        <v>10011521</v>
+      </c>
+      <c r="J233">
+        <v>249</v>
+      </c>
+      <c r="M233">
+        <v>99999999</v>
+      </c>
+      <c r="N233" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O233" s="7">
+        <v>0.30418981481481483</v>
+      </c>
+      <c r="P233">
+        <v>353905</v>
+      </c>
+      <c r="Q233" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R233" s="7">
+        <v>0.3130324074074074</v>
+      </c>
+      <c r="S233">
+        <v>353910</v>
+      </c>
+      <c r="T233">
+        <v>0</v>
+      </c>
+      <c r="U233">
+        <v>82460</v>
+      </c>
+      <c r="V233">
+        <v>34460</v>
+      </c>
+      <c r="W233">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>490</v>
+      </c>
+      <c r="B234">
+        <v>1326006</v>
+      </c>
+      <c r="E234" t="s">
+        <v>113</v>
+      </c>
+      <c r="F234">
+        <v>490</v>
+      </c>
+      <c r="G234" t="s">
+        <v>490</v>
+      </c>
+      <c r="H234">
+        <v>8428651</v>
+      </c>
+      <c r="I234">
+        <v>10011503</v>
+      </c>
+      <c r="J234">
+        <v>405</v>
+      </c>
+      <c r="M234">
+        <v>99999999</v>
+      </c>
+      <c r="N234" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O234" s="7">
+        <v>0.30855324074074075</v>
+      </c>
+      <c r="P234">
+        <v>353906</v>
+      </c>
+      <c r="Q234" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R234" s="7">
+        <v>0.31716435185185188</v>
+      </c>
+      <c r="S234">
+        <v>353912</v>
+      </c>
+      <c r="T234">
+        <v>0</v>
+      </c>
+      <c r="U234">
+        <v>95260</v>
+      </c>
+      <c r="V234">
+        <v>34300</v>
+      </c>
+      <c r="W234">
+        <v>60960</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>121104</v>
+      </c>
+      <c r="B235">
+        <v>1700793</v>
+      </c>
+      <c r="E235" t="s">
+        <v>113</v>
+      </c>
+      <c r="F235">
+        <v>121104</v>
+      </c>
+      <c r="G235" t="s">
+        <v>491</v>
+      </c>
+      <c r="H235">
+        <v>2202612</v>
+      </c>
+      <c r="I235">
+        <v>10012170</v>
+      </c>
+      <c r="J235">
+        <v>444</v>
+      </c>
+      <c r="M235">
+        <v>5000000</v>
+      </c>
+      <c r="N235" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O235" s="7">
+        <v>0.31212962962962965</v>
+      </c>
+      <c r="P235">
+        <v>353908</v>
+      </c>
+      <c r="Q235" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R235" s="7">
+        <v>0.32405092592592594</v>
+      </c>
+      <c r="S235">
+        <v>353915</v>
+      </c>
+      <c r="T235">
+        <v>0</v>
+      </c>
+      <c r="U235">
+        <v>79900</v>
+      </c>
+      <c r="V235">
+        <v>32360</v>
+      </c>
+      <c r="W235">
+        <v>47540</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>17</v>
+      </c>
+      <c r="B236">
+        <v>1699513</v>
+      </c>
+      <c r="E236" t="s">
+        <v>113</v>
+      </c>
+      <c r="F236">
+        <v>17</v>
+      </c>
+      <c r="G236" t="s">
+        <v>492</v>
+      </c>
+      <c r="H236">
+        <v>2509069</v>
+      </c>
+      <c r="I236">
+        <v>10011414</v>
+      </c>
+      <c r="J236">
+        <v>281</v>
+      </c>
+      <c r="M236">
+        <v>5600000</v>
+      </c>
+      <c r="N236" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O236" s="7">
+        <v>0.31947916666666665</v>
+      </c>
+      <c r="P236">
+        <v>353913</v>
+      </c>
+      <c r="Q236" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R236" s="7">
+        <v>0.3324537037037037</v>
+      </c>
+      <c r="S236">
+        <v>353917</v>
+      </c>
+      <c r="T236">
+        <v>0</v>
+      </c>
+      <c r="U236">
+        <v>78980</v>
+      </c>
+      <c r="V236">
+        <v>31960</v>
+      </c>
+      <c r="W236">
+        <v>47020</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>57</v>
+      </c>
+      <c r="B237">
+        <v>1679427</v>
+      </c>
+      <c r="E237" t="s">
+        <v>113</v>
+      </c>
+      <c r="F237">
+        <v>57</v>
+      </c>
+      <c r="G237" t="s">
+        <v>493</v>
+      </c>
+      <c r="H237">
+        <v>2257619</v>
+      </c>
+      <c r="I237">
+        <v>10031006</v>
+      </c>
+      <c r="J237">
+        <v>984</v>
+      </c>
+      <c r="M237">
+        <v>24000000</v>
+      </c>
+      <c r="N237" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O237" s="7">
+        <v>0.31550925925925927</v>
+      </c>
+      <c r="P237">
+        <v>353911</v>
+      </c>
+      <c r="Q237" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R237" s="7">
+        <v>0.33481481481481479</v>
+      </c>
+      <c r="S237">
+        <v>353919</v>
+      </c>
+      <c r="T237">
+        <v>0</v>
+      </c>
+      <c r="U237">
+        <v>79000</v>
+      </c>
+      <c r="V237">
+        <v>32560</v>
+      </c>
+      <c r="W237">
+        <v>46440</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>161113</v>
+      </c>
+      <c r="B238">
+        <v>1700793</v>
+      </c>
+      <c r="E238" t="s">
+        <v>113</v>
+      </c>
+      <c r="F238">
+        <v>161113</v>
+      </c>
+      <c r="G238" t="s">
+        <v>494</v>
+      </c>
+      <c r="H238">
+        <v>2202613</v>
+      </c>
+      <c r="I238">
+        <v>10012170</v>
+      </c>
+      <c r="J238">
+        <v>444</v>
+      </c>
+      <c r="M238">
+        <v>5000000</v>
+      </c>
+      <c r="N238" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O238" s="7">
+        <v>0.32665509259259257</v>
+      </c>
+      <c r="P238">
+        <v>353916</v>
+      </c>
+      <c r="Q238" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R238" s="7">
+        <v>0.33665509259259258</v>
+      </c>
+      <c r="S238">
+        <v>353920</v>
+      </c>
+      <c r="T238">
+        <v>0</v>
+      </c>
+      <c r="U238">
+        <v>80280</v>
+      </c>
+      <c r="V238">
+        <v>31800</v>
+      </c>
+      <c r="W238">
+        <v>48480</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>469</v>
+      </c>
+      <c r="B239">
+        <v>1448545</v>
+      </c>
+      <c r="E239" t="s">
+        <v>113</v>
+      </c>
+      <c r="F239">
+        <v>469</v>
+      </c>
+      <c r="G239" t="s">
+        <v>495</v>
+      </c>
+      <c r="H239">
+        <v>54717</v>
+      </c>
+      <c r="I239">
+        <v>10011660</v>
+      </c>
+      <c r="J239">
+        <v>149</v>
+      </c>
+      <c r="M239">
+        <v>1120000</v>
+      </c>
+      <c r="N239" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O239" s="7">
+        <v>0.32364583333333335</v>
+      </c>
+      <c r="P239">
+        <v>353914</v>
+      </c>
+      <c r="Q239" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R239" s="7">
+        <v>0.33875</v>
+      </c>
+      <c r="S239">
+        <v>353922</v>
+      </c>
+      <c r="T239">
+        <v>0</v>
+      </c>
+      <c r="U239">
+        <v>118560</v>
+      </c>
+      <c r="V239">
+        <v>52900</v>
+      </c>
+      <c r="W239">
+        <v>65660</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>1718</v>
+      </c>
+      <c r="B240">
+        <v>1605502</v>
+      </c>
+      <c r="E240" t="s">
+        <v>113</v>
+      </c>
+      <c r="F240">
+        <v>1718</v>
+      </c>
+      <c r="G240" t="s">
+        <v>496</v>
+      </c>
+      <c r="H240">
+        <v>27916</v>
+      </c>
+      <c r="I240">
+        <v>10011004</v>
+      </c>
+      <c r="J240">
+        <v>173</v>
+      </c>
+      <c r="M240">
+        <v>7000000</v>
+      </c>
+      <c r="N240" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O240" s="7">
+        <v>0.34641203703703705</v>
+      </c>
+      <c r="P240">
+        <v>353924</v>
+      </c>
+      <c r="Q240" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R240" s="7">
+        <v>0.34657407407407409</v>
+      </c>
+      <c r="S240">
+        <v>353925</v>
+      </c>
+      <c r="T240">
+        <v>0</v>
+      </c>
+      <c r="U240">
+        <v>78000</v>
+      </c>
+      <c r="V240">
+        <v>44440</v>
+      </c>
+      <c r="W240">
+        <v>33560</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>22531</v>
+      </c>
+      <c r="B241">
+        <v>1448548</v>
+      </c>
+      <c r="E241" t="s">
+        <v>113</v>
+      </c>
+      <c r="F241">
+        <v>22531</v>
+      </c>
+      <c r="G241" t="s">
+        <v>497</v>
+      </c>
+      <c r="H241">
+        <v>833632</v>
+      </c>
+      <c r="I241">
+        <v>10011660</v>
+      </c>
+      <c r="J241">
+        <v>149</v>
+      </c>
+      <c r="M241">
+        <v>1120000</v>
+      </c>
+      <c r="N241" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O241" s="7">
+        <v>0.333125</v>
+      </c>
+      <c r="P241">
+        <v>353918</v>
+      </c>
+      <c r="Q241" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R241" s="7">
+        <v>0.35038194444444443</v>
+      </c>
+      <c r="S241">
+        <v>353928</v>
+      </c>
+      <c r="T241">
+        <v>0</v>
+      </c>
+      <c r="U241">
+        <v>98880</v>
+      </c>
+      <c r="V241">
+        <v>41260</v>
+      </c>
+      <c r="W241">
+        <v>57620</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>131</v>
+      </c>
+      <c r="B242">
+        <v>1699513</v>
+      </c>
+      <c r="E242" t="s">
+        <v>113</v>
+      </c>
+      <c r="F242">
+        <v>131</v>
+      </c>
+      <c r="G242" t="s">
+        <v>498</v>
+      </c>
+      <c r="H242">
+        <v>2518857</v>
+      </c>
+      <c r="I242">
+        <v>10011414</v>
+      </c>
+      <c r="J242">
+        <v>285</v>
+      </c>
+      <c r="M242">
+        <v>5600000</v>
+      </c>
+      <c r="N242" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O242" s="7">
+        <v>0.33763888888888888</v>
+      </c>
+      <c r="P242">
+        <v>353921</v>
+      </c>
+      <c r="Q242" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R242" s="7">
+        <v>0.36034722222222221</v>
+      </c>
+      <c r="S242">
+        <v>353932</v>
+      </c>
+      <c r="T242">
+        <v>0</v>
+      </c>
+      <c r="U242">
+        <v>95580</v>
+      </c>
+      <c r="V242">
+        <v>34120</v>
+      </c>
+      <c r="W242">
+        <v>61460</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>19</v>
+      </c>
+      <c r="B243">
+        <v>1699513</v>
+      </c>
+      <c r="E243" t="s">
+        <v>113</v>
+      </c>
+      <c r="F243">
+        <v>19</v>
+      </c>
+      <c r="G243" t="s">
+        <v>499</v>
+      </c>
+      <c r="H243">
+        <v>2518860</v>
+      </c>
+      <c r="I243">
+        <v>10011414</v>
+      </c>
+      <c r="J243">
+        <v>285</v>
+      </c>
+      <c r="M243">
+        <v>5600000</v>
+      </c>
+      <c r="N243" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O243" s="7">
+        <v>0.34370370370370368</v>
+      </c>
+      <c r="P243">
+        <v>353923</v>
+      </c>
+      <c r="Q243" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R243" s="7">
+        <v>0.36449074074074073</v>
+      </c>
+      <c r="S243">
+        <v>353934</v>
+      </c>
+      <c r="T243">
+        <v>0</v>
+      </c>
+      <c r="U243">
+        <v>96440</v>
+      </c>
+      <c r="V243">
+        <v>34580</v>
+      </c>
+      <c r="W243">
+        <v>61860</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>43</v>
+      </c>
+      <c r="B244">
+        <v>1699694</v>
+      </c>
+      <c r="E244" t="s">
+        <v>113</v>
+      </c>
+      <c r="F244">
+        <v>43</v>
+      </c>
+      <c r="G244" t="s">
+        <v>500</v>
+      </c>
+      <c r="H244">
+        <v>768365</v>
+      </c>
+      <c r="I244">
+        <v>10011558</v>
+      </c>
+      <c r="J244">
+        <v>602</v>
+      </c>
+      <c r="M244">
+        <v>40320</v>
+      </c>
+      <c r="N244" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O244" s="7">
+        <v>0.35094907407407405</v>
+      </c>
+      <c r="P244">
+        <v>353929</v>
+      </c>
+      <c r="Q244" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R244" s="7">
+        <v>0.36679398148148146</v>
+      </c>
+      <c r="S244">
+        <v>353936</v>
+      </c>
+      <c r="T244">
+        <v>0</v>
+      </c>
+      <c r="U244">
+        <v>76500</v>
+      </c>
+      <c r="V244">
+        <v>41440</v>
+      </c>
+      <c r="W244">
+        <v>35060</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>916</v>
+      </c>
+      <c r="B245">
+        <v>1702035</v>
+      </c>
+      <c r="E245" t="s">
+        <v>113</v>
+      </c>
+      <c r="F245">
+        <v>916</v>
+      </c>
+      <c r="G245" t="s">
+        <v>501</v>
+      </c>
+      <c r="H245">
+        <v>508335</v>
+      </c>
+      <c r="I245">
+        <v>10011414</v>
+      </c>
+      <c r="J245">
+        <v>285</v>
+      </c>
+      <c r="M245">
+        <v>2240000</v>
+      </c>
+      <c r="N245" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O245" s="7">
+        <v>0.35743055555555553</v>
+      </c>
+      <c r="P245">
+        <v>353931</v>
+      </c>
+      <c r="Q245" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R245" s="7">
+        <v>0.37026620370370372</v>
+      </c>
+      <c r="S245">
+        <v>353938</v>
+      </c>
+      <c r="T245">
+        <v>0</v>
+      </c>
+      <c r="U245">
+        <v>112720</v>
+      </c>
+      <c r="V245">
+        <v>40140</v>
+      </c>
+      <c r="W245">
+        <v>72580</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>55</v>
+      </c>
+      <c r="B246">
+        <v>1688844</v>
+      </c>
+      <c r="E246" t="s">
+        <v>113</v>
+      </c>
+      <c r="F246">
+        <v>55</v>
+      </c>
+      <c r="G246" t="s">
+        <v>502</v>
+      </c>
+      <c r="H246">
+        <v>9042</v>
+      </c>
+      <c r="I246">
+        <v>10011513</v>
+      </c>
+      <c r="J246">
+        <v>432</v>
+      </c>
+      <c r="L246" t="s">
+        <v>503</v>
+      </c>
+      <c r="M246">
+        <v>1280600</v>
+      </c>
+      <c r="N246" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O246" s="7">
+        <v>0.37153935185185183</v>
+      </c>
+      <c r="P246">
+        <v>353939</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R246" s="7">
+        <v>0.37174768518518519</v>
+      </c>
+      <c r="S246">
+        <v>353940</v>
+      </c>
+      <c r="T246">
+        <v>0</v>
+      </c>
+      <c r="U246">
+        <v>101940</v>
+      </c>
+      <c r="V246">
+        <v>39760</v>
+      </c>
+      <c r="W246">
+        <v>62180</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>55</v>
+      </c>
+      <c r="B247">
+        <v>1688844</v>
+      </c>
+      <c r="E247" t="s">
+        <v>113</v>
+      </c>
+      <c r="F247">
+        <v>55</v>
+      </c>
+      <c r="G247" t="s">
+        <v>504</v>
+      </c>
+      <c r="H247">
+        <v>9041</v>
+      </c>
+      <c r="I247">
+        <v>10011513</v>
+      </c>
+      <c r="J247">
+        <v>432</v>
+      </c>
+      <c r="L247" t="s">
+        <v>505</v>
+      </c>
+      <c r="M247">
+        <v>1280600</v>
+      </c>
+      <c r="N247" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O247" s="7">
+        <v>0.37278935185185186</v>
+      </c>
+      <c r="P247">
+        <v>353941</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R247" s="7">
+        <v>0.37288194444444445</v>
+      </c>
+      <c r="S247">
+        <v>353942</v>
+      </c>
+      <c r="T247">
+        <v>0</v>
+      </c>
+      <c r="U247">
+        <v>100600</v>
+      </c>
+      <c r="V247">
+        <v>39980</v>
+      </c>
+      <c r="W247">
+        <v>60620</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>31</v>
+      </c>
+      <c r="B248">
+        <v>1699513</v>
+      </c>
+      <c r="E248" t="s">
+        <v>113</v>
+      </c>
+      <c r="F248">
+        <v>31</v>
+      </c>
+      <c r="G248" t="s">
+        <v>506</v>
+      </c>
+      <c r="H248">
+        <v>2518900</v>
+      </c>
+      <c r="I248">
+        <v>10011414</v>
+      </c>
+      <c r="J248">
+        <v>285</v>
+      </c>
+      <c r="M248">
+        <v>5600000</v>
+      </c>
+      <c r="N248" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O248" s="7">
+        <v>0.36363425925925924</v>
+      </c>
+      <c r="P248">
+        <v>353933</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R248" s="7">
+        <v>0.37546296296296294</v>
+      </c>
+      <c r="S248">
+        <v>353944</v>
+      </c>
+      <c r="T248">
+        <v>0</v>
+      </c>
+      <c r="U248">
+        <v>97760</v>
+      </c>
+      <c r="V248">
+        <v>35460</v>
+      </c>
+      <c r="W248">
+        <v>62300</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>23</v>
+      </c>
+      <c r="B249">
+        <v>1699513</v>
+      </c>
+      <c r="E249" t="s">
+        <v>113</v>
+      </c>
+      <c r="F249">
+        <v>23</v>
+      </c>
+      <c r="G249" t="s">
+        <v>507</v>
+      </c>
+      <c r="H249">
+        <v>2518872</v>
+      </c>
+      <c r="I249">
+        <v>10011414</v>
+      </c>
+      <c r="J249">
+        <v>281</v>
+      </c>
+      <c r="M249">
+        <v>5600000</v>
+      </c>
+      <c r="N249" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O249" s="7">
+        <v>0.3676388888888889</v>
+      </c>
+      <c r="P249">
+        <v>353937</v>
+      </c>
+      <c r="Q249" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R249" s="7">
+        <v>0.37825231481481481</v>
+      </c>
+      <c r="S249">
+        <v>353946</v>
+      </c>
+      <c r="T249">
+        <v>0</v>
+      </c>
+      <c r="U249">
+        <v>92540</v>
+      </c>
+      <c r="V249">
+        <v>30640</v>
+      </c>
+      <c r="W249">
+        <v>61900</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>1718</v>
+      </c>
+      <c r="B250">
+        <v>1605482</v>
+      </c>
+      <c r="E250" t="s">
+        <v>113</v>
+      </c>
+      <c r="F250">
+        <v>1718</v>
+      </c>
+      <c r="G250" t="s">
+        <v>508</v>
+      </c>
+      <c r="H250">
+        <v>27920</v>
+      </c>
+      <c r="I250">
+        <v>10011512</v>
+      </c>
+      <c r="J250" t="s">
+        <v>509</v>
+      </c>
+      <c r="M250">
+        <v>36400000</v>
+      </c>
+      <c r="N250" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O250" s="7">
+        <v>0.38401620370370371</v>
+      </c>
+      <c r="P250">
+        <v>353947</v>
+      </c>
+      <c r="Q250" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R250" s="7">
+        <v>0.38414351851851852</v>
+      </c>
+      <c r="S250">
+        <v>353948</v>
+      </c>
+      <c r="T250">
+        <v>0</v>
+      </c>
+      <c r="U250">
+        <v>95280</v>
+      </c>
+      <c r="V250">
+        <v>44440</v>
+      </c>
+      <c r="W250">
+        <v>50840</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>123</v>
+      </c>
+      <c r="B251">
+        <v>1694755</v>
+      </c>
+      <c r="E251" t="s">
+        <v>113</v>
+      </c>
+      <c r="F251">
+        <v>123</v>
+      </c>
+      <c r="G251" t="s">
+        <v>510</v>
+      </c>
+      <c r="H251">
+        <v>763468</v>
+      </c>
+      <c r="I251">
+        <v>10011509</v>
+      </c>
+      <c r="J251">
+        <v>503</v>
+      </c>
+      <c r="M251">
+        <v>134400</v>
+      </c>
+      <c r="N251" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O251" s="7">
+        <v>0.37410879629629629</v>
+      </c>
+      <c r="P251">
+        <v>353943</v>
+      </c>
+      <c r="Q251" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R251" s="7">
+        <v>0.38709490740740743</v>
+      </c>
+      <c r="S251">
+        <v>353949</v>
+      </c>
+      <c r="T251">
+        <v>0</v>
+      </c>
+      <c r="U251">
+        <v>78960</v>
+      </c>
+      <c r="V251">
+        <v>36700</v>
+      </c>
+      <c r="W251">
+        <v>42260</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>126</v>
+      </c>
+      <c r="B252">
+        <v>1699517</v>
+      </c>
+      <c r="E252" t="s">
+        <v>113</v>
+      </c>
+      <c r="F252">
+        <v>126</v>
+      </c>
+      <c r="G252" t="s">
+        <v>511</v>
+      </c>
+      <c r="H252">
+        <v>161205</v>
+      </c>
+      <c r="I252">
+        <v>10011414</v>
+      </c>
+      <c r="J252">
+        <v>281</v>
+      </c>
+      <c r="M252">
+        <v>6720000</v>
+      </c>
+      <c r="N252" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O252" s="7">
+        <v>0.38869212962962962</v>
+      </c>
+      <c r="P252">
+        <v>353950</v>
+      </c>
+      <c r="Q252" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R252" s="7">
+        <v>0.39379629629629631</v>
+      </c>
+      <c r="S252">
+        <v>353951</v>
+      </c>
+      <c r="T252">
+        <v>0</v>
+      </c>
+      <c r="U252">
+        <v>99480</v>
+      </c>
+      <c r="V252">
+        <v>34280</v>
+      </c>
+      <c r="W252">
+        <v>65200</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>1776</v>
+      </c>
+      <c r="B253">
+        <v>1702035</v>
+      </c>
+      <c r="E253" t="s">
+        <v>113</v>
+      </c>
+      <c r="F253">
+        <v>1776</v>
+      </c>
+      <c r="G253" t="s">
+        <v>512</v>
+      </c>
+      <c r="H253">
+        <v>508336</v>
+      </c>
+      <c r="I253">
+        <v>10011414</v>
+      </c>
+      <c r="J253">
+        <v>285</v>
+      </c>
+      <c r="M253">
+        <v>2240000</v>
+      </c>
+      <c r="N253" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O253" s="7">
+        <v>0.37723379629629628</v>
+      </c>
+      <c r="P253">
+        <v>353945</v>
+      </c>
+      <c r="Q253" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R253" s="7">
+        <v>0.39504629629629628</v>
+      </c>
+      <c r="S253">
+        <v>353952</v>
+      </c>
+      <c r="T253">
+        <v>0</v>
+      </c>
+      <c r="U253">
+        <v>124860</v>
+      </c>
+      <c r="V253">
+        <v>39640</v>
+      </c>
+      <c r="W253">
+        <v>85220</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>106</v>
+      </c>
+      <c r="B254">
+        <v>1699517</v>
+      </c>
+      <c r="E254" t="s">
+        <v>113</v>
+      </c>
+      <c r="F254">
+        <v>106</v>
+      </c>
+      <c r="G254" t="s">
+        <v>513</v>
+      </c>
+      <c r="H254">
+        <v>161208</v>
+      </c>
+      <c r="I254">
+        <v>10011414</v>
+      </c>
+      <c r="J254">
+        <v>281</v>
+      </c>
+      <c r="L254" t="s">
+        <v>514</v>
+      </c>
+      <c r="M254">
+        <v>6720000</v>
+      </c>
+      <c r="N254" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O254" s="7">
+        <v>0.39916666666666667</v>
+      </c>
+      <c r="P254">
+        <v>353954</v>
+      </c>
+      <c r="Q254" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R254" s="7">
+        <v>0.40995370370370371</v>
+      </c>
+      <c r="S254">
+        <v>353956</v>
+      </c>
+      <c r="T254">
+        <v>0</v>
+      </c>
+      <c r="U254">
+        <v>79180</v>
+      </c>
+      <c r="V254">
+        <v>32240</v>
+      </c>
+      <c r="W254">
+        <v>46940</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>1718</v>
+      </c>
+      <c r="B255">
+        <v>1605482</v>
+      </c>
+      <c r="E255" t="s">
+        <v>113</v>
+      </c>
+      <c r="F255">
+        <v>1718</v>
+      </c>
+      <c r="G255" t="s">
+        <v>515</v>
+      </c>
+      <c r="H255">
+        <v>27924</v>
+      </c>
+      <c r="I255">
+        <v>10011512</v>
+      </c>
+      <c r="J255" t="s">
+        <v>509</v>
+      </c>
+      <c r="M255">
+        <v>36400000</v>
+      </c>
+      <c r="N255" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O255" s="7">
+        <v>0.42376157407407405</v>
+      </c>
+      <c r="P255">
+        <v>353958</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R255" s="7">
+        <v>0.42388888888888887</v>
+      </c>
+      <c r="S255">
+        <v>353959</v>
+      </c>
+      <c r="T255">
+        <v>0</v>
+      </c>
+      <c r="U255">
+        <v>82340</v>
+      </c>
+      <c r="V255">
+        <v>44440</v>
+      </c>
+      <c r="W255">
+        <v>37900</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>1718</v>
+      </c>
+      <c r="B256">
+        <v>1605482</v>
+      </c>
+      <c r="E256" t="s">
+        <v>113</v>
+      </c>
+      <c r="F256">
+        <v>1718</v>
+      </c>
+      <c r="G256" t="s">
+        <v>516</v>
+      </c>
+      <c r="H256">
+        <v>27925</v>
+      </c>
+      <c r="I256">
+        <v>10011512</v>
+      </c>
+      <c r="J256" t="s">
+        <v>82</v>
+      </c>
+      <c r="M256">
+        <v>36400000</v>
+      </c>
+      <c r="N256" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O256" s="7">
+        <v>0.44131944444444443</v>
+      </c>
+      <c r="P256">
+        <v>353962</v>
+      </c>
+      <c r="Q256" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R256" s="7">
+        <v>0.44146990740740738</v>
+      </c>
+      <c r="S256">
+        <v>353963</v>
+      </c>
+      <c r="T256">
+        <v>0</v>
+      </c>
+      <c r="U256">
+        <v>98980</v>
+      </c>
+      <c r="V256">
+        <v>44440</v>
+      </c>
+      <c r="W256">
+        <v>54540</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>108</v>
+      </c>
+      <c r="B257">
+        <v>1699517</v>
+      </c>
+      <c r="E257" t="s">
+        <v>113</v>
+      </c>
+      <c r="F257">
+        <v>108</v>
+      </c>
+      <c r="G257" t="s">
+        <v>517</v>
+      </c>
+      <c r="H257">
+        <v>161217</v>
+      </c>
+      <c r="I257">
+        <v>10011414</v>
+      </c>
+      <c r="J257">
+        <v>285</v>
+      </c>
+      <c r="M257">
+        <v>6720000</v>
+      </c>
+      <c r="N257" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O257" s="7">
+        <v>0.44393518518518521</v>
+      </c>
+      <c r="P257">
+        <v>353964</v>
+      </c>
+      <c r="Q257" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R257" s="7">
+        <v>0.45633101851851854</v>
+      </c>
+      <c r="S257">
+        <v>353965</v>
+      </c>
+      <c r="T257">
+        <v>0</v>
+      </c>
+      <c r="U257">
+        <v>114540</v>
+      </c>
+      <c r="V257">
+        <v>40800</v>
+      </c>
+      <c r="W257">
+        <v>73740</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>105</v>
+      </c>
+      <c r="B258">
+        <v>1699517</v>
+      </c>
+      <c r="E258" t="s">
+        <v>113</v>
+      </c>
+      <c r="F258">
+        <v>105</v>
+      </c>
+      <c r="G258" t="s">
+        <v>518</v>
+      </c>
+      <c r="H258">
+        <v>161220</v>
+      </c>
+      <c r="I258">
+        <v>10011414</v>
+      </c>
+      <c r="J258">
+        <v>281</v>
+      </c>
+      <c r="M258">
+        <v>6720000</v>
+      </c>
+      <c r="N258" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O258" s="7">
+        <v>0.4667013888888889</v>
+      </c>
+      <c r="P258">
+        <v>353966</v>
+      </c>
+      <c r="Q258" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R258" s="7">
+        <v>0.47513888888888889</v>
+      </c>
+      <c r="S258">
+        <v>353968</v>
+      </c>
+      <c r="T258">
+        <v>0</v>
+      </c>
+      <c r="U258">
+        <v>79060</v>
+      </c>
+      <c r="V258">
+        <v>37860</v>
+      </c>
+      <c r="W258">
+        <v>41200</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>1718</v>
+      </c>
+      <c r="B259">
+        <v>1605482</v>
+      </c>
+      <c r="E259" t="s">
+        <v>113</v>
+      </c>
+      <c r="F259">
+        <v>1718</v>
+      </c>
+      <c r="G259" t="s">
+        <v>519</v>
+      </c>
+      <c r="H259">
+        <v>27927</v>
+      </c>
+      <c r="I259">
+        <v>10011512</v>
+      </c>
+      <c r="J259" t="s">
+        <v>82</v>
+      </c>
+      <c r="M259">
+        <v>36400000</v>
+      </c>
+      <c r="N259" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O259" s="7">
+        <v>0.48562499999999997</v>
+      </c>
+      <c r="P259">
+        <v>353971</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R259" s="7">
+        <v>0.48596064814814816</v>
+      </c>
+      <c r="S259">
+        <v>353972</v>
+      </c>
+      <c r="T259">
+        <v>0</v>
+      </c>
+      <c r="U259">
+        <v>98580</v>
+      </c>
+      <c r="V259">
+        <v>44440</v>
+      </c>
+      <c r="W259">
+        <v>54140</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>666</v>
+      </c>
+      <c r="B260">
+        <v>1702480</v>
+      </c>
+      <c r="E260" t="s">
+        <v>113</v>
+      </c>
+      <c r="F260">
+        <v>666</v>
+      </c>
+      <c r="G260" t="s">
+        <v>520</v>
+      </c>
+      <c r="H260">
+        <v>589943</v>
+      </c>
+      <c r="I260">
+        <v>10011509</v>
+      </c>
+      <c r="J260">
+        <v>503</v>
+      </c>
+      <c r="M260">
+        <v>44800</v>
+      </c>
+      <c r="N260" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O260" s="7">
+        <v>0.48041666666666666</v>
+      </c>
+      <c r="P260">
+        <v>353969</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R260" s="7">
+        <v>0.49587962962962961</v>
+      </c>
+      <c r="S260">
+        <v>353974</v>
+      </c>
+      <c r="T260">
+        <v>0</v>
+      </c>
+      <c r="U260">
+        <v>77640</v>
+      </c>
+      <c r="V260">
+        <v>45740</v>
+      </c>
+      <c r="W260">
+        <v>31900</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>2023</v>
+      </c>
+      <c r="B261">
+        <v>1700793</v>
+      </c>
+      <c r="E261" t="s">
+        <v>113</v>
+      </c>
+      <c r="F261">
+        <v>2023</v>
+      </c>
+      <c r="G261" t="s">
+        <v>521</v>
+      </c>
+      <c r="H261">
+        <v>2202616</v>
+      </c>
+      <c r="I261">
+        <v>10012170</v>
+      </c>
+      <c r="J261">
+        <v>444</v>
+      </c>
+      <c r="M261">
+        <v>5000000</v>
+      </c>
+      <c r="N261" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O261" s="7">
+        <v>0.48423611111111109</v>
+      </c>
+      <c r="P261">
+        <v>353970</v>
+      </c>
+      <c r="Q261" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R261" s="7">
+        <v>0.49722222222222223</v>
+      </c>
+      <c r="S261">
+        <v>353975</v>
+      </c>
+      <c r="T261">
+        <v>0</v>
+      </c>
+      <c r="U261">
+        <v>79560</v>
+      </c>
+      <c r="V261">
+        <v>34620</v>
+      </c>
+      <c r="W261">
+        <v>44940</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1201</v>
+      </c>
+      <c r="B262">
+        <v>1605482</v>
+      </c>
+      <c r="E262" t="s">
+        <v>113</v>
+      </c>
+      <c r="F262">
+        <v>1201</v>
+      </c>
+      <c r="G262" t="s">
+        <v>522</v>
+      </c>
+      <c r="H262">
+        <v>27929</v>
+      </c>
+      <c r="I262">
+        <v>10011512</v>
+      </c>
+      <c r="J262" t="s">
+        <v>82</v>
+      </c>
+      <c r="M262">
+        <v>36400000</v>
+      </c>
+      <c r="N262" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O262" s="7">
+        <v>0.49909722222222225</v>
+      </c>
+      <c r="P262">
+        <v>353976</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R262" s="7">
+        <v>0.49922453703703706</v>
+      </c>
+      <c r="S262">
+        <v>353977</v>
+      </c>
+      <c r="T262">
+        <v>0</v>
+      </c>
+      <c r="U262">
+        <v>113240</v>
+      </c>
+      <c r="V262">
+        <v>64120</v>
+      </c>
+      <c r="W262">
+        <v>49120</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>128</v>
+      </c>
+      <c r="B263">
+        <v>1699517</v>
+      </c>
+      <c r="E263" t="s">
+        <v>113</v>
+      </c>
+      <c r="F263">
+        <v>128</v>
+      </c>
+      <c r="G263" t="s">
+        <v>523</v>
+      </c>
+      <c r="H263">
+        <v>161221</v>
+      </c>
+      <c r="I263">
+        <v>10011414</v>
+      </c>
+      <c r="J263">
+        <v>285</v>
+      </c>
+      <c r="M263">
+        <v>6720000</v>
+      </c>
+      <c r="N263" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O263" s="7">
+        <v>0.4874074074074074</v>
+      </c>
+      <c r="P263">
+        <v>353973</v>
+      </c>
+      <c r="Q263" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R263" s="7">
+        <v>0.49983796296296296</v>
+      </c>
+      <c r="S263">
+        <v>353978</v>
+      </c>
+      <c r="T263">
+        <v>0</v>
+      </c>
+      <c r="U263">
+        <v>112800</v>
+      </c>
+      <c r="V263">
+        <v>36560</v>
+      </c>
+      <c r="W263">
+        <v>76240</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>55</v>
+      </c>
+      <c r="B264">
+        <v>1688844</v>
+      </c>
+      <c r="E264" t="s">
+        <v>113</v>
+      </c>
+      <c r="F264">
+        <v>55</v>
+      </c>
+      <c r="G264" t="s">
+        <v>524</v>
+      </c>
+      <c r="H264">
+        <v>9081</v>
+      </c>
+      <c r="I264">
+        <v>10011513</v>
+      </c>
+      <c r="J264">
+        <v>432</v>
+      </c>
+      <c r="M264">
+        <v>1280600</v>
+      </c>
+      <c r="N264" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O264" s="7">
+        <v>0.47120370370370368</v>
+      </c>
+      <c r="P264">
+        <v>353967</v>
+      </c>
+      <c r="Q264" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R264" s="7">
+        <v>0.50402777777777774</v>
+      </c>
+      <c r="S264">
+        <v>353980</v>
+      </c>
+      <c r="T264">
+        <v>0</v>
+      </c>
+      <c r="U264">
+        <v>102620</v>
+      </c>
+      <c r="V264">
+        <v>39700</v>
+      </c>
+      <c r="W264">
+        <v>62920</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>38</v>
+      </c>
+      <c r="B265">
+        <v>1668367</v>
+      </c>
+      <c r="E265" t="s">
+        <v>113</v>
+      </c>
+      <c r="F265">
+        <v>38</v>
+      </c>
+      <c r="G265" t="s">
+        <v>525</v>
+      </c>
+      <c r="H265">
+        <v>75813</v>
+      </c>
+      <c r="I265">
+        <v>10011425</v>
+      </c>
+      <c r="J265" t="s">
+        <v>144</v>
+      </c>
+      <c r="M265">
+        <v>6720000</v>
+      </c>
+      <c r="N265" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O265" s="7">
+        <v>0.5010648148148148</v>
+      </c>
+      <c r="P265">
+        <v>353979</v>
+      </c>
+      <c r="Q265" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0.51270833333333332</v>
+      </c>
+      <c r="S265">
+        <v>353981</v>
+      </c>
+      <c r="T265">
+        <v>0</v>
+      </c>
+      <c r="U265">
+        <v>78560</v>
+      </c>
+      <c r="V265">
+        <v>32760</v>
+      </c>
+      <c r="W265">
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>1718</v>
+      </c>
+      <c r="B266">
+        <v>1605540</v>
+      </c>
+      <c r="E266" t="s">
+        <v>113</v>
+      </c>
+      <c r="F266">
+        <v>1718</v>
+      </c>
+      <c r="G266" t="s">
+        <v>526</v>
+      </c>
+      <c r="H266">
+        <v>27932</v>
+      </c>
+      <c r="I266">
+        <v>10011653</v>
+      </c>
+      <c r="J266">
+        <v>236</v>
+      </c>
+      <c r="M266">
+        <v>1500000</v>
+      </c>
+      <c r="N266" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O266" s="7">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="P266">
+        <v>353982</v>
+      </c>
+      <c r="Q266" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R266" s="7">
+        <v>0.51528935185185187</v>
+      </c>
+      <c r="S266">
+        <v>353983</v>
+      </c>
+      <c r="T266">
+        <v>0</v>
+      </c>
+      <c r="U266">
+        <v>91720</v>
+      </c>
+      <c r="V266">
+        <v>44440</v>
+      </c>
+      <c r="W266">
+        <v>47280</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>1201</v>
+      </c>
+      <c r="B267">
+        <v>1605482</v>
+      </c>
+      <c r="E267" t="s">
+        <v>113</v>
+      </c>
+      <c r="F267">
+        <v>1201</v>
+      </c>
+      <c r="G267" t="s">
+        <v>527</v>
+      </c>
+      <c r="H267">
+        <v>27933</v>
+      </c>
+      <c r="I267">
+        <v>10011512</v>
+      </c>
+      <c r="J267" t="s">
+        <v>82</v>
+      </c>
+      <c r="M267">
+        <v>36400000</v>
+      </c>
+      <c r="N267" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O267" s="7">
+        <v>0.51915509259259263</v>
+      </c>
+      <c r="P267">
+        <v>353985</v>
+      </c>
+      <c r="Q267" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R267" s="7">
+        <v>0.51930555555555558</v>
+      </c>
+      <c r="S267">
+        <v>353986</v>
+      </c>
+      <c r="T267">
+        <v>0</v>
+      </c>
+      <c r="U267">
+        <v>109460</v>
+      </c>
+      <c r="V267">
+        <v>64120</v>
+      </c>
+      <c r="W267">
+        <v>45340</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>1</v>
+      </c>
+      <c r="B268">
+        <v>1700793</v>
+      </c>
+      <c r="E268" t="s">
+        <v>113</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+      <c r="G268" t="s">
+        <v>528</v>
+      </c>
+      <c r="H268">
+        <v>2202618</v>
+      </c>
+      <c r="I268">
+        <v>10012170</v>
+      </c>
+      <c r="J268">
+        <v>444</v>
+      </c>
+      <c r="M268">
+        <v>5000000</v>
+      </c>
+      <c r="N268" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O268" s="7">
+        <v>0.51613425925925926</v>
+      </c>
+      <c r="P268">
+        <v>353984</v>
+      </c>
+      <c r="Q268" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R268" s="7">
+        <v>0.52789351851851851</v>
+      </c>
+      <c r="S268">
+        <v>353988</v>
+      </c>
+      <c r="T268">
+        <v>0</v>
+      </c>
+      <c r="U268">
+        <v>79740</v>
+      </c>
+      <c r="V268">
+        <v>32880</v>
+      </c>
+      <c r="W268">
+        <v>46860</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>1201</v>
+      </c>
+      <c r="B269">
+        <v>1605482</v>
+      </c>
+      <c r="E269" t="s">
+        <v>113</v>
+      </c>
+      <c r="F269">
+        <v>1201</v>
+      </c>
+      <c r="G269" t="s">
+        <v>529</v>
+      </c>
+      <c r="H269">
+        <v>27936</v>
+      </c>
+      <c r="I269">
+        <v>10011512</v>
+      </c>
+      <c r="J269" t="s">
+        <v>82</v>
+      </c>
+      <c r="M269">
+        <v>36400000</v>
+      </c>
+      <c r="N269" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O269" s="7">
+        <v>0.53924768518518518</v>
+      </c>
+      <c r="P269">
+        <v>353991</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R269" s="7">
+        <v>0.53938657407407409</v>
+      </c>
+      <c r="S269">
+        <v>353992</v>
+      </c>
+      <c r="T269">
+        <v>0</v>
+      </c>
+      <c r="U269">
+        <v>108800</v>
+      </c>
+      <c r="V269">
+        <v>64120</v>
+      </c>
+      <c r="W269">
+        <v>44680</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>31</v>
+      </c>
+      <c r="B270">
+        <v>1699513</v>
+      </c>
+      <c r="E270" t="s">
+        <v>113</v>
+      </c>
+      <c r="F270">
+        <v>31</v>
+      </c>
+      <c r="G270" t="s">
+        <v>530</v>
+      </c>
+      <c r="H270">
+        <v>2521857</v>
+      </c>
+      <c r="I270">
+        <v>10011414</v>
+      </c>
+      <c r="J270">
+        <v>281</v>
+      </c>
+      <c r="M270">
+        <v>5600000</v>
+      </c>
+      <c r="N270" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O270" s="7">
+        <v>0.52942129629629631</v>
+      </c>
+      <c r="P270">
+        <v>353989</v>
+      </c>
+      <c r="Q270" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R270" s="7">
+        <v>0.53989583333333335</v>
+      </c>
+      <c r="S270">
+        <v>353993</v>
+      </c>
+      <c r="T270">
+        <v>0</v>
+      </c>
+      <c r="U270">
+        <v>96700</v>
+      </c>
+      <c r="V270">
+        <v>35360</v>
+      </c>
+      <c r="W270">
+        <v>61340</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>1718</v>
+      </c>
+      <c r="B271">
+        <v>1605540</v>
+      </c>
+      <c r="E271" t="s">
+        <v>113</v>
+      </c>
+      <c r="F271">
+        <v>1718</v>
+      </c>
+      <c r="G271" t="s">
+        <v>531</v>
+      </c>
+      <c r="H271">
+        <v>27937</v>
+      </c>
+      <c r="I271">
+        <v>10011653</v>
+      </c>
+      <c r="J271">
+        <v>236</v>
+      </c>
+      <c r="M271">
+        <v>1500000</v>
+      </c>
+      <c r="N271" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O271" s="7">
+        <v>0.54361111111111116</v>
+      </c>
+      <c r="P271">
+        <v>353994</v>
+      </c>
+      <c r="Q271" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R271" s="7">
+        <v>0.54378472222222218</v>
+      </c>
+      <c r="S271">
+        <v>353995</v>
+      </c>
+      <c r="T271">
+        <v>0</v>
+      </c>
+      <c r="U271">
+        <v>91920</v>
+      </c>
+      <c r="V271">
+        <v>44440</v>
+      </c>
+      <c r="W271">
+        <v>47480</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>707</v>
+      </c>
+      <c r="B272">
+        <v>1702483</v>
+      </c>
+      <c r="E272" t="s">
+        <v>113</v>
+      </c>
+      <c r="F272">
+        <v>707</v>
+      </c>
+      <c r="G272" t="s">
+        <v>532</v>
+      </c>
+      <c r="H272">
+        <v>1085798</v>
+      </c>
+      <c r="I272">
+        <v>10011513</v>
+      </c>
+      <c r="J272">
+        <v>431</v>
+      </c>
+      <c r="M272">
+        <v>560000</v>
+      </c>
+      <c r="N272" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O272" s="7">
+        <v>0.52134259259259264</v>
+      </c>
+      <c r="P272">
+        <v>353987</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R272" s="7">
+        <v>0.54468749999999999</v>
+      </c>
+      <c r="S272">
+        <v>353996</v>
+      </c>
+      <c r="T272">
+        <v>0</v>
+      </c>
+      <c r="U272">
+        <v>77560</v>
+      </c>
+      <c r="V272">
+        <v>42540</v>
+      </c>
+      <c r="W272">
+        <v>35020</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>107</v>
+      </c>
+      <c r="B273">
+        <v>1699517</v>
+      </c>
+      <c r="E273" t="s">
+        <v>113</v>
+      </c>
+      <c r="F273">
+        <v>107</v>
+      </c>
+      <c r="G273" t="s">
+        <v>533</v>
+      </c>
+      <c r="H273">
+        <v>161224</v>
+      </c>
+      <c r="I273">
+        <v>10011414</v>
+      </c>
+      <c r="J273">
+        <v>281</v>
+      </c>
+      <c r="M273">
+        <v>6720000</v>
+      </c>
+      <c r="N273" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O273" s="7">
+        <v>0.53758101851851847</v>
+      </c>
+      <c r="P273">
+        <v>353990</v>
+      </c>
+      <c r="Q273" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R273" s="7">
+        <v>0.5481597222222222</v>
+      </c>
+      <c r="S273">
+        <v>353998</v>
+      </c>
+      <c r="T273">
+        <v>0</v>
+      </c>
+      <c r="U273">
+        <v>79740</v>
+      </c>
+      <c r="V273">
+        <v>38580</v>
+      </c>
+      <c r="W273">
+        <v>41160</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>126</v>
+      </c>
+      <c r="B274">
+        <v>1699517</v>
+      </c>
+      <c r="E274" t="s">
+        <v>113</v>
+      </c>
+      <c r="F274">
+        <v>126</v>
+      </c>
+      <c r="G274" t="s">
+        <v>534</v>
+      </c>
+      <c r="H274">
+        <v>161227</v>
+      </c>
+      <c r="I274">
+        <v>10011414</v>
+      </c>
+      <c r="J274">
+        <v>281</v>
+      </c>
+      <c r="M274">
+        <v>6720000</v>
+      </c>
+      <c r="N274" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O274" s="7">
+        <v>0.54703703703703699</v>
+      </c>
+      <c r="P274">
+        <v>353997</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R274" s="7">
+        <v>0.55313657407407413</v>
+      </c>
+      <c r="S274">
+        <v>354001</v>
+      </c>
+      <c r="T274">
+        <v>0</v>
+      </c>
+      <c r="U274">
+        <v>105120</v>
+      </c>
+      <c r="V274">
+        <v>34220</v>
+      </c>
+      <c r="W274">
+        <v>70900</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>12001</v>
+      </c>
+      <c r="B275">
+        <v>1605482</v>
+      </c>
+      <c r="E275" t="s">
+        <v>113</v>
+      </c>
+      <c r="F275">
+        <v>12001</v>
+      </c>
+      <c r="G275" t="s">
+        <v>535</v>
+      </c>
+      <c r="H275">
+        <v>27938</v>
+      </c>
+      <c r="I275">
+        <v>10011512</v>
+      </c>
+      <c r="J275" t="s">
+        <v>82</v>
+      </c>
+      <c r="M275">
+        <v>36400000</v>
+      </c>
+      <c r="N275" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O275" s="7">
+        <v>0.56260416666666668</v>
+      </c>
+      <c r="P275">
+        <v>354016</v>
+      </c>
+      <c r="Q275" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R275" s="7">
+        <v>0.56275462962962963</v>
+      </c>
+      <c r="S275">
+        <v>354017</v>
+      </c>
+      <c r="T275">
+        <v>0</v>
+      </c>
+      <c r="U275">
+        <v>111020</v>
+      </c>
+      <c r="V275">
+        <v>64120</v>
+      </c>
+      <c r="W275">
+        <v>46900</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>1718</v>
+      </c>
+      <c r="B276">
+        <v>1605540</v>
+      </c>
+      <c r="E276" t="s">
+        <v>113</v>
+      </c>
+      <c r="F276">
+        <v>1718</v>
+      </c>
+      <c r="G276" t="s">
+        <v>536</v>
+      </c>
+      <c r="H276">
+        <v>27941</v>
+      </c>
+      <c r="I276">
+        <v>10011653</v>
+      </c>
+      <c r="J276">
+        <v>236</v>
+      </c>
+      <c r="M276">
+        <v>1500000</v>
+      </c>
+      <c r="N276" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O276" s="7">
+        <v>0.57284722222222217</v>
+      </c>
+      <c r="P276">
+        <v>354025</v>
+      </c>
+      <c r="Q276" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R276" s="7">
+        <v>0.57315972222222222</v>
+      </c>
+      <c r="S276">
+        <v>354026</v>
+      </c>
+      <c r="T276">
+        <v>0</v>
+      </c>
+      <c r="U276">
+        <v>97780</v>
+      </c>
+      <c r="V276">
+        <v>44440</v>
+      </c>
+      <c r="W276">
+        <v>53340</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>19</v>
+      </c>
+      <c r="B277">
+        <v>1699513</v>
+      </c>
+      <c r="E277" t="s">
+        <v>113</v>
+      </c>
+      <c r="F277">
+        <v>19</v>
+      </c>
+      <c r="G277" t="s">
+        <v>537</v>
+      </c>
+      <c r="H277">
+        <v>2524578</v>
+      </c>
+      <c r="I277">
+        <v>10011414</v>
+      </c>
+      <c r="J277">
+        <v>281</v>
+      </c>
+      <c r="M277">
+        <v>5600000</v>
+      </c>
+      <c r="N277" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O277" s="7">
+        <v>0.56901620370370365</v>
+      </c>
+      <c r="P277">
+        <v>354024</v>
+      </c>
+      <c r="Q277" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R277" s="7">
+        <v>0.57697916666666671</v>
+      </c>
+      <c r="S277">
+        <v>354027</v>
+      </c>
+      <c r="T277">
+        <v>0</v>
+      </c>
+      <c r="U277">
+        <v>94360</v>
+      </c>
+      <c r="V277">
+        <v>34480</v>
+      </c>
+      <c r="W277">
+        <v>59880</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>1201</v>
+      </c>
+      <c r="B278">
+        <v>1605482</v>
+      </c>
+      <c r="E278" t="s">
+        <v>113</v>
+      </c>
+      <c r="F278">
+        <v>1201</v>
+      </c>
+      <c r="G278" t="s">
+        <v>538</v>
+      </c>
+      <c r="H278">
+        <v>27943</v>
+      </c>
+      <c r="I278">
+        <v>10011512</v>
+      </c>
+      <c r="J278" t="s">
+        <v>82</v>
+      </c>
+      <c r="M278">
+        <v>36400000</v>
+      </c>
+      <c r="N278" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O278" s="7">
+        <v>0.58023148148148151</v>
+      </c>
+      <c r="P278">
+        <v>354032</v>
+      </c>
+      <c r="Q278" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R278" s="7">
+        <v>0.58040509259259254</v>
+      </c>
+      <c r="S278">
+        <v>354033</v>
+      </c>
+      <c r="T278">
+        <v>0</v>
+      </c>
+      <c r="U278">
+        <v>107540</v>
+      </c>
+      <c r="V278">
+        <v>64120</v>
+      </c>
+      <c r="W278">
+        <v>43420</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>23</v>
+      </c>
+      <c r="B279">
+        <v>1699513</v>
+      </c>
+      <c r="E279" t="s">
+        <v>113</v>
+      </c>
+      <c r="F279">
+        <v>23</v>
+      </c>
+      <c r="G279" t="s">
+        <v>539</v>
+      </c>
+      <c r="H279">
+        <v>2525030</v>
+      </c>
+      <c r="I279">
+        <v>10011414</v>
+      </c>
+      <c r="J279">
+        <v>281</v>
+      </c>
+      <c r="M279">
+        <v>5600000</v>
+      </c>
+      <c r="N279" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O279" s="7">
+        <v>0.58697916666666672</v>
+      </c>
+      <c r="P279">
+        <v>354034</v>
+      </c>
+      <c r="Q279" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R279" s="7">
+        <v>0.59466435185185185</v>
+      </c>
+      <c r="S279">
+        <v>354035</v>
+      </c>
+      <c r="T279">
+        <v>0</v>
+      </c>
+      <c r="U279">
+        <v>91340</v>
+      </c>
+      <c r="V279">
+        <v>30660</v>
+      </c>
+      <c r="W279">
+        <v>60680</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>70</v>
+      </c>
+      <c r="B280">
+        <v>1679427</v>
+      </c>
+      <c r="E280" t="s">
+        <v>113</v>
+      </c>
+      <c r="F280">
+        <v>70</v>
+      </c>
+      <c r="G280" t="s">
+        <v>540</v>
+      </c>
+      <c r="H280">
+        <v>2257676</v>
+      </c>
+      <c r="I280">
+        <v>10031006</v>
+      </c>
+      <c r="J280">
+        <v>984</v>
+      </c>
+      <c r="M280">
+        <v>24000000</v>
+      </c>
+      <c r="N280" s="6">
+        <v>46273</v>
+      </c>
+      <c r="O280" s="7">
+        <v>0.71243055555555557</v>
+      </c>
+      <c r="P280">
+        <v>354058</v>
+      </c>
+      <c r="Q280" s="6">
+        <v>46273</v>
+      </c>
+      <c r="R280" s="7">
+        <v>0.7449189814814815</v>
+      </c>
+      <c r="S280">
+        <v>354059</v>
+      </c>
+      <c r="T280">
+        <v>0</v>
+      </c>
+      <c r="U280">
+        <v>77420</v>
+      </c>
+      <c r="V280">
+        <v>30480</v>
+      </c>
+      <c r="W280">
+        <v>46940</v>
       </c>
     </row>
   </sheetData>
@@ -63258,18 +66441,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="I1" s="63" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="I1" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="64"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="67"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -63308,7 +66491,7 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="64"/>
+      <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
@@ -64146,25 +67329,25 @@
       <c r="A33" s="24" t="s">
         <v>476</v>
       </c>
-      <c r="B33" s="65" t="s">
+      <c r="B33" s="60" t="s">
         <v>477</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="61" t="s">
         <v>474</v>
       </c>
-      <c r="D33" s="65" t="s">
+      <c r="D33" s="60" t="s">
         <v>477</v>
       </c>
-      <c r="E33" s="65" t="s">
+      <c r="E33" s="60" t="s">
         <v>477</v>
       </c>
-      <c r="F33" s="65" t="s">
+      <c r="F33" s="60" t="s">
         <v>477</v>
       </c>
-      <c r="G33" s="65" t="s">
+      <c r="G33" s="60" t="s">
         <v>477</v>
       </c>
-      <c r="H33" s="65" t="s">
+      <c r="H33" s="60" t="s">
         <v>477</v>
       </c>
       <c r="I33" s="42">
@@ -64173,7 +67356,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="62" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="43" t="s">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6818C523-2462-471D-AE75-7F314D737D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F56E705-0A70-4642-AD3C-77AB479BD041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4609" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4625" uniqueCount="542">
   <si>
     <t>Date</t>
   </si>
@@ -1661,12 +1661,15 @@
   <si>
     <t>H145128</t>
   </si>
+  <si>
+    <t>Empty 9/9</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1734,6 +1737,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1966,7 +1974,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2010,15 +2018,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
@@ -2035,30 +2034,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2070,12 +2047,6 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2083,12 +2054,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2134,6 +2099,53 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -50275,7 +50287,7 @@
         <v>124</v>
       </c>
       <c r="H10">
-        <v>832879</v>
+        <v>132601</v>
       </c>
       <c r="I10">
         <v>10011660</v>
@@ -66441,18 +66453,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="I1" s="66" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="I1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="67"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66491,92 +66503,98 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="67"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="50">
+      <c r="B3" s="54">
         <v>1326020</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="55">
         <v>10011657</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="54">
         <v>266600</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="54">
         <v>60600</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="54">
         <v>206000</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="65">
         <v>266350</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="51">
+      <c r="J3" s="66">
+        <v>60750</v>
+      </c>
+      <c r="K3" s="67">
         <v>947</v>
       </c>
-      <c r="L3" s="35"/>
+      <c r="L3" s="59" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21" t="s">
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="39"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="59" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="38">
         <v>1668373</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="38">
         <v>10011503</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="40">
         <v>260080</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="40">
         <v>58740</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="40">
         <v>201340</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="41">
         <v>259300</v>
       </c>
-      <c r="J5" s="57">
+      <c r="J5" s="42">
         <v>59750</v>
       </c>
-      <c r="K5" s="58">
+      <c r="K5" s="43">
         <v>402</v>
       </c>
       <c r="L5" s="13" t="s">
@@ -66596,60 +66614,72 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="49"/>
+      <c r="I6" s="36"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="49"/>
+      <c r="K6" s="36"/>
       <c r="L6" s="17" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="50">
+      <c r="B7" s="54">
         <v>1325985</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="55">
         <v>10011533</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="54">
         <v>276800</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="54">
         <v>65300</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="54">
         <v>211500</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="56">
         <v>276150</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="J7" s="57">
+        <v>71200</v>
+      </c>
+      <c r="K7" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="29"/>
+      <c r="L7" s="59" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="C8" s="21" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="29"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="59" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -66676,13 +66706,13 @@
       <c r="H9" s="11">
         <v>200350</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="34">
         <v>259850</v>
       </c>
       <c r="J9" s="12">
         <v>59150</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="35" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="13" t="s">
@@ -66704,9 +66734,9 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="49"/>
+      <c r="I10" s="36"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="49"/>
+      <c r="K10" s="36"/>
       <c r="L10" s="17" t="s">
         <v>165</v>
       </c>
@@ -66736,13 +66766,13 @@
       <c r="H11" s="11">
         <v>199640</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="34">
         <v>259900</v>
       </c>
       <c r="J11" s="12">
         <v>59400</v>
       </c>
-      <c r="K11" s="48" t="s">
+      <c r="K11" s="35" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="13" t="s">
@@ -66764,9 +66794,9 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="49"/>
+      <c r="I12" s="36"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="49"/>
+      <c r="K12" s="36"/>
       <c r="L12" s="17" t="s">
         <v>165</v>
       </c>
@@ -66796,13 +66826,13 @@
       <c r="H13" s="11">
         <v>199010</v>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="34">
         <v>259050</v>
       </c>
       <c r="J13" s="12">
         <v>59700</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="35">
         <v>402</v>
       </c>
       <c r="L13" s="13" t="s">
@@ -66822,9 +66852,9 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="49"/>
+      <c r="I14" s="36"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="49"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="17" t="s">
         <v>68</v>
       </c>
@@ -66854,13 +66884,13 @@
       <c r="H15" s="11">
         <v>200080</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="34">
         <v>259700</v>
       </c>
       <c r="J15" s="12">
         <v>59400</v>
       </c>
-      <c r="K15" s="48" t="s">
+      <c r="K15" s="35" t="s">
         <v>72</v>
       </c>
       <c r="L15" s="13" t="s">
@@ -66882,9 +66912,9 @@
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
-      <c r="I16" s="49"/>
+      <c r="I16" s="36"/>
       <c r="J16" s="15"/>
-      <c r="K16" s="49"/>
+      <c r="K16" s="36"/>
       <c r="L16" s="17" t="s">
         <v>348</v>
       </c>
@@ -66914,13 +66944,13 @@
       <c r="H17" s="11">
         <v>200640</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="34">
         <v>262250</v>
       </c>
       <c r="J17" s="12">
         <v>62100</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="35" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="13" t="s">
@@ -66942,116 +66972,128 @@
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="49"/>
+      <c r="I18" s="36"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="49"/>
+      <c r="K18" s="36"/>
       <c r="L18" s="17" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="9">
         <v>1692213</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="9">
         <v>10011509</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="11">
         <v>211850</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="11">
         <v>68300</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="11">
         <v>143550</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="34">
         <v>214850</v>
       </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="45">
+      <c r="J19" s="12">
+        <v>70700</v>
+      </c>
+      <c r="K19" s="35">
         <v>503</v>
       </c>
-      <c r="L19" s="46"/>
+      <c r="L19" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="40" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="30"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="17" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="9">
         <v>1692213</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="9">
         <v>10011509</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="11">
         <v>251150</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="11">
         <v>78250</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="11">
         <v>172900</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="34">
         <v>258500</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="45">
+      <c r="J21" s="12">
+        <v>79600</v>
+      </c>
+      <c r="K21" s="35">
         <v>503</v>
       </c>
-      <c r="L21" s="46"/>
+      <c r="L21" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="40" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="30"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="17" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
@@ -67078,13 +67120,13 @@
       <c r="H23" s="11">
         <v>201600</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="34">
         <v>266450</v>
       </c>
       <c r="J23" s="12">
         <v>63900</v>
       </c>
-      <c r="K23" s="48">
+      <c r="K23" s="35">
         <v>149</v>
       </c>
       <c r="L23" s="13" t="s">
@@ -67104,64 +67146,70 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
-      <c r="I24" s="49"/>
+      <c r="I24" s="36"/>
       <c r="J24" s="15"/>
-      <c r="K24" s="49"/>
+      <c r="K24" s="36"/>
       <c r="L24" s="17" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="9">
         <v>1695919</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="9">
         <v>10011503</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="11">
         <v>281000</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="11">
         <v>74000</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="11">
         <v>207000</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="34">
         <v>284900</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="45">
+      <c r="J25" s="12">
+        <v>75450</v>
+      </c>
+      <c r="K25" s="35">
         <v>402</v>
       </c>
-      <c r="L25" s="46"/>
+      <c r="L25" s="59" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="40" t="s">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="30"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="59" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
@@ -67188,13 +67236,13 @@
       <c r="H27" s="11">
         <v>125900</v>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="34">
         <v>201700</v>
       </c>
       <c r="J27" s="12">
         <v>77350</v>
       </c>
-      <c r="K27" s="48" t="s">
+      <c r="K27" s="35" t="s">
         <v>74</v>
       </c>
       <c r="L27" s="13" t="s">
@@ -67216,9 +67264,9 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
-      <c r="I28" s="49"/>
+      <c r="I28" s="36"/>
       <c r="J28" s="15"/>
-      <c r="K28" s="49"/>
+      <c r="K28" s="36"/>
       <c r="L28" s="17" t="s">
         <v>252</v>
       </c>
@@ -67248,13 +67296,13 @@
       <c r="H29" s="11">
         <v>219700</v>
       </c>
-      <c r="I29" s="47">
+      <c r="I29" s="34">
         <v>283750</v>
       </c>
       <c r="J29" s="12">
         <v>65800</v>
       </c>
-      <c r="K29" s="48">
+      <c r="K29" s="35">
         <v>149</v>
       </c>
       <c r="L29" s="13" t="s">
@@ -67274,359 +67322,405 @@
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
-      <c r="I30" s="49"/>
+      <c r="I30" s="36"/>
       <c r="J30" s="15"/>
-      <c r="K30" s="59"/>
+      <c r="K30" s="44"/>
       <c r="L30" s="17" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="9">
         <v>1326015</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="9">
         <v>10011558</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="11">
         <v>262800</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="11">
         <v>67800</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="11">
         <v>195000</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="34">
         <v>263700</v>
       </c>
+      <c r="J31" s="12">
+        <v>70550</v>
+      </c>
+      <c r="K31" s="35">
+        <v>602</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="40" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="32"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="17" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="46" t="s">
         <v>474</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="G33" s="60" t="s">
+      <c r="G33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="H33" s="60" t="s">
+      <c r="H33" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="I33" s="42">
+      <c r="I33" s="31">
         <v>253250</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="C34" s="62" t="s">
+      <c r="K33" s="27"/>
+      <c r="L33" s="26"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="C34" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="31"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
+      <c r="I34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="26"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="9">
         <v>1437870</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="9">
         <v>10011660</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="11">
         <v>259850</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="11">
         <v>60620</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="11">
         <v>199230</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="34">
         <v>259600</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="40" t="s">
+      <c r="J35" s="12">
+        <v>60300</v>
+      </c>
+      <c r="K35" s="35">
+        <v>149</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="32"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="17" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="23">
         <v>1692221</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="23">
         <v>10011509</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="28">
+      <c r="F37" s="25">
         <v>236203</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="25">
         <v>70636</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="25">
         <v>165567</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="33">
         <v>237900</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="40" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="32"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="23">
         <v>1692202</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="23">
         <v>10011503</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="25">
         <v>248417</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="25">
         <v>70548</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="25">
         <v>177869</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="33">
         <v>249850</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="40" t="s">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="41" t="s">
+      <c r="D40" s="30" t="s">
         <v>485</v>
       </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="28"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="23">
         <v>1692195</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="23">
         <v>10011558</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="24" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="25">
         <v>253355</v>
       </c>
-      <c r="G41" s="28">
+      <c r="G41" s="25">
         <v>70724</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="25">
         <v>182631</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="33">
         <v>255150</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="40" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="41" t="s">
+      <c r="D42" s="30" t="s">
         <v>485</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="32"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="28"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="9">
         <v>1692211</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="9">
         <v>10011660</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="11">
         <v>247932</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="11">
         <v>69093</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="11">
         <v>178839</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="34">
         <v>248350</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="40" t="s">
+      <c r="J43" s="12">
+        <v>68850</v>
+      </c>
+      <c r="K43" s="35">
+        <v>149</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="41" t="s">
+      <c r="D44" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="17" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="23">
         <v>1692221</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="23">
         <v>10011509</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="25">
         <v>236512</v>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="25">
         <v>70592</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="25">
         <v>165920</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="33">
         <v>238350</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="22"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="40" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="41" t="s">
+      <c r="D46" s="30" t="s">
         <v>485</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="32"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF876CE4-61CB-474B-8DF7-8A95C5A47E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579578DF-2A55-40F7-B9ED-4B4B1A1A7C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6243" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6300" uniqueCount="746">
   <si>
     <t>Date</t>
   </si>
@@ -2228,6 +2228,54 @@
   <si>
     <t>H145236</t>
   </si>
+  <si>
+    <t>40Y/602</t>
+  </si>
+  <si>
+    <t>RG&gt;181 Stainless</t>
+  </si>
+  <si>
+    <t>Empty 9/11</t>
+  </si>
+  <si>
+    <t>AEX19516</t>
+  </si>
+  <si>
+    <t>AEX19553</t>
+  </si>
+  <si>
+    <t>AEX26567</t>
+  </si>
+  <si>
+    <t>AEX26600</t>
+  </si>
+  <si>
+    <t>CLVX804271</t>
+  </si>
+  <si>
+    <t>GNWR4053</t>
+  </si>
+  <si>
+    <t>GNWR4086</t>
+  </si>
+  <si>
+    <t>GNWR4135</t>
+  </si>
+  <si>
+    <t>Sheets/Coils</t>
+  </si>
+  <si>
+    <t>Sheets/Loose</t>
+  </si>
+  <si>
+    <t>Cut Coil/Sheets</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>14R/947</t>
+  </si>
 </sst>
 </file>
 
@@ -2538,7 +2586,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2584,7 +2632,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2597,16 +2644,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2640,9 +2682,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2690,18 +2729,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2716,6 +2743,28 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -90926,7 +90975,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80722F43-7756-4701-9ABB-7A6774075D14}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -90943,18 +90992,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="I1" s="72" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="I1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="64"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -90993,98 +91042,98 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="73"/>
+      <c r="M2" s="64"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="42">
         <v>1326020</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="48">
+      <c r="D3" s="43">
         <v>10011657</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="47">
+      <c r="F3" s="42">
         <v>266600</v>
       </c>
-      <c r="G3" s="47">
+      <c r="G3" s="42">
         <v>60600</v>
       </c>
-      <c r="H3" s="47">
+      <c r="H3" s="42">
         <v>206000</v>
       </c>
-      <c r="I3" s="58">
+      <c r="I3" s="53">
         <v>266350</v>
       </c>
-      <c r="J3" s="59">
+      <c r="J3" s="54">
         <v>60750</v>
       </c>
-      <c r="K3" s="60">
+      <c r="K3" s="55">
         <v>947</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="47" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="54" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="52" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="47" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="34">
         <v>1668373</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="34">
         <v>10011503</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="36">
         <v>260080</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="36">
         <v>58740</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="36">
         <v>201340</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="37">
         <v>259300</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="38">
         <v>59750</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="39">
         <v>402</v>
       </c>
       <c r="L5" s="13" t="s">
@@ -91104,70 +91153,70 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="36"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="36"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="42">
         <v>1325985</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="43">
         <v>10011533</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="42">
         <v>276800</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="42">
         <v>65300</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="42">
         <v>211500</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="44">
         <v>276150</v>
       </c>
-      <c r="J7" s="50">
+      <c r="J7" s="45">
         <v>71200</v>
       </c>
-      <c r="K7" s="51" t="s">
+      <c r="K7" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="52" t="s">
+      <c r="L7" s="47" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="52" t="s">
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="47" t="s">
         <v>247</v>
       </c>
     </row>
@@ -91196,13 +91245,13 @@
       <c r="H9" s="11">
         <v>200350</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="30">
         <v>259850</v>
       </c>
       <c r="J9" s="12">
         <v>59150</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="31" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="13" t="s">
@@ -91224,9 +91273,9 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="36"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="36"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="17" t="s">
         <v>112</v>
       </c>
@@ -91256,13 +91305,13 @@
       <c r="H11" s="11">
         <v>199640</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="30">
         <v>259900</v>
       </c>
       <c r="J11" s="12">
         <v>59400</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="31" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="13" t="s">
@@ -91284,9 +91333,9 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="36"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="36"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="17" t="s">
         <v>112</v>
       </c>
@@ -91316,13 +91365,13 @@
       <c r="H13" s="11">
         <v>199010</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="30">
         <v>259050</v>
       </c>
       <c r="J13" s="12">
         <v>59700</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="31">
         <v>402</v>
       </c>
       <c r="L13" s="13" t="s">
@@ -91342,9 +91391,9 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="36"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="36"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="17" t="s">
         <v>68</v>
       </c>
@@ -91374,13 +91423,13 @@
       <c r="H15" s="11">
         <v>200080</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="30">
         <v>259700</v>
       </c>
       <c r="J15" s="12">
         <v>59400</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="31" t="s">
         <v>72</v>
       </c>
       <c r="L15" s="13" t="s">
@@ -91402,9 +91451,9 @@
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
-      <c r="I16" s="36"/>
+      <c r="I16" s="32"/>
       <c r="J16" s="15"/>
-      <c r="K16" s="36"/>
+      <c r="K16" s="32"/>
       <c r="L16" s="17" t="s">
         <v>170</v>
       </c>
@@ -91434,13 +91483,13 @@
       <c r="H17" s="11">
         <v>200640</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="30">
         <v>262250</v>
       </c>
       <c r="J17" s="12">
         <v>62100</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="31" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="13" t="s">
@@ -91462,9 +91511,9 @@
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="36"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="32"/>
       <c r="L18" s="17" t="s">
         <v>170</v>
       </c>
@@ -91494,13 +91543,13 @@
       <c r="H19" s="11">
         <v>143550</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="30">
         <v>214850</v>
       </c>
       <c r="J19" s="12">
         <v>70700</v>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="31">
         <v>503</v>
       </c>
       <c r="L19" s="13" t="s">
@@ -91520,9 +91569,9 @@
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="36"/>
+      <c r="I20" s="32"/>
       <c r="J20" s="15"/>
-      <c r="K20" s="36"/>
+      <c r="K20" s="32"/>
       <c r="L20" s="17" t="s">
         <v>247</v>
       </c>
@@ -91552,13 +91601,13 @@
       <c r="H21" s="11">
         <v>172900</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="30">
         <v>258500</v>
       </c>
       <c r="J21" s="12">
         <v>79600</v>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="31">
         <v>503</v>
       </c>
       <c r="L21" s="13" t="s">
@@ -91578,9 +91627,9 @@
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
-      <c r="I22" s="36"/>
+      <c r="I22" s="32"/>
       <c r="J22" s="15"/>
-      <c r="K22" s="36"/>
+      <c r="K22" s="32"/>
       <c r="L22" s="17" t="s">
         <v>247</v>
       </c>
@@ -91610,13 +91659,13 @@
       <c r="H23" s="11">
         <v>201600</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="30">
         <v>266450</v>
       </c>
       <c r="J23" s="12">
         <v>63900</v>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="31">
         <v>149</v>
       </c>
       <c r="L23" s="13" t="s">
@@ -91636,9 +91685,9 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
-      <c r="I24" s="36"/>
+      <c r="I24" s="32"/>
       <c r="J24" s="15"/>
-      <c r="K24" s="36"/>
+      <c r="K24" s="32"/>
       <c r="L24" s="17" t="s">
         <v>112</v>
       </c>
@@ -91668,16 +91717,16 @@
       <c r="H25" s="11">
         <v>207000</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="30">
         <v>284900</v>
       </c>
       <c r="J25" s="12">
         <v>75450</v>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="31">
         <v>402</v>
       </c>
-      <c r="L25" s="52" t="s">
+      <c r="L25" s="47" t="s">
         <v>35</v>
       </c>
     </row>
@@ -91694,10 +91743,10 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
-      <c r="I26" s="36"/>
+      <c r="I26" s="32"/>
       <c r="J26" s="15"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="52" t="s">
+      <c r="K26" s="32"/>
+      <c r="L26" s="47" t="s">
         <v>247</v>
       </c>
     </row>
@@ -91726,13 +91775,13 @@
       <c r="H27" s="11">
         <v>125900</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="30">
         <v>201700</v>
       </c>
       <c r="J27" s="12">
         <v>77350</v>
       </c>
-      <c r="K27" s="35" t="s">
+      <c r="K27" s="31" t="s">
         <v>74</v>
       </c>
       <c r="L27" s="13" t="s">
@@ -91754,9 +91803,9 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
-      <c r="I28" s="36"/>
+      <c r="I28" s="32"/>
       <c r="J28" s="15"/>
-      <c r="K28" s="36"/>
+      <c r="K28" s="32"/>
       <c r="L28" s="17" t="s">
         <v>138</v>
       </c>
@@ -91786,13 +91835,13 @@
       <c r="H29" s="11">
         <v>219700</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="30">
         <v>283750</v>
       </c>
       <c r="J29" s="12">
         <v>65800</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="31">
         <v>149</v>
       </c>
       <c r="L29" s="13" t="s">
@@ -91812,9 +91861,9 @@
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
-      <c r="I30" s="36"/>
+      <c r="I30" s="32"/>
       <c r="J30" s="15"/>
-      <c r="K30" s="44"/>
+      <c r="K30" s="40"/>
       <c r="L30" s="17" t="s">
         <v>138</v>
       </c>
@@ -91844,13 +91893,13 @@
       <c r="H31" s="11">
         <v>195000</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="30">
         <v>263700</v>
       </c>
       <c r="J31" s="12">
         <v>70550</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="31">
         <v>602</v>
       </c>
       <c r="L31" s="13" t="s">
@@ -91870,57 +91919,70 @@
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
-      <c r="I32" s="36"/>
+      <c r="I32" s="32"/>
       <c r="J32" s="15"/>
-      <c r="K32" s="36"/>
+      <c r="K32" s="32"/>
       <c r="L32" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="65">
+      <c r="B33" s="68">
         <v>1326018</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="69" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="9">
         <v>10011503</v>
       </c>
-      <c r="E33" s="65" t="s">
+      <c r="E33" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="66">
+      <c r="F33" s="70">
         <v>254300</v>
       </c>
-      <c r="G33" s="66">
+      <c r="G33" s="70">
         <v>66100</v>
       </c>
-      <c r="H33" s="66">
+      <c r="H33" s="70">
         <v>188200</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="44">
         <v>253250</v>
       </c>
-      <c r="K33" s="67">
+      <c r="J33" s="71">
+        <v>66950</v>
+      </c>
+      <c r="K33" s="46">
         <v>402</v>
       </c>
-      <c r="L33" s="26"/>
+      <c r="L33" s="47" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="41"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="26"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="47" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
@@ -91947,13 +92009,13 @@
       <c r="H35" s="11">
         <v>199230</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="30">
         <v>259600</v>
       </c>
       <c r="J35" s="12">
         <v>60300</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="31">
         <v>149</v>
       </c>
       <c r="L35" s="13" t="s">
@@ -91973,144 +92035,188 @@
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="15"/>
-      <c r="I36" s="36"/>
+      <c r="I36" s="32"/>
       <c r="J36" s="15"/>
-      <c r="K36" s="36"/>
+      <c r="K36" s="32"/>
       <c r="L36" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="9">
         <v>1692221</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="9">
         <v>10011509</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="11">
         <v>236203</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="11">
         <v>70636</v>
       </c>
-      <c r="H37" s="25">
+      <c r="H37" s="11">
         <v>165567</v>
       </c>
-      <c r="I37" s="33">
+      <c r="I37" s="30">
         <v>237900</v>
       </c>
+      <c r="J37" s="12">
+        <v>70800</v>
+      </c>
+      <c r="K37" s="31">
+        <v>509</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="19"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="29" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="28"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="17" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="9">
         <v>1692202</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="9">
         <v>10011503</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="11">
         <v>248417</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="11">
         <v>70548</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="11">
         <v>177869</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="30">
         <v>249850</v>
       </c>
+      <c r="J39" s="12">
+        <v>70450</v>
+      </c>
+      <c r="K39" s="31" t="s">
+        <v>730</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="29" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="28"/>
+      <c r="E40" s="18" t="s">
+        <v>731</v>
+      </c>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="17" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="9">
         <v>1692195</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="9">
         <v>10011558</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="11">
         <v>253355</v>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="11">
         <v>70724</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="11">
         <v>182631</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="30">
         <v>255150</v>
       </c>
+      <c r="J41" s="12">
+        <v>70900</v>
+      </c>
+      <c r="K41" s="31">
+        <v>602</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="29" t="s">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="28"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="17" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -92137,13 +92243,13 @@
       <c r="H43" s="11">
         <v>178839</v>
       </c>
-      <c r="I43" s="34">
+      <c r="I43" s="30">
         <v>248350</v>
       </c>
       <c r="J43" s="12">
         <v>68850</v>
       </c>
-      <c r="K43" s="35">
+      <c r="K43" s="31">
         <v>149</v>
       </c>
       <c r="L43" s="13" t="s">
@@ -92163,56 +92269,490 @@
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="15"/>
-      <c r="I44" s="36"/>
+      <c r="I44" s="32"/>
       <c r="J44" s="15"/>
-      <c r="K44" s="36"/>
+      <c r="K44" s="32"/>
       <c r="L44" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="9">
         <v>1692221</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="9">
         <v>10011509</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="11">
         <v>236512</v>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="11">
         <v>70592</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="11">
         <v>165920</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="30">
         <v>238350</v>
       </c>
+      <c r="J45" s="12">
+        <v>69550</v>
+      </c>
+      <c r="K45" s="31">
+        <v>509</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="19"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="29" t="s">
+      <c r="A46" s="14"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="28"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="17" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>733</v>
+      </c>
+      <c r="B47" s="22">
+        <v>1326015</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D47" s="22">
+        <v>10011558</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" s="24">
+        <v>259300</v>
+      </c>
+      <c r="G47" s="24">
+        <v>67900</v>
+      </c>
+      <c r="H47" s="24">
+        <v>191400</v>
+      </c>
+      <c r="I47" s="29">
+        <v>259950</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="K47" s="65">
+        <v>602</v>
+      </c>
+      <c r="L47" s="66"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="19"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>741</v>
+      </c>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="67"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>734</v>
+      </c>
+      <c r="B49" s="22">
+        <v>1326018</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D49" s="22">
+        <v>10011503</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="24">
+        <v>247600</v>
+      </c>
+      <c r="G49" s="24">
+        <v>70700</v>
+      </c>
+      <c r="H49" s="24">
+        <v>176900</v>
+      </c>
+      <c r="I49" s="29">
+        <v>248350</v>
+      </c>
+      <c r="J49" s="24"/>
+      <c r="K49" s="65">
+        <v>402</v>
+      </c>
+      <c r="L49" s="66"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="67"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>735</v>
+      </c>
+      <c r="B51" s="22">
+        <v>1668373</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="22">
+        <v>10011503</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="24">
+        <v>260360</v>
+      </c>
+      <c r="G51" s="24">
+        <v>58000</v>
+      </c>
+      <c r="H51" s="24">
+        <v>202360</v>
+      </c>
+      <c r="I51" s="29">
+        <v>261000</v>
+      </c>
+      <c r="J51" s="24"/>
+      <c r="K51" s="65">
+        <v>405</v>
+      </c>
+      <c r="L51" s="66"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="19"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>743</v>
+      </c>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="67"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>736</v>
+      </c>
+      <c r="B53" s="22">
+        <v>1325985</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D53" s="22">
+        <v>10011533</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" s="24">
+        <v>252200</v>
+      </c>
+      <c r="G53" s="24">
+        <v>61900</v>
+      </c>
+      <c r="H53" s="24">
+        <v>190300</v>
+      </c>
+      <c r="I53" s="29">
+        <v>252750</v>
+      </c>
+      <c r="J53" s="24"/>
+      <c r="K53" s="65" t="s">
+        <v>744</v>
+      </c>
+      <c r="L53" s="66"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="19"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="67"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>737</v>
+      </c>
+      <c r="B55" s="22">
+        <v>1326018</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D55" s="22">
+        <v>10011503</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55" s="24">
+        <v>280700</v>
+      </c>
+      <c r="G55" s="24">
+        <v>66800</v>
+      </c>
+      <c r="H55" s="24">
+        <v>213900</v>
+      </c>
+      <c r="I55" s="29">
+        <v>281300</v>
+      </c>
+      <c r="J55" s="24"/>
+      <c r="K55" s="65">
+        <v>405</v>
+      </c>
+      <c r="L55" s="66"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="19"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>741</v>
+      </c>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="67"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>738</v>
+      </c>
+      <c r="B57" s="22">
+        <v>1442707</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="22">
+        <v>10011503</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57" s="24">
+        <v>260350</v>
+      </c>
+      <c r="G57" s="24">
+        <v>60600</v>
+      </c>
+      <c r="H57" s="24">
+        <v>199750</v>
+      </c>
+      <c r="I57" s="29">
+        <v>261000</v>
+      </c>
+      <c r="J57" s="24"/>
+      <c r="K57" s="65">
+        <v>402</v>
+      </c>
+      <c r="L57" s="66"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="19"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="67"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="21" t="s">
+        <v>739</v>
+      </c>
+      <c r="B59" s="22">
+        <v>1437870</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D59" s="22">
+        <v>10011660</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F59" s="24">
+        <v>259000</v>
+      </c>
+      <c r="G59" s="24">
+        <v>59060</v>
+      </c>
+      <c r="H59" s="24">
+        <v>199940</v>
+      </c>
+      <c r="I59" s="29">
+        <v>259850</v>
+      </c>
+      <c r="J59" s="24"/>
+      <c r="K59" s="65" t="s">
+        <v>745</v>
+      </c>
+      <c r="L59" s="66"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="19"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="67"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="21" t="s">
+        <v>740</v>
+      </c>
+      <c r="B61" s="22">
+        <v>1390356</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="22">
+        <v>10011509</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61" s="24">
+        <v>260900</v>
+      </c>
+      <c r="G61" s="24">
+        <v>63540</v>
+      </c>
+      <c r="H61" s="24">
+        <v>197360</v>
+      </c>
+      <c r="I61" s="29">
+        <v>260750</v>
+      </c>
+      <c r="J61" s="24"/>
+      <c r="K61" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="66"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="19"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63B2FC0-0004-402E-BF7D-3D308C634DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E996B5-85E5-4F8D-A393-5F51E24BE07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -226,9 +226,6 @@
   </si>
   <si>
     <t>60R/947</t>
-  </si>
-  <si>
-    <t>ZVBX19057</t>
   </si>
   <si>
     <t>ZVBX20040</t>
@@ -947,7 +944,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1">
         <v>439114</v>
@@ -1203,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80722F43-7756-4701-9ABB-7A6774075D14}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -1803,16 +1800,16 @@
         <v>29</v>
       </c>
       <c r="F23" s="11">
-        <v>283410</v>
+        <v>281170</v>
       </c>
       <c r="G23" s="11">
-        <v>74540</v>
+        <v>80250</v>
       </c>
       <c r="H23" s="11">
-        <v>208870</v>
+        <v>200920</v>
       </c>
       <c r="I23" s="18">
-        <v>284500</v>
+        <v>282850</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="14">
@@ -1835,56 +1832,6 @@
       <c r="J24" s="13"/>
       <c r="K24" s="16"/>
       <c r="L24" s="17"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="9">
-        <v>1701738</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="9">
-        <v>10011503</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="11">
-        <v>281170</v>
-      </c>
-      <c r="G25" s="11">
-        <v>80250</v>
-      </c>
-      <c r="H25" s="11">
-        <v>200920</v>
-      </c>
-      <c r="I25" s="18">
-        <v>282850</v>
-      </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="14">
-        <v>405</v>
-      </c>
-      <c r="L25" s="15"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC0009-E073-4920-858B-8C1F491E6E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40368E1B-CFEE-4153-ADCE-B39006887F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="130">
   <si>
     <t>Date</t>
   </si>
@@ -138,12 +138,6 @@
     <t>SA3</t>
   </si>
   <si>
-    <t>AK TUBE LLC</t>
-  </si>
-  <si>
-    <t>Kroot</t>
-  </si>
-  <si>
     <t>TOTAL LBS</t>
   </si>
   <si>
@@ -154,9 +148,6 @@
   </si>
   <si>
     <t>Omnisource</t>
-  </si>
-  <si>
-    <t>RG&gt;436Stainless</t>
   </si>
   <si>
     <t>RG&gt;181Stainless</t>
@@ -189,37 +180,13 @@
     <t>50Y/602</t>
   </si>
   <si>
-    <t>CLVX804059</t>
-  </si>
-  <si>
     <t>OMNX102096</t>
-  </si>
-  <si>
-    <t>OMNX2473</t>
   </si>
   <si>
     <t>Placeholder</t>
   </si>
   <si>
     <t>Material</t>
-  </si>
-  <si>
-    <t>GNWR4085</t>
-  </si>
-  <si>
-    <t>40R/947</t>
-  </si>
-  <si>
-    <t>GONX340027</t>
-  </si>
-  <si>
-    <t>RMGX9089</t>
-  </si>
-  <si>
-    <t>60R/947</t>
-  </si>
-  <si>
-    <t>ZVBX20040</t>
   </si>
   <si>
     <t>032809/1</t>
@@ -443,6 +410,24 @@
   <si>
     <t>H146171</t>
   </si>
+  <si>
+    <t>CLVX804434</t>
+  </si>
+  <si>
+    <t>CLVX804441</t>
+  </si>
+  <si>
+    <t>ZVBX6129</t>
+  </si>
+  <si>
+    <t>TENNECO INC</t>
+  </si>
+  <si>
+    <t>ZVBX6141</t>
+  </si>
+  <si>
+    <t>S 430/409 Blend</t>
+  </si>
 </sst>
 </file>
 
@@ -538,7 +523,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -727,6 +712,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -736,7 +845,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -783,11 +892,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -807,6 +912,46 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,7 +1299,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B1">
         <v>409141</v>
@@ -1166,10 +1311,10 @@
         <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G1">
         <v>96</v>
@@ -1192,7 +1337,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>181218</v>
@@ -1204,10 +1349,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>285</v>
@@ -1230,7 +1375,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>181218</v>
@@ -1242,13 +1387,13 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H3">
         <v>10011512</v>
@@ -1268,7 +1413,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>181218</v>
@@ -1280,10 +1425,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>444</v>
@@ -1306,7 +1451,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>181218</v>
@@ -1318,10 +1463,10 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>525</v>
@@ -1344,7 +1489,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>181219</v>
@@ -1382,7 +1527,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>181219</v>
@@ -1420,7 +1565,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>181211</v>
@@ -1458,7 +1603,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>181211</v>
@@ -1496,7 +1641,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>181211</v>
@@ -1534,7 +1679,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>181211</v>
@@ -1572,7 +1717,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>181211</v>
@@ -1610,7 +1755,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>181211</v>
@@ -1648,7 +1793,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B14">
         <v>181211</v>
@@ -1686,7 +1831,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B15">
         <v>181211</v>
@@ -1724,7 +1869,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>181211</v>
@@ -1762,7 +1907,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B17">
         <v>181211</v>
@@ -1800,7 +1945,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>181211</v>
@@ -1838,7 +1983,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B19">
         <v>181212</v>
@@ -1850,10 +1995,10 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G19">
         <v>281</v>
@@ -1876,7 +2021,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>181212</v>
@@ -1888,13 +2033,13 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H20">
         <v>10011512</v>
@@ -1914,7 +2059,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>181212</v>
@@ -1926,10 +2071,10 @@
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G21">
         <v>249</v>
@@ -1952,7 +2097,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>181212</v>
@@ -1964,10 +2109,10 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G22">
         <v>444</v>
@@ -1990,7 +2135,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>181212</v>
@@ -2002,10 +2147,10 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G23">
         <v>444</v>
@@ -2028,7 +2173,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>181212</v>
@@ -2040,10 +2185,10 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G24">
         <v>525</v>
@@ -2066,7 +2211,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>181212</v>
@@ -2078,10 +2223,10 @@
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G25">
         <v>984</v>
@@ -2104,7 +2249,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>181212</v>
@@ -2116,10 +2261,10 @@
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G26">
         <v>864</v>
@@ -2142,7 +2287,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>181216</v>
@@ -2180,7 +2325,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>181216</v>
@@ -2218,7 +2363,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B29">
         <v>181216</v>
@@ -2256,7 +2401,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B30">
         <v>181216</v>
@@ -2294,7 +2439,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B31">
         <v>181217</v>
@@ -2332,7 +2477,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B32">
         <v>181217</v>
@@ -2370,7 +2515,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B33">
         <v>181217</v>
@@ -2382,10 +2527,10 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G33">
         <v>444</v>
@@ -2408,7 +2553,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B34">
         <v>181217</v>
@@ -2420,10 +2565,10 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G34">
         <v>984</v>
@@ -2446,7 +2591,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B35">
         <v>181217</v>
@@ -2458,10 +2603,10 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G35">
         <v>864</v>
@@ -2484,7 +2629,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>181218</v>
@@ -2496,10 +2641,10 @@
         <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G36">
         <v>285</v>
@@ -2522,7 +2667,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B37">
         <v>181218</v>
@@ -2534,13 +2679,13 @@
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H37">
         <v>10011512</v>
@@ -2560,7 +2705,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B38">
         <v>181218</v>
@@ -2572,10 +2717,10 @@
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F38" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G38">
         <v>249</v>
@@ -2598,7 +2743,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B39">
         <v>181218</v>
@@ -2610,10 +2755,10 @@
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G39">
         <v>444</v>
@@ -2636,7 +2781,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B40">
         <v>181218</v>
@@ -2648,10 +2793,10 @@
         <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G40">
         <v>525</v>
@@ -2674,7 +2819,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B41">
         <v>181219</v>
@@ -2712,7 +2857,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B42">
         <v>181219</v>
@@ -2750,7 +2895,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B43">
         <v>181211</v>
@@ -2788,7 +2933,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B44">
         <v>181211</v>
@@ -2826,7 +2971,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <v>181211</v>
@@ -2864,7 +3009,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B46">
         <v>181211</v>
@@ -2902,7 +3047,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B47">
         <v>181211</v>
@@ -2940,7 +3085,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B48">
         <v>181211</v>
@@ -2978,7 +3123,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B49">
         <v>181211</v>
@@ -3016,7 +3161,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B50">
         <v>181211</v>
@@ -3054,7 +3199,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B51">
         <v>181211</v>
@@ -3092,7 +3237,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B52">
         <v>181211</v>
@@ -3130,7 +3275,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B53">
         <v>181211</v>
@@ -3168,7 +3313,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B54">
         <v>181212</v>
@@ -3180,10 +3325,10 @@
         <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F54" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G54">
         <v>281</v>
@@ -3206,7 +3351,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B55">
         <v>181212</v>
@@ -3218,10 +3363,10 @@
         <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F55" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G55">
         <v>95</v>
@@ -3244,7 +3389,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B56">
         <v>181212</v>
@@ -3256,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="E56" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F56" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G56">
         <v>95</v>
@@ -3282,7 +3427,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B57">
         <v>181212</v>
@@ -3294,13 +3439,13 @@
         <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G57" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H57">
         <v>10011512</v>
@@ -3320,7 +3465,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B58">
         <v>181212</v>
@@ -3332,10 +3477,10 @@
         <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F58" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G58">
         <v>249</v>
@@ -3358,7 +3503,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B59">
         <v>181212</v>
@@ -3370,10 +3515,10 @@
         <v>17</v>
       </c>
       <c r="E59" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F59" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G59">
         <v>249</v>
@@ -3396,7 +3541,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B60">
         <v>181212</v>
@@ -3408,10 +3553,10 @@
         <v>17</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G60">
         <v>444</v>
@@ -3434,7 +3579,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B61">
         <v>181212</v>
@@ -3446,10 +3591,10 @@
         <v>17</v>
       </c>
       <c r="E61" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G61">
         <v>444</v>
@@ -3472,7 +3617,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B62">
         <v>181212</v>
@@ -3484,10 +3629,10 @@
         <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F62" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G62">
         <v>525</v>
@@ -3510,7 +3655,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B63">
         <v>181212</v>
@@ -3522,10 +3667,10 @@
         <v>17</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F63" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G63">
         <v>984</v>
@@ -3548,7 +3693,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>181212</v>
@@ -3560,10 +3705,10 @@
         <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G64">
         <v>864</v>
@@ -3586,7 +3731,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>409141</v>
@@ -3598,10 +3743,10 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G65">
         <v>171</v>
@@ -3624,7 +3769,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B66">
         <v>409141</v>
@@ -3636,10 +3781,10 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F66" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G66">
         <v>285</v>
@@ -3662,7 +3807,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B67">
         <v>409141</v>
@@ -3674,10 +3819,10 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F67" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G67">
         <v>285</v>
@@ -3700,7 +3845,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B68">
         <v>409141</v>
@@ -3712,10 +3857,10 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F68" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G68">
         <v>285</v>
@@ -3738,7 +3883,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B69">
         <v>409141</v>
@@ -3750,10 +3895,10 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F69" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G69">
         <v>96</v>
@@ -3776,7 +3921,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B70">
         <v>409141</v>
@@ -3788,10 +3933,10 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F70" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G70">
         <v>96</v>
@@ -3814,7 +3959,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B71">
         <v>409141</v>
@@ -3826,10 +3971,10 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G71">
         <v>96</v>
@@ -3852,7 +3997,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B72">
         <v>409141</v>
@@ -3864,10 +4009,10 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F72" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G72">
         <v>96</v>
@@ -3890,7 +4035,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B73">
         <v>409141</v>
@@ -3902,10 +4047,10 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F73" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G73">
         <v>402</v>
@@ -3928,7 +4073,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B74">
         <v>409141</v>
@@ -3940,10 +4085,10 @@
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G74">
         <v>402</v>
@@ -3966,7 +4111,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B75">
         <v>409141</v>
@@ -3978,10 +4123,10 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G75">
         <v>410</v>
@@ -4004,7 +4149,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B76">
         <v>409141</v>
@@ -4016,13 +4161,13 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F76" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G76" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H76">
         <v>10011512</v>
@@ -4042,7 +4187,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B77">
         <v>409141</v>
@@ -4054,10 +4199,10 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F77" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G77">
         <v>322</v>
@@ -4080,7 +4225,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B78">
         <v>409142</v>
@@ -4118,7 +4263,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B79">
         <v>409142</v>
@@ -4136,7 +4281,7 @@
         <v>32</v>
       </c>
       <c r="G79" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H79">
         <v>10011425</v>
@@ -4156,7 +4301,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B80">
         <v>409142</v>
@@ -4194,7 +4339,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B81">
         <v>409142</v>
@@ -4232,7 +4377,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B82">
         <v>409142</v>
@@ -4270,7 +4415,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B83">
         <v>409142</v>
@@ -4282,13 +4427,13 @@
         <v>19</v>
       </c>
       <c r="E83" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F83" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G83" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H83">
         <v>10011512</v>
@@ -4308,7 +4453,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B84">
         <v>409142</v>
@@ -4346,7 +4491,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B85">
         <v>409142</v>
@@ -4358,10 +4503,10 @@
         <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F85" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G85">
         <v>444</v>
@@ -4384,7 +4529,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B86">
         <v>409142</v>
@@ -4396,10 +4541,10 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F86" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G86">
         <v>444</v>
@@ -4422,7 +4567,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B87">
         <v>409142</v>
@@ -4434,10 +4579,10 @@
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G87">
         <v>525</v>
@@ -4460,7 +4605,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B88">
         <v>409142</v>
@@ -4472,10 +4617,10 @@
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F88" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G88">
         <v>984</v>
@@ -4498,7 +4643,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B89">
         <v>409142</v>
@@ -4510,10 +4655,10 @@
         <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F89" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G89">
         <v>864</v>
@@ -4536,7 +4681,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B90">
         <v>409146</v>
@@ -4548,10 +4693,10 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F90" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G90">
         <v>171</v>
@@ -4574,7 +4719,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B91">
         <v>409146</v>
@@ -4586,10 +4731,10 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F91" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G91">
         <v>285</v>
@@ -4612,7 +4757,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B92">
         <v>409146</v>
@@ -4624,10 +4769,10 @@
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F92" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G92">
         <v>402</v>
@@ -4650,7 +4795,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B93">
         <v>409146</v>
@@ -4662,10 +4807,10 @@
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F93" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G93">
         <v>410</v>
@@ -4688,7 +4833,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B94">
         <v>409146</v>
@@ -4700,13 +4845,13 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F94" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H94">
         <v>10011512</v>
@@ -4726,7 +4871,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B95">
         <v>409147</v>
@@ -4764,7 +4909,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B96">
         <v>409147</v>
@@ -4802,7 +4947,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B97">
         <v>409147</v>
@@ -4840,7 +4985,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B98">
         <v>409147</v>
@@ -4852,10 +4997,10 @@
         <v>16</v>
       </c>
       <c r="E98" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F98" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G98">
         <v>444</v>
@@ -4878,7 +5023,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B99">
         <v>409147</v>
@@ -4890,10 +5035,10 @@
         <v>16</v>
       </c>
       <c r="E99" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F99" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G99">
         <v>984</v>
@@ -4916,7 +5061,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B100">
         <v>409147</v>
@@ -4928,10 +5073,10 @@
         <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F100" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G100">
         <v>864</v>
@@ -4954,7 +5099,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B101">
         <v>409148</v>
@@ -4966,10 +5111,10 @@
         <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F101" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G101">
         <v>281</v>
@@ -4992,7 +5137,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B102">
         <v>409148</v>
@@ -5010,7 +5155,7 @@
         <v>32</v>
       </c>
       <c r="G102" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H102">
         <v>10011425</v>
@@ -5030,7 +5175,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B103">
         <v>409148</v>
@@ -5068,7 +5213,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B104">
         <v>409148</v>
@@ -5080,13 +5225,13 @@
         <v>15</v>
       </c>
       <c r="E104" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F104" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G104" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H104">
         <v>10011512</v>
@@ -5106,7 +5251,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B105">
         <v>409148</v>
@@ -5118,10 +5263,10 @@
         <v>15</v>
       </c>
       <c r="E105" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F105" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G105">
         <v>444</v>
@@ -5144,7 +5289,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B106">
         <v>409148</v>
@@ -5156,10 +5301,10 @@
         <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F106" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G106">
         <v>525</v>
@@ -5182,7 +5327,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B107">
         <v>409149</v>
@@ -5220,7 +5365,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B108">
         <v>409149</v>
@@ -5258,7 +5403,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B109">
         <v>409149</v>
@@ -5296,7 +5441,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B110">
         <v>409147</v>
@@ -5311,7 +5456,7 @@
         <v>31</v>
       </c>
       <c r="F110" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G110">
         <v>984</v>
@@ -5334,7 +5479,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B111">
         <v>409141</v>
@@ -5346,10 +5491,10 @@
         <v>23</v>
       </c>
       <c r="E111" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F111" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G111">
         <v>171</v>
@@ -5372,7 +5517,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B112">
         <v>409141</v>
@@ -5384,10 +5529,10 @@
         <v>23</v>
       </c>
       <c r="E112" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F112" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G112">
         <v>285</v>
@@ -5410,7 +5555,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B113">
         <v>409141</v>
@@ -5422,10 +5567,10 @@
         <v>23</v>
       </c>
       <c r="E113" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F113" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G113">
         <v>285</v>
@@ -5448,7 +5593,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B114">
         <v>409141</v>
@@ -5460,10 +5605,10 @@
         <v>23</v>
       </c>
       <c r="E114" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F114" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G114">
         <v>285</v>
@@ -5486,7 +5631,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B115">
         <v>409141</v>
@@ -5498,10 +5643,10 @@
         <v>23</v>
       </c>
       <c r="E115" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F115" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G115">
         <v>96</v>
@@ -5524,7 +5669,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B116">
         <v>409141</v>
@@ -5536,10 +5681,10 @@
         <v>23</v>
       </c>
       <c r="E116" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F116" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G116">
         <v>98</v>
@@ -5562,7 +5707,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B117">
         <v>409141</v>
@@ -5574,10 +5719,10 @@
         <v>23</v>
       </c>
       <c r="E117" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F117" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G117">
         <v>96</v>
@@ -5600,7 +5745,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B118">
         <v>409141</v>
@@ -5612,10 +5757,10 @@
         <v>23</v>
       </c>
       <c r="E118" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F118" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G118">
         <v>96</v>
@@ -5638,7 +5783,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B119">
         <v>409141</v>
@@ -5650,10 +5795,10 @@
         <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G119">
         <v>402</v>
@@ -5676,7 +5821,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B120">
         <v>409141</v>
@@ -5688,10 +5833,10 @@
         <v>23</v>
       </c>
       <c r="E120" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G120">
         <v>402</v>
@@ -5714,7 +5859,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B121">
         <v>409141</v>
@@ -5726,10 +5871,10 @@
         <v>23</v>
       </c>
       <c r="E121" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F121" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G121">
         <v>410</v>
@@ -5752,7 +5897,7 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B122">
         <v>409141</v>
@@ -5764,13 +5909,13 @@
         <v>23</v>
       </c>
       <c r="E122" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F122" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G122" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H122">
         <v>10011512</v>
@@ -5790,7 +5935,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B123">
         <v>409141</v>
@@ -5802,10 +5947,10 @@
         <v>23</v>
       </c>
       <c r="E123" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F123" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G123">
         <v>322</v>
@@ -5828,7 +5973,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B124">
         <v>409142</v>
@@ -5866,7 +6011,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B125">
         <v>409142</v>
@@ -5884,7 +6029,7 @@
         <v>32</v>
       </c>
       <c r="G125" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H125">
         <v>10011425</v>
@@ -5904,7 +6049,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B126">
         <v>409142</v>
@@ -5942,7 +6087,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B127">
         <v>409142</v>
@@ -5980,7 +6125,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B128">
         <v>409142</v>
@@ -6018,7 +6163,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B129">
         <v>409142</v>
@@ -6030,13 +6175,13 @@
         <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F129" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G129" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H129">
         <v>10011512</v>
@@ -6056,7 +6201,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B130">
         <v>409142</v>
@@ -6094,7 +6239,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B131">
         <v>409142</v>
@@ -6106,10 +6251,10 @@
         <v>12</v>
       </c>
       <c r="E131" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F131" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G131">
         <v>444</v>
@@ -6132,7 +6277,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B132">
         <v>409142</v>
@@ -6144,10 +6289,10 @@
         <v>12</v>
       </c>
       <c r="E132" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F132" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G132">
         <v>444</v>
@@ -6170,7 +6315,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B133">
         <v>409142</v>
@@ -6182,10 +6327,10 @@
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F133" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G133">
         <v>525</v>
@@ -6208,7 +6353,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B134">
         <v>409142</v>
@@ -6220,10 +6365,10 @@
         <v>12</v>
       </c>
       <c r="E134" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F134" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G134">
         <v>984</v>
@@ -6246,7 +6391,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B135">
         <v>409142</v>
@@ -6258,10 +6403,10 @@
         <v>12</v>
       </c>
       <c r="E135" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F135" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G135">
         <v>864</v>
@@ -6284,7 +6429,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B136">
         <v>409142</v>
@@ -6322,7 +6467,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B137">
         <v>409142</v>
@@ -6340,7 +6485,7 @@
         <v>32</v>
       </c>
       <c r="G137" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H137">
         <v>10011425</v>
@@ -6360,7 +6505,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B138">
         <v>409142</v>
@@ -6398,7 +6543,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B139">
         <v>409142</v>
@@ -6436,7 +6581,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B140">
         <v>409142</v>
@@ -6474,7 +6619,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B141">
         <v>409142</v>
@@ -6486,13 +6631,13 @@
         <v>17</v>
       </c>
       <c r="E141" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F141" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G141" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H141">
         <v>10011512</v>
@@ -6512,7 +6657,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B142">
         <v>409142</v>
@@ -6550,7 +6695,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B143">
         <v>409142</v>
@@ -6562,10 +6707,10 @@
         <v>17</v>
       </c>
       <c r="E143" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F143" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G143">
         <v>444</v>
@@ -6588,7 +6733,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B144">
         <v>409142</v>
@@ -6600,10 +6745,10 @@
         <v>17</v>
       </c>
       <c r="E144" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F144" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G144">
         <v>444</v>
@@ -6626,7 +6771,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B145">
         <v>409142</v>
@@ -6638,10 +6783,10 @@
         <v>17</v>
       </c>
       <c r="E145" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F145" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G145">
         <v>525</v>
@@ -6664,7 +6809,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B146">
         <v>409142</v>
@@ -6676,10 +6821,10 @@
         <v>17</v>
       </c>
       <c r="E146" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F146" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G146">
         <v>984</v>
@@ -6702,7 +6847,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B147">
         <v>409142</v>
@@ -6714,10 +6859,10 @@
         <v>17</v>
       </c>
       <c r="E147" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F147" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G147">
         <v>864</v>
@@ -6740,7 +6885,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B148">
         <v>409141</v>
@@ -6752,10 +6897,10 @@
         <v>23</v>
       </c>
       <c r="E148" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F148" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G148">
         <v>171</v>
@@ -6778,7 +6923,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B149">
         <v>409141</v>
@@ -6790,10 +6935,10 @@
         <v>23</v>
       </c>
       <c r="E149" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F149" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G149">
         <v>285</v>
@@ -6816,7 +6961,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B150">
         <v>409141</v>
@@ -6828,10 +6973,10 @@
         <v>23</v>
       </c>
       <c r="E150" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F150" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G150">
         <v>285</v>
@@ -6854,7 +6999,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B151">
         <v>409141</v>
@@ -6866,10 +7011,10 @@
         <v>23</v>
       </c>
       <c r="E151" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F151" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G151">
         <v>285</v>
@@ -6892,7 +7037,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B152">
         <v>409141</v>
@@ -6904,10 +7049,10 @@
         <v>23</v>
       </c>
       <c r="E152" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F152" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G152">
         <v>96</v>
@@ -6930,7 +7075,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B153">
         <v>409141</v>
@@ -6942,10 +7087,10 @@
         <v>23</v>
       </c>
       <c r="E153" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F153" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G153">
         <v>96</v>
@@ -6968,7 +7113,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B154">
         <v>409141</v>
@@ -6980,10 +7125,10 @@
         <v>23</v>
       </c>
       <c r="E154" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F154" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G154">
         <v>96</v>
@@ -7006,7 +7151,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B155">
         <v>409141</v>
@@ -7018,10 +7163,10 @@
         <v>23</v>
       </c>
       <c r="E155" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F155" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G155">
         <v>96</v>
@@ -7044,7 +7189,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B156">
         <v>409141</v>
@@ -7056,10 +7201,10 @@
         <v>23</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F156" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G156">
         <v>402</v>
@@ -7082,7 +7227,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B157">
         <v>409141</v>
@@ -7094,10 +7239,10 @@
         <v>23</v>
       </c>
       <c r="E157" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F157" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G157">
         <v>402</v>
@@ -7120,7 +7265,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B158">
         <v>409141</v>
@@ -7132,10 +7277,10 @@
         <v>23</v>
       </c>
       <c r="E158" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F158" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G158">
         <v>410</v>
@@ -7158,7 +7303,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B159">
         <v>409141</v>
@@ -7170,13 +7315,13 @@
         <v>23</v>
       </c>
       <c r="E159" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F159" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G159" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H159">
         <v>10011512</v>
@@ -7196,7 +7341,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B160">
         <v>409141</v>
@@ -7208,10 +7353,10 @@
         <v>23</v>
       </c>
       <c r="E160" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F160" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G160">
         <v>322</v>
@@ -7234,7 +7379,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B161">
         <v>409142</v>
@@ -7272,7 +7417,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B162">
         <v>409142</v>
@@ -7290,7 +7435,7 @@
         <v>32</v>
       </c>
       <c r="G162" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H162">
         <v>10011425</v>
@@ -7310,7 +7455,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B163">
         <v>409142</v>
@@ -7348,7 +7493,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B164">
         <v>409142</v>
@@ -7386,7 +7531,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B165">
         <v>409142</v>
@@ -7424,7 +7569,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B166">
         <v>409142</v>
@@ -7436,13 +7581,13 @@
         <v>18</v>
       </c>
       <c r="E166" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F166" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G166" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H166">
         <v>10011512</v>
@@ -7462,7 +7607,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B167">
         <v>409142</v>
@@ -7500,7 +7645,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B168">
         <v>409142</v>
@@ -7512,10 +7657,10 @@
         <v>18</v>
       </c>
       <c r="E168" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F168" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G168">
         <v>444</v>
@@ -7538,7 +7683,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B169">
         <v>409142</v>
@@ -7550,10 +7695,10 @@
         <v>18</v>
       </c>
       <c r="E169" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F169" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G169">
         <v>444</v>
@@ -7576,7 +7721,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B170">
         <v>409142</v>
@@ -7588,10 +7733,10 @@
         <v>18</v>
       </c>
       <c r="E170" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F170" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G170">
         <v>525</v>
@@ -7614,7 +7759,7 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B171">
         <v>409142</v>
@@ -7626,10 +7771,10 @@
         <v>18</v>
       </c>
       <c r="E171" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F171" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G171">
         <v>984</v>
@@ -7652,7 +7797,7 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B172">
         <v>409142</v>
@@ -7664,10 +7809,10 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F172" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G172">
         <v>864</v>
@@ -7690,7 +7835,7 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B173">
         <v>409146</v>
@@ -7702,10 +7847,10 @@
         <v>14</v>
       </c>
       <c r="E173" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F173" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G173">
         <v>171</v>
@@ -7728,7 +7873,7 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B174">
         <v>409146</v>
@@ -7740,10 +7885,10 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F174" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G174">
         <v>285</v>
@@ -7766,7 +7911,7 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B175">
         <v>409146</v>
@@ -7778,10 +7923,10 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F175" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G175">
         <v>402</v>
@@ -7804,7 +7949,7 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B176">
         <v>409146</v>
@@ -7816,10 +7961,10 @@
         <v>14</v>
       </c>
       <c r="E176" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F176" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G176">
         <v>410</v>
@@ -7842,7 +7987,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B177">
         <v>409146</v>
@@ -7854,13 +7999,13 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F177" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G177" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H177">
         <v>10011512</v>
@@ -7880,7 +8025,7 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B178">
         <v>409147</v>
@@ -7918,7 +8063,7 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B179">
         <v>409147</v>
@@ -7930,10 +8075,10 @@
         <v>19</v>
       </c>
       <c r="E179" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F179" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G179">
         <v>285</v>
@@ -7956,7 +8101,7 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B180">
         <v>409147</v>
@@ -7994,7 +8139,7 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B181">
         <v>409147</v>
@@ -8006,10 +8151,10 @@
         <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F181" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G181">
         <v>444</v>
@@ -8032,7 +8177,7 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B182">
         <v>409147</v>
@@ -8044,10 +8189,10 @@
         <v>19</v>
       </c>
       <c r="E182" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F182" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G182">
         <v>984</v>
@@ -8070,7 +8215,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B183">
         <v>409147</v>
@@ -8082,10 +8227,10 @@
         <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F183" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G183">
         <v>864</v>
@@ -8108,7 +8253,7 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B184">
         <v>409148</v>
@@ -8120,10 +8265,10 @@
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F184" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G184">
         <v>281</v>
@@ -8146,7 +8291,7 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B185">
         <v>409148</v>
@@ -8164,7 +8309,7 @@
         <v>32</v>
       </c>
       <c r="G185" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H185">
         <v>10011425</v>
@@ -8184,7 +8329,7 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B186">
         <v>409148</v>
@@ -8222,7 +8367,7 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B187">
         <v>409148</v>
@@ -8234,13 +8379,13 @@
         <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F187" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G187" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H187">
         <v>10011512</v>
@@ -8260,7 +8405,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B188">
         <v>409148</v>
@@ -8272,10 +8417,10 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F188" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G188">
         <v>444</v>
@@ -8298,7 +8443,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B189">
         <v>409148</v>
@@ -8310,10 +8455,10 @@
         <v>11</v>
       </c>
       <c r="E189" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F189" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G189">
         <v>525</v>
@@ -8336,7 +8481,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B190">
         <v>409149</v>
@@ -8374,7 +8519,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B191">
         <v>409149</v>
@@ -8412,7 +8557,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B192">
         <v>409149</v>
@@ -8450,7 +8595,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B193">
         <v>409141</v>
@@ -8462,10 +8607,10 @@
         <v>24</v>
       </c>
       <c r="E193" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F193" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G193">
         <v>171</v>
@@ -8488,7 +8633,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B194">
         <v>409141</v>
@@ -8500,10 +8645,10 @@
         <v>24</v>
       </c>
       <c r="E194" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F194" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G194">
         <v>285</v>
@@ -8526,7 +8671,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B195">
         <v>409141</v>
@@ -8538,10 +8683,10 @@
         <v>24</v>
       </c>
       <c r="E195" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F195" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G195">
         <v>285</v>
@@ -8564,7 +8709,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B196">
         <v>409141</v>
@@ -8576,10 +8721,10 @@
         <v>24</v>
       </c>
       <c r="E196" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F196" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G196">
         <v>285</v>
@@ -8602,7 +8747,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B197">
         <v>409141</v>
@@ -8614,10 +8759,10 @@
         <v>24</v>
       </c>
       <c r="E197" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F197" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G197">
         <v>96</v>
@@ -8640,7 +8785,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B198">
         <v>409141</v>
@@ -8652,10 +8797,10 @@
         <v>24</v>
       </c>
       <c r="E198" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F198" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G198">
         <v>96</v>
@@ -8678,7 +8823,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B199">
         <v>409141</v>
@@ -8690,10 +8835,10 @@
         <v>24</v>
       </c>
       <c r="E199" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F199" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G199">
         <v>96</v>
@@ -8716,7 +8861,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B200">
         <v>409141</v>
@@ -8728,10 +8873,10 @@
         <v>24</v>
       </c>
       <c r="E200" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F200" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G200">
         <v>96</v>
@@ -8754,7 +8899,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B201">
         <v>409141</v>
@@ -8766,10 +8911,10 @@
         <v>24</v>
       </c>
       <c r="E201" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F201" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G201">
         <v>402</v>
@@ -8792,7 +8937,7 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B202">
         <v>409141</v>
@@ -8804,10 +8949,10 @@
         <v>24</v>
       </c>
       <c r="E202" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F202" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G202">
         <v>402</v>
@@ -8830,7 +8975,7 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B203">
         <v>409141</v>
@@ -8842,10 +8987,10 @@
         <v>24</v>
       </c>
       <c r="E203" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F203" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G203">
         <v>410</v>
@@ -8868,7 +9013,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B204">
         <v>409141</v>
@@ -8880,13 +9025,13 @@
         <v>24</v>
       </c>
       <c r="E204" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F204" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G204" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H204">
         <v>10011512</v>
@@ -8906,7 +9051,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B205">
         <v>409141</v>
@@ -8918,10 +9063,10 @@
         <v>24</v>
       </c>
       <c r="E205" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F205" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G205">
         <v>322</v>
@@ -8944,7 +9089,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B206">
         <v>409141</v>
@@ -8956,10 +9101,10 @@
         <v>24</v>
       </c>
       <c r="E206" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F206" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G206">
         <v>171</v>
@@ -8982,7 +9127,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B207">
         <v>409141</v>
@@ -8994,10 +9139,10 @@
         <v>24</v>
       </c>
       <c r="E207" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F207" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G207">
         <v>285</v>
@@ -9020,7 +9165,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B208">
         <v>409141</v>
@@ -9032,10 +9177,10 @@
         <v>24</v>
       </c>
       <c r="E208" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F208" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G208">
         <v>285</v>
@@ -9058,7 +9203,7 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B209">
         <v>409141</v>
@@ -9070,10 +9215,10 @@
         <v>24</v>
       </c>
       <c r="E209" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F209" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G209">
         <v>285</v>
@@ -9096,7 +9241,7 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B210">
         <v>409141</v>
@@ -9108,10 +9253,10 @@
         <v>24</v>
       </c>
       <c r="E210" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F210" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G210">
         <v>96</v>
@@ -9134,7 +9279,7 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B211">
         <v>409141</v>
@@ -9146,10 +9291,10 @@
         <v>24</v>
       </c>
       <c r="E211" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F211" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G211">
         <v>96</v>
@@ -9172,7 +9317,7 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B212">
         <v>409141</v>
@@ -9184,10 +9329,10 @@
         <v>24</v>
       </c>
       <c r="E212" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F212" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G212">
         <v>96</v>
@@ -9210,7 +9355,7 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B213">
         <v>409141</v>
@@ -9222,10 +9367,10 @@
         <v>24</v>
       </c>
       <c r="E213" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F213" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G213">
         <v>96</v>
@@ -9248,7 +9393,7 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B214">
         <v>409141</v>
@@ -9260,10 +9405,10 @@
         <v>24</v>
       </c>
       <c r="E214" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F214" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G214">
         <v>402</v>
@@ -9286,7 +9431,7 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B215">
         <v>409141</v>
@@ -9298,10 +9443,10 @@
         <v>24</v>
       </c>
       <c r="E215" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F215" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G215">
         <v>402</v>
@@ -9324,7 +9469,7 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B216">
         <v>409141</v>
@@ -9336,10 +9481,10 @@
         <v>24</v>
       </c>
       <c r="E216" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F216" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G216">
         <v>410</v>
@@ -9362,7 +9507,7 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B217">
         <v>409141</v>
@@ -9374,13 +9519,13 @@
         <v>24</v>
       </c>
       <c r="E217" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F217" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G217" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H217">
         <v>10011512</v>
@@ -9400,7 +9545,7 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B218">
         <v>409141</v>
@@ -9412,10 +9557,10 @@
         <v>24</v>
       </c>
       <c r="E218" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F218" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G218">
         <v>322</v>
@@ -9438,7 +9583,7 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B219">
         <v>409142</v>
@@ -9476,7 +9621,7 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B220">
         <v>409142</v>
@@ -9494,7 +9639,7 @@
         <v>32</v>
       </c>
       <c r="G220" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H220">
         <v>10011425</v>
@@ -9514,7 +9659,7 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B221">
         <v>409142</v>
@@ -9552,7 +9697,7 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B222">
         <v>409142</v>
@@ -9590,7 +9735,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B223">
         <v>409142</v>
@@ -9628,7 +9773,7 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B224">
         <v>409142</v>
@@ -9640,13 +9785,13 @@
         <v>17</v>
       </c>
       <c r="E224" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F224" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G224" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H224">
         <v>10011512</v>
@@ -9666,7 +9811,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B225">
         <v>409142</v>
@@ -9704,7 +9849,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B226">
         <v>409142</v>
@@ -9716,10 +9861,10 @@
         <v>17</v>
       </c>
       <c r="E226" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F226" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G226">
         <v>444</v>
@@ -9742,7 +9887,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B227">
         <v>409142</v>
@@ -9754,10 +9899,10 @@
         <v>17</v>
       </c>
       <c r="E227" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F227" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G227">
         <v>444</v>
@@ -9780,7 +9925,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B228">
         <v>409142</v>
@@ -9792,10 +9937,10 @@
         <v>17</v>
       </c>
       <c r="E228" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F228" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G228">
         <v>525</v>
@@ -9818,7 +9963,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B229">
         <v>409142</v>
@@ -9830,10 +9975,10 @@
         <v>17</v>
       </c>
       <c r="E229" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F229" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G229">
         <v>984</v>
@@ -9856,7 +10001,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B230">
         <v>409142</v>
@@ -9868,10 +10013,10 @@
         <v>17</v>
       </c>
       <c r="E230" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F230" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G230">
         <v>864</v>
@@ -9894,7 +10039,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B231">
         <v>409146</v>
@@ -9906,10 +10051,10 @@
         <v>16</v>
       </c>
       <c r="E231" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F231" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G231">
         <v>171</v>
@@ -9932,7 +10077,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B232">
         <v>409146</v>
@@ -9944,10 +10089,10 @@
         <v>16</v>
       </c>
       <c r="E232" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F232" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G232">
         <v>285</v>
@@ -9970,7 +10115,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B233">
         <v>409146</v>
@@ -9982,10 +10127,10 @@
         <v>16</v>
       </c>
       <c r="E233" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F233" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G233">
         <v>402</v>
@@ -10008,7 +10153,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B234">
         <v>409146</v>
@@ -10020,10 +10165,10 @@
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F234" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G234">
         <v>410</v>
@@ -10046,7 +10191,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B235">
         <v>409146</v>
@@ -10058,13 +10203,13 @@
         <v>16</v>
       </c>
       <c r="E235" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F235" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G235" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H235">
         <v>10011512</v>
@@ -10084,7 +10229,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B236">
         <v>409147</v>
@@ -10122,7 +10267,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B237">
         <v>409147</v>
@@ -10160,7 +10305,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B238">
         <v>409147</v>
@@ -10198,7 +10343,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B239">
         <v>409147</v>
@@ -10213,7 +10358,7 @@
         <v>31</v>
       </c>
       <c r="F239" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G239">
         <v>444</v>
@@ -10236,7 +10381,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B240">
         <v>409147</v>
@@ -10251,7 +10396,7 @@
         <v>31</v>
       </c>
       <c r="F240" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G240">
         <v>984</v>
@@ -10274,7 +10419,7 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B241">
         <v>409147</v>
@@ -10289,7 +10434,7 @@
         <v>31</v>
       </c>
       <c r="F241" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G241">
         <v>864</v>
@@ -10312,7 +10457,7 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B242">
         <v>409148</v>
@@ -10324,10 +10469,10 @@
         <v>13</v>
       </c>
       <c r="E242" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F242" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G242">
         <v>285</v>
@@ -10350,7 +10495,7 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B243">
         <v>409148</v>
@@ -10368,7 +10513,7 @@
         <v>32</v>
       </c>
       <c r="G243" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H243">
         <v>10011425</v>
@@ -10388,7 +10533,7 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B244">
         <v>409148</v>
@@ -10426,7 +10571,7 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B245">
         <v>409148</v>
@@ -10441,10 +10586,10 @@
         <v>31</v>
       </c>
       <c r="F245" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G245" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H245">
         <v>10011512</v>
@@ -10464,7 +10609,7 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B246">
         <v>409148</v>
@@ -10479,7 +10624,7 @@
         <v>31</v>
       </c>
       <c r="F246" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G246">
         <v>444</v>
@@ -10502,7 +10647,7 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B247">
         <v>409148</v>
@@ -10517,7 +10662,7 @@
         <v>31</v>
       </c>
       <c r="F247" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G247">
         <v>525</v>
@@ -10550,19 +10695,19 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1">
         <v>1679427</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H1">
         <v>2259851</v>
@@ -10615,13 +10760,13 @@
         <v>1679427</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H2">
         <v>2259859</v>
@@ -10674,13 +10819,13 @@
         <v>1325989</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>530</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H3">
         <v>8460536</v>
@@ -10733,13 +10878,13 @@
         <v>1326006</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>495</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H4">
         <v>8460563</v>
@@ -10792,13 +10937,13 @@
         <v>1326014</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>531</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H5">
         <v>8460566</v>
@@ -10851,13 +10996,13 @@
         <v>1668366</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>409</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H6">
         <v>75975</v>
@@ -10866,7 +11011,7 @@
         <v>10011425</v>
       </c>
       <c r="J6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>6720000</v>
@@ -10910,13 +11055,13 @@
         <v>1448549</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>22531</v>
       </c>
       <c r="G7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H7">
         <v>833649</v>
@@ -10969,13 +11114,13 @@
         <v>1708026</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F8">
         <v>831</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H8">
         <v>54113</v>
@@ -11028,13 +11173,13 @@
         <v>1708018</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>99268</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H9">
         <v>2218660</v>
@@ -11087,13 +11232,13 @@
         <v>1708026</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>123</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H10">
         <v>54114</v>
@@ -11146,13 +11291,13 @@
         <v>1708018</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>2023</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2218667</v>
@@ -11205,13 +11350,13 @@
         <v>1708018</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12">
         <v>151115</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H12">
         <v>2218669</v>
@@ -11264,13 +11409,13 @@
         <v>1448549</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>22675</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H13">
         <v>833648</v>
@@ -11323,13 +11468,13 @@
         <v>1708018</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H14">
         <v>2218676</v>
@@ -11382,13 +11527,13 @@
         <v>1595390</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15">
         <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H15">
         <v>1100164</v>
@@ -11441,13 +11586,13 @@
         <v>1708018</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H16">
         <v>2218675</v>
@@ -11500,13 +11645,13 @@
         <v>1708018</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H17">
         <v>2218671</v>
@@ -11559,13 +11704,13 @@
         <v>1708018</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>161113</v>
       </c>
       <c r="G18" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H18">
         <v>2218678</v>
@@ -11618,13 +11763,13 @@
         <v>1708018</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F19">
         <v>141103</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H19">
         <v>2218677</v>
@@ -11677,13 +11822,13 @@
         <v>1708018</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F20">
         <v>140101</v>
       </c>
       <c r="G20" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H20">
         <v>2218679</v>
@@ -11736,13 +11881,13 @@
         <v>1708018</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21">
         <v>101</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H21">
         <v>2218680</v>
@@ -11795,13 +11940,13 @@
         <v>1689648</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22">
         <v>139</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H22">
         <v>14194</v>
@@ -11854,13 +11999,13 @@
         <v>1326013</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F23">
         <v>77</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H23">
         <v>100120261</v>
@@ -11869,7 +12014,7 @@
         <v>10011669</v>
       </c>
       <c r="J23" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M23">
         <v>99999999</v>
@@ -11913,13 +12058,13 @@
         <v>1708018</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F24">
         <v>121104</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H24">
         <v>2218681</v>
@@ -11966,19 +12111,19 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B25">
         <v>1701738</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G25" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I25">
         <v>10011503</v>
@@ -12028,13 +12173,13 @@
         <v>1708018</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F26">
         <v>140102</v>
       </c>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H26">
         <v>2218682</v>
@@ -12087,13 +12232,13 @@
         <v>1710065</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F27">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H27">
         <v>3131</v>
@@ -12146,13 +12291,13 @@
         <v>1708018</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F28">
         <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H28">
         <v>2218683</v>
@@ -12205,13 +12350,13 @@
         <v>1325984</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F29">
         <v>783</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H29">
         <v>100120262</v>
@@ -12264,13 +12409,13 @@
         <v>1708018</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F30">
         <v>161105</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H30">
         <v>2224593</v>
@@ -12323,13 +12468,13 @@
         <v>1709881</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F31">
         <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H31">
         <v>2755929</v>
@@ -12382,13 +12527,13 @@
         <v>1326013</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F32">
         <v>783</v>
       </c>
       <c r="G32" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H32">
         <v>100120263</v>
@@ -12441,13 +12586,13 @@
         <v>1699699</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F33">
         <v>245</v>
       </c>
       <c r="G33" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H33">
         <v>775075</v>
@@ -12535,11 +12680,11 @@
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>53</v>
+      <c r="C2" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>48</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -12603,8 +12748,8 @@
       <c r="A2" s="6">
         <v>46296</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>54</v>
+      <c r="B2" s="21" t="s">
+        <v>49</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -12612,16 +12757,16 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>53</v>
+      <c r="E2" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -12629,7 +12774,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -12643,7 +12788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80722F43-7756-4701-9ABB-7A6774075D14}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -12660,18 +12805,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="I1" s="28" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="I1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="29">
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="27">
         <v>51</v>
       </c>
     </row>
@@ -12712,17 +12857,17 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="29"/>
+      <c r="M2" s="27"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="9">
         <v>1692221</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="9">
         <v>10011509</v>
@@ -12744,7 +12889,7 @@
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L3" s="15"/>
     </row>
@@ -12752,11 +12897,11 @@
       <c r="A4" s="12"/>
       <c r="B4" s="13"/>
       <c r="C4" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="21" t="s">
-        <v>40</v>
+      <c r="E4" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
@@ -12768,13 +12913,13 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B5" s="9">
         <v>1692202</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="9">
         <v>10011503</v>
@@ -12796,7 +12941,7 @@
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L5" s="15"/>
     </row>
@@ -12804,11 +12949,11 @@
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="21" t="s">
-        <v>40</v>
+      <c r="E6" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -12820,13 +12965,13 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="9">
         <v>1699707</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9">
         <v>10011509</v>
@@ -12847,7 +12992,7 @@
         <v>232700</v>
       </c>
       <c r="J7" s="11"/>
-      <c r="K7" s="24">
+      <c r="K7" s="22">
         <v>505</v>
       </c>
       <c r="L7" s="15"/>
@@ -12856,7 +13001,7 @@
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -12870,167 +13015,161 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B9" s="9">
-        <v>1326015</v>
+        <v>1692221</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9">
-        <v>10011558</v>
+        <v>10011509</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
-        <v>271400</v>
+        <v>278532</v>
       </c>
       <c r="G9" s="11">
-        <v>72500</v>
+        <v>77735</v>
       </c>
       <c r="H9" s="11">
-        <v>198900</v>
+        <v>200797</v>
       </c>
       <c r="I9" s="18">
-        <v>273200</v>
+        <v>275150</v>
       </c>
       <c r="J9" s="11"/>
-      <c r="K9" s="14">
-        <v>602</v>
+      <c r="K9" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="22" t="s">
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="34"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="36">
+        <v>1326018</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="36">
+        <v>10011503</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="38">
+        <v>277800</v>
+      </c>
+      <c r="G11" s="38">
+        <v>65900</v>
+      </c>
+      <c r="H11" s="38">
+        <v>211900</v>
+      </c>
+      <c r="I11" s="18">
+        <v>278800</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="14">
+        <v>405</v>
+      </c>
+      <c r="L11" s="39"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="40"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="9">
-        <v>1692221</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="9">
-        <v>10011509</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="11">
-        <v>278532</v>
-      </c>
-      <c r="G11" s="11">
-        <v>77735</v>
-      </c>
-      <c r="H11" s="11">
-        <v>200797</v>
-      </c>
-      <c r="I11" s="18">
-        <v>275150</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="22" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="20" t="s">
-        <v>40</v>
-      </c>
+      <c r="E12" s="13"/>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="16"/>
       <c r="J12" s="13"/>
       <c r="K12" s="16"/>
-      <c r="L12" s="17"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>52</v>
+      <c r="A13" s="42" t="s">
+        <v>125</v>
       </c>
       <c r="B13" s="9">
-        <v>1692225</v>
+        <v>1326015</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="9">
-        <v>10011509</v>
+        <v>10011558</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F13" s="11">
-        <v>237482</v>
+        <v>273700</v>
       </c>
       <c r="G13" s="11">
-        <v>70548</v>
+        <v>65900</v>
       </c>
       <c r="H13" s="11">
-        <v>166934</v>
-      </c>
-      <c r="I13" s="18">
-        <v>237450</v>
-      </c>
+        <v>207800</v>
+      </c>
+      <c r="I13" s="28"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="15"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="43"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="13"/>
-      <c r="C14" s="22" t="s">
-        <v>38</v>
+      <c r="C14" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="20" t="s">
-        <v>40</v>
-      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="16"/>
       <c r="J14" s="13"/>
       <c r="K14" s="16"/>
-      <c r="L14" s="17"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>55</v>
+      <c r="A15" s="42" t="s">
+        <v>126</v>
       </c>
       <c r="B15" s="9">
-        <v>1442707</v>
+        <v>1490615</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D15" s="9">
         <v>10011503</v>
@@ -13039,192 +13178,84 @@
         <v>29</v>
       </c>
       <c r="F15" s="11">
-        <v>233000</v>
+        <v>193200</v>
       </c>
       <c r="G15" s="11">
-        <v>60500</v>
+        <v>66800</v>
       </c>
       <c r="H15" s="11">
-        <v>172500</v>
-      </c>
-      <c r="I15" s="18">
-        <v>232150</v>
-      </c>
+        <v>126400</v>
+      </c>
+      <c r="I15" s="28"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15" s="15"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="43"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="13"/>
       <c r="C16" s="19" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D16" s="13"/>
-      <c r="E16" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="16"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="17"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>57</v>
+      <c r="A17" s="42" t="s">
+        <v>128</v>
       </c>
       <c r="B17" s="9">
-        <v>1326018</v>
+        <v>1437341</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D17" s="9">
-        <v>10011503</v>
+        <v>10011660</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="F17" s="11">
-        <v>258400</v>
+        <v>284000</v>
       </c>
       <c r="G17" s="11">
-        <v>71000</v>
+        <v>68200</v>
       </c>
       <c r="H17" s="11">
-        <v>187400</v>
+        <v>215800</v>
       </c>
       <c r="I17" s="18">
-        <v>258950</v>
+        <v>285850</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="14">
-        <v>405</v>
-      </c>
-      <c r="L17" s="15"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+        <v>149</v>
+      </c>
+      <c r="L17" s="43"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="44"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
       <c r="I18" s="16"/>
       <c r="J18" s="13"/>
       <c r="K18" s="16"/>
-      <c r="L18" s="17"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="9">
-        <v>1326015</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="9">
-        <v>10011558</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="11">
-        <v>253200</v>
-      </c>
-      <c r="G19" s="11">
-        <v>64400</v>
-      </c>
-      <c r="H19" s="11">
-        <v>188800</v>
-      </c>
-      <c r="I19" s="18">
-        <v>253400</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="L19" s="15"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="17"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="9">
-        <v>1701738</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="9">
-        <v>10011503</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="11">
-        <v>281170</v>
-      </c>
-      <c r="G21" s="11">
-        <v>80250</v>
-      </c>
-      <c r="H21" s="11">
-        <v>200920</v>
-      </c>
-      <c r="I21" s="18">
-        <v>282850</v>
-      </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="14">
-        <v>405</v>
-      </c>
-      <c r="L21" s="15"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="17"/>
+      <c r="L18" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01037D5D-2805-4CB7-B799-23A6CCDE8801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46302D-54CA-44E6-90E6-9A877A5E318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="301">
   <si>
     <t>Date</t>
   </si>
@@ -938,6 +938,9 @@
   <si>
     <t>H146230</t>
   </si>
+  <si>
+    <t>TBD</t>
+  </si>
 </sst>
 </file>
 
@@ -1355,7 +1358,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1405,9 +1408,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -43835,18 +43835,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="44"/>
-      <c r="I1" s="45" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="43"/>
+      <c r="I1" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="46">
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="45">
         <v>51</v>
       </c>
     </row>
@@ -43887,7 +43887,7 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="46"/>
+      <c r="M2" s="45"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -44078,40 +44078,40 @@
       <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="C10" s="25" t="s">
+      <c r="A10" s="23"/>
+      <c r="C10" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="28"/>
+      <c r="I10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>1326018</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>10011503</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="31">
         <v>277800</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="31">
         <v>65900</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="31">
         <v>211900</v>
       </c>
       <c r="I11" s="18">
@@ -44121,10 +44121,10 @@
       <c r="K11" s="14">
         <v>405</v>
       </c>
-      <c r="L11" s="33"/>
+      <c r="L11" s="32"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
         <v>26</v>
@@ -44137,10 +44137,10 @@
       <c r="I12" s="16"/>
       <c r="J12" s="13"/>
       <c r="K12" s="16"/>
-      <c r="L12" s="35"/>
+      <c r="L12" s="34"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="35" t="s">
         <v>125</v>
       </c>
       <c r="B13" s="9">
@@ -44164,13 +44164,17 @@
       <c r="H13" s="11">
         <v>207800</v>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="18">
+        <v>274100</v>
+      </c>
       <c r="J13" s="11"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="37"/>
+      <c r="K13" s="14">
+        <v>602</v>
+      </c>
+      <c r="L13" s="36"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="13"/>
       <c r="C14" s="19" t="s">
         <v>26</v>
@@ -44183,10 +44187,10 @@
       <c r="I14" s="16"/>
       <c r="J14" s="13"/>
       <c r="K14" s="16"/>
-      <c r="L14" s="35"/>
+      <c r="L14" s="34"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="35" t="s">
         <v>126</v>
       </c>
       <c r="B15" s="9">
@@ -44210,13 +44214,17 @@
       <c r="H15" s="11">
         <v>126400</v>
       </c>
-      <c r="I15" s="23"/>
+      <c r="I15" s="18">
+        <v>192800</v>
+      </c>
       <c r="J15" s="11"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="37"/>
+      <c r="K15" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="L15" s="36"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="13"/>
       <c r="C16" s="19" t="s">
         <v>27</v>
@@ -44229,10 +44237,10 @@
       <c r="I16" s="16"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="35"/>
+      <c r="L16" s="34"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="35" t="s">
         <v>128</v>
       </c>
       <c r="B17" s="9">
@@ -44263,23 +44271,23 @@
       <c r="K17" s="14">
         <v>149</v>
       </c>
-      <c r="L17" s="37"/>
+      <c r="L17" s="36"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40" t="s">
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="16"/>
       <c r="J18" s="13"/>
       <c r="K18" s="16"/>
-      <c r="L18" s="41"/>
+      <c r="L18" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FB9FE9-FFA8-4C5F-B664-7BEB8A00DC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341B42F7-1643-46BA-BD5D-C41D2924FCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3972" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="365">
   <si>
     <t>Date</t>
   </si>
@@ -939,9 +939,6 @@
     <t>H146230</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>032852/3</t>
   </si>
   <si>
@@ -1130,6 +1127,12 @@
   <si>
     <t>H146253</t>
   </si>
+  <si>
+    <t>Released</t>
+  </si>
+  <si>
+    <t>Empty 10/6</t>
+  </si>
 </sst>
 </file>
 
@@ -1217,15 +1220,21 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1437,37 +1446,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1507,37 +1485,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1547,7 +1494,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1606,35 +1553,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1650,6 +1576,37 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -38170,7 +38127,7 @@
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B953">
         <v>409108</v>
@@ -38208,7 +38165,7 @@
     </row>
     <row r="954" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B954">
         <v>409108</v>
@@ -38246,7 +38203,7 @@
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B955">
         <v>409108</v>
@@ -38284,7 +38241,7 @@
     </row>
     <row r="956" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B956">
         <v>409108</v>
@@ -38322,7 +38279,7 @@
     </row>
     <row r="957" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B957">
         <v>409108</v>
@@ -38360,7 +38317,7 @@
     </row>
     <row r="958" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B958">
         <v>409108</v>
@@ -38398,7 +38355,7 @@
     </row>
     <row r="959" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B959">
         <v>409109</v>
@@ -38436,7 +38393,7 @@
     </row>
     <row r="960" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B960">
         <v>409109</v>
@@ -38474,7 +38431,7 @@
     </row>
     <row r="961" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B961">
         <v>409109</v>
@@ -38512,7 +38469,7 @@
     </row>
     <row r="962" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B962">
         <v>409101</v>
@@ -38550,7 +38507,7 @@
     </row>
     <row r="963" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B963">
         <v>409101</v>
@@ -38588,7 +38545,7 @@
     </row>
     <row r="964" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B964">
         <v>409101</v>
@@ -38626,7 +38583,7 @@
     </row>
     <row r="965" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B965">
         <v>409101</v>
@@ -38664,7 +38621,7 @@
     </row>
     <row r="966" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B966">
         <v>409101</v>
@@ -38702,7 +38659,7 @@
     </row>
     <row r="967" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B967">
         <v>409101</v>
@@ -38740,7 +38697,7 @@
     </row>
     <row r="968" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B968">
         <v>409101</v>
@@ -38778,7 +38735,7 @@
     </row>
     <row r="969" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B969">
         <v>409101</v>
@@ -38816,7 +38773,7 @@
     </row>
     <row r="970" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B970">
         <v>409101</v>
@@ -38854,7 +38811,7 @@
     </row>
     <row r="971" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B971">
         <v>409101</v>
@@ -38892,7 +38849,7 @@
     </row>
     <row r="972" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B972">
         <v>409101</v>
@@ -38930,7 +38887,7 @@
     </row>
     <row r="973" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B973">
         <v>409101</v>
@@ -39196,7 +39153,7 @@
     </row>
     <row r="980" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B980">
         <v>409101</v>
@@ -39234,7 +39191,7 @@
     </row>
     <row r="981" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B981">
         <v>409101</v>
@@ -39272,7 +39229,7 @@
     </row>
     <row r="982" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B982">
         <v>409101</v>
@@ -39310,7 +39267,7 @@
     </row>
     <row r="983" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B983">
         <v>409101</v>
@@ -39348,7 +39305,7 @@
     </row>
     <row r="984" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B984">
         <v>409101</v>
@@ -39386,7 +39343,7 @@
     </row>
     <row r="985" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B985">
         <v>409101</v>
@@ -39424,7 +39381,7 @@
     </row>
     <row r="986" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B986">
         <v>409101</v>
@@ -39462,7 +39419,7 @@
     </row>
     <row r="987" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B987">
         <v>409101</v>
@@ -39500,7 +39457,7 @@
     </row>
     <row r="988" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B988">
         <v>409101</v>
@@ -39538,7 +39495,7 @@
     </row>
     <row r="989" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B989">
         <v>409101</v>
@@ -39576,7 +39533,7 @@
     </row>
     <row r="990" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B990">
         <v>409101</v>
@@ -39614,7 +39571,7 @@
     </row>
     <row r="991" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B991">
         <v>409101</v>
@@ -39652,7 +39609,7 @@
     </row>
     <row r="992" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B992">
         <v>409102</v>
@@ -39690,7 +39647,7 @@
     </row>
     <row r="993" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B993">
         <v>409102</v>
@@ -39728,7 +39685,7 @@
     </row>
     <row r="994" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B994">
         <v>409102</v>
@@ -39766,7 +39723,7 @@
     </row>
     <row r="995" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B995">
         <v>409102</v>
@@ -39804,7 +39761,7 @@
     </row>
     <row r="996" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B996">
         <v>409102</v>
@@ -39842,7 +39799,7 @@
     </row>
     <row r="997" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B997">
         <v>409102</v>
@@ -39880,7 +39837,7 @@
     </row>
     <row r="998" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B998">
         <v>409102</v>
@@ -39918,7 +39875,7 @@
     </row>
     <row r="999" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B999">
         <v>409102</v>
@@ -39956,7 +39913,7 @@
     </row>
     <row r="1000" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1000">
         <v>409102</v>
@@ -39994,7 +39951,7 @@
     </row>
     <row r="1001" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1001">
         <v>409102</v>
@@ -40032,7 +39989,7 @@
     </row>
     <row r="1002" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1002">
         <v>409102</v>
@@ -40070,7 +40027,7 @@
     </row>
     <row r="1003" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1003">
         <v>409102</v>
@@ -40108,7 +40065,7 @@
     </row>
     <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1004">
         <v>409101</v>
@@ -40146,7 +40103,7 @@
     </row>
     <row r="1005" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1005">
         <v>409101</v>
@@ -40184,7 +40141,7 @@
     </row>
     <row r="1006" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1006">
         <v>409101</v>
@@ -40222,7 +40179,7 @@
     </row>
     <row r="1007" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1007">
         <v>409101</v>
@@ -40260,7 +40217,7 @@
     </row>
     <row r="1008" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1008">
         <v>409101</v>
@@ -40298,7 +40255,7 @@
     </row>
     <row r="1009" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1009">
         <v>409101</v>
@@ -40336,7 +40293,7 @@
     </row>
     <row r="1010" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1010">
         <v>409101</v>
@@ -40374,7 +40331,7 @@
     </row>
     <row r="1011" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1011">
         <v>409101</v>
@@ -40412,7 +40369,7 @@
     </row>
     <row r="1012" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1012">
         <v>409101</v>
@@ -40450,7 +40407,7 @@
     </row>
     <row r="1013" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1013">
         <v>409101</v>
@@ -40488,7 +40445,7 @@
     </row>
     <row r="1014" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1014">
         <v>409101</v>
@@ -40526,7 +40483,7 @@
     </row>
     <row r="1015" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1015">
         <v>409101</v>
@@ -40564,7 +40521,7 @@
     </row>
     <row r="1016" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1016">
         <v>409102</v>
@@ -40602,7 +40559,7 @@
     </row>
     <row r="1017" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1017">
         <v>409102</v>
@@ -40640,7 +40597,7 @@
     </row>
     <row r="1018" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1018">
         <v>409102</v>
@@ -40678,7 +40635,7 @@
     </row>
     <row r="1019" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1019">
         <v>409102</v>
@@ -40716,7 +40673,7 @@
     </row>
     <row r="1020" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1020">
         <v>409102</v>
@@ -40754,7 +40711,7 @@
     </row>
     <row r="1021" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1021">
         <v>409102</v>
@@ -40792,7 +40749,7 @@
     </row>
     <row r="1022" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1022">
         <v>409102</v>
@@ -40830,7 +40787,7 @@
     </row>
     <row r="1023" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1023">
         <v>409102</v>
@@ -40868,7 +40825,7 @@
     </row>
     <row r="1024" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1024">
         <v>409102</v>
@@ -40906,7 +40863,7 @@
     </row>
     <row r="1025" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1025">
         <v>409102</v>
@@ -40944,7 +40901,7 @@
     </row>
     <row r="1026" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1026">
         <v>409102</v>
@@ -40982,7 +40939,7 @@
     </row>
     <row r="1027" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1027">
         <v>409102</v>
@@ -41020,7 +40977,7 @@
     </row>
     <row r="1028" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1028">
         <v>409106</v>
@@ -41058,7 +41015,7 @@
     </row>
     <row r="1029" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1029">
         <v>409106</v>
@@ -41096,7 +41053,7 @@
     </row>
     <row r="1030" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1030">
         <v>409106</v>
@@ -41134,7 +41091,7 @@
     </row>
     <row r="1031" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1031">
         <v>409106</v>
@@ -41172,7 +41129,7 @@
     </row>
     <row r="1032" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1032">
         <v>409106</v>
@@ -41210,7 +41167,7 @@
     </row>
     <row r="1033" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1033">
         <v>409107</v>
@@ -41248,7 +41205,7 @@
     </row>
     <row r="1034" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1034">
         <v>409107</v>
@@ -41286,7 +41243,7 @@
     </row>
     <row r="1035" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1035">
         <v>409107</v>
@@ -41324,7 +41281,7 @@
     </row>
     <row r="1036" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1036">
         <v>409107</v>
@@ -41362,7 +41319,7 @@
     </row>
     <row r="1037" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1037">
         <v>409107</v>
@@ -41400,7 +41357,7 @@
     </row>
     <row r="1038" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1038">
         <v>409107</v>
@@ -41438,7 +41395,7 @@
     </row>
     <row r="1039" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1039">
         <v>409108</v>
@@ -41476,7 +41433,7 @@
     </row>
     <row r="1040" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1040">
         <v>409108</v>
@@ -41514,7 +41471,7 @@
     </row>
     <row r="1041" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1041">
         <v>409108</v>
@@ -41552,7 +41509,7 @@
     </row>
     <row r="1042" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1042">
         <v>409108</v>
@@ -41590,7 +41547,7 @@
     </row>
     <row r="1043" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1043">
         <v>409108</v>
@@ -41628,7 +41585,7 @@
     </row>
     <row r="1044" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1044">
         <v>409108</v>
@@ -41666,7 +41623,7 @@
     </row>
     <row r="1045" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1045">
         <v>409109</v>
@@ -41704,7 +41661,7 @@
     </row>
     <row r="1046" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1046">
         <v>409109</v>
@@ -41742,7 +41699,7 @@
     </row>
     <row r="1047" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1047">
         <v>409109</v>
@@ -41780,7 +41737,7 @@
     </row>
     <row r="1048" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1048">
         <v>436111</v>
@@ -41818,7 +41775,7 @@
     </row>
     <row r="1049" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1049">
         <v>436111</v>
@@ -41856,7 +41813,7 @@
     </row>
     <row r="1050" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1050">
         <v>436111</v>
@@ -41894,7 +41851,7 @@
     </row>
     <row r="1051" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1051">
         <v>436111</v>
@@ -41932,7 +41889,7 @@
     </row>
     <row r="1052" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1052">
         <v>436111</v>
@@ -41970,7 +41927,7 @@
     </row>
     <row r="1053" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1053">
         <v>436111</v>
@@ -42008,7 +41965,7 @@
     </row>
     <row r="1054" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1054">
         <v>436111</v>
@@ -42046,7 +42003,7 @@
     </row>
     <row r="1055" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1055">
         <v>436111</v>
@@ -42084,7 +42041,7 @@
     </row>
     <row r="1056" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1056">
         <v>436111</v>
@@ -42122,7 +42079,7 @@
     </row>
     <row r="1057" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1057">
         <v>436111</v>
@@ -42160,7 +42117,7 @@
     </row>
     <row r="1058" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1058">
         <v>436111</v>
@@ -42198,7 +42155,7 @@
     </row>
     <row r="1059" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1059">
         <v>436111</v>
@@ -42236,7 +42193,7 @@
     </row>
     <row r="1060" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1060">
         <v>436112</v>
@@ -42274,7 +42231,7 @@
     </row>
     <row r="1061" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1061">
         <v>436112</v>
@@ -42312,7 +42269,7 @@
     </row>
     <row r="1062" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1062">
         <v>436112</v>
@@ -42350,7 +42307,7 @@
     </row>
     <row r="1063" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1063">
         <v>436112</v>
@@ -42388,7 +42345,7 @@
     </row>
     <row r="1064" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1064">
         <v>436112</v>
@@ -42426,7 +42383,7 @@
     </row>
     <row r="1065" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1065">
         <v>436112</v>
@@ -42464,7 +42421,7 @@
     </row>
     <row r="1066" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1066">
         <v>436112</v>
@@ -42502,7 +42459,7 @@
     </row>
     <row r="1067" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1067">
         <v>436112</v>
@@ -42540,7 +42497,7 @@
     </row>
     <row r="1068" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1068">
         <v>436112</v>
@@ -42578,7 +42535,7 @@
     </row>
     <row r="1069" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1069">
         <v>436112</v>
@@ -42616,7 +42573,7 @@
     </row>
     <row r="1070" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1070">
         <v>436112</v>
@@ -42654,7 +42611,7 @@
     </row>
     <row r="1071" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B1071">
         <v>436116</v>
@@ -42692,7 +42649,7 @@
     </row>
     <row r="1072" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B1072">
         <v>436116</v>
@@ -42730,7 +42687,7 @@
     </row>
     <row r="1073" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B1073">
         <v>436116</v>
@@ -42768,7 +42725,7 @@
     </row>
     <row r="1074" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B1074">
         <v>436116</v>
@@ -42806,7 +42763,7 @@
     </row>
     <row r="1075" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1075">
         <v>436117</v>
@@ -42844,7 +42801,7 @@
     </row>
     <row r="1076" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1076">
         <v>436117</v>
@@ -42882,7 +42839,7 @@
     </row>
     <row r="1077" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1077">
         <v>436117</v>
@@ -42920,7 +42877,7 @@
     </row>
     <row r="1078" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1078">
         <v>436117</v>
@@ -42958,7 +42915,7 @@
     </row>
     <row r="1079" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1079">
         <v>436117</v>
@@ -42996,7 +42953,7 @@
     </row>
     <row r="1080" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1080">
         <v>436117</v>
@@ -43034,7 +42991,7 @@
     </row>
     <row r="1081" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1081">
         <v>436118</v>
@@ -43072,7 +43029,7 @@
     </row>
     <row r="1082" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1082">
         <v>436118</v>
@@ -43110,7 +43067,7 @@
     </row>
     <row r="1083" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1083">
         <v>436118</v>
@@ -43148,7 +43105,7 @@
     </row>
     <row r="1084" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1084">
         <v>436118</v>
@@ -43186,7 +43143,7 @@
     </row>
     <row r="1085" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1085">
         <v>436118</v>
@@ -43224,7 +43181,7 @@
     </row>
     <row r="1086" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1086">
         <v>436119</v>
@@ -43262,7 +43219,7 @@
     </row>
     <row r="1087" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1087">
         <v>436119</v>
@@ -43300,7 +43257,7 @@
     </row>
     <row r="1088" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1088">
         <v>436111</v>
@@ -43338,7 +43295,7 @@
     </row>
     <row r="1089" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1089">
         <v>436111</v>
@@ -43376,7 +43333,7 @@
     </row>
     <row r="1090" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1090">
         <v>436111</v>
@@ -43414,7 +43371,7 @@
     </row>
     <row r="1091" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1091">
         <v>436111</v>
@@ -43452,7 +43409,7 @@
     </row>
     <row r="1092" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1092">
         <v>436111</v>
@@ -43490,7 +43447,7 @@
     </row>
     <row r="1093" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1093">
         <v>436111</v>
@@ -43528,7 +43485,7 @@
     </row>
     <row r="1094" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1094">
         <v>436111</v>
@@ -43566,7 +43523,7 @@
     </row>
     <row r="1095" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1095">
         <v>436111</v>
@@ -43604,7 +43561,7 @@
     </row>
     <row r="1096" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1096">
         <v>436111</v>
@@ -43642,7 +43599,7 @@
     </row>
     <row r="1097" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1097">
         <v>436111</v>
@@ -43680,7 +43637,7 @@
     </row>
     <row r="1098" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1098">
         <v>436111</v>
@@ -43718,7 +43675,7 @@
     </row>
     <row r="1099" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1099">
         <v>436111</v>
@@ -43756,7 +43713,7 @@
     </row>
     <row r="1100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1100">
         <v>436112</v>
@@ -43794,7 +43751,7 @@
     </row>
     <row r="1101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1101">
         <v>436112</v>
@@ -43832,7 +43789,7 @@
     </row>
     <row r="1102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1102">
         <v>436112</v>
@@ -43870,7 +43827,7 @@
     </row>
     <row r="1103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1103">
         <v>436112</v>
@@ -43908,7 +43865,7 @@
     </row>
     <row r="1104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1104">
         <v>436112</v>
@@ -43946,7 +43903,7 @@
     </row>
     <row r="1105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1105">
         <v>436112</v>
@@ -43984,7 +43941,7 @@
     </row>
     <row r="1106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1106">
         <v>436112</v>
@@ -44022,7 +43979,7 @@
     </row>
     <row r="1107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1107">
         <v>436112</v>
@@ -44060,7 +44017,7 @@
     </row>
     <row r="1108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1108">
         <v>436112</v>
@@ -44098,7 +44055,7 @@
     </row>
     <row r="1109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1109">
         <v>436112</v>
@@ -44136,7 +44093,7 @@
     </row>
     <row r="1110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1110">
         <v>436112</v>
@@ -44174,7 +44131,7 @@
     </row>
     <row r="1111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1111">
         <v>436111</v>
@@ -44212,7 +44169,7 @@
     </row>
     <row r="1112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1112">
         <v>171106</v>
@@ -44250,7 +44207,7 @@
     </row>
     <row r="1113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1113">
         <v>171106</v>
@@ -44288,7 +44245,7 @@
     </row>
     <row r="1114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1114">
         <v>171106</v>
@@ -44326,7 +44283,7 @@
     </row>
     <row r="1115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1115">
         <v>171106</v>
@@ -44364,7 +44321,7 @@
     </row>
     <row r="1116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1116">
         <v>171107</v>
@@ -44402,7 +44359,7 @@
     </row>
     <row r="1117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1117">
         <v>171107</v>
@@ -44440,7 +44397,7 @@
     </row>
     <row r="1118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1118">
         <v>171107</v>
@@ -44478,7 +44435,7 @@
     </row>
     <row r="1119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1119">
         <v>171107</v>
@@ -44516,7 +44473,7 @@
     </row>
     <row r="1120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1120">
         <v>171107</v>
@@ -44554,7 +44511,7 @@
     </row>
     <row r="1121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1121">
         <v>171107</v>
@@ -44592,7 +44549,7 @@
     </row>
     <row r="1122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1122">
         <v>171108</v>
@@ -44630,7 +44587,7 @@
     </row>
     <row r="1123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1123">
         <v>171108</v>
@@ -44668,7 +44625,7 @@
     </row>
     <row r="1124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1124">
         <v>171108</v>
@@ -44706,7 +44663,7 @@
     </row>
     <row r="1125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1125">
         <v>171108</v>
@@ -44744,7 +44701,7 @@
     </row>
     <row r="1126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1126">
         <v>171108</v>
@@ -44782,7 +44739,7 @@
     </row>
     <row r="1127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1127">
         <v>171108</v>
@@ -44820,7 +44777,7 @@
     </row>
     <row r="1128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1128">
         <v>171109</v>
@@ -44858,7 +44815,7 @@
     </row>
     <row r="1129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1129">
         <v>171109</v>
@@ -44896,7 +44853,7 @@
     </row>
     <row r="1130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1130">
         <v>439111</v>
@@ -44934,7 +44891,7 @@
     </row>
     <row r="1131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1131">
         <v>439111</v>
@@ -44972,7 +44929,7 @@
     </row>
     <row r="1132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1132">
         <v>439111</v>
@@ -45010,7 +44967,7 @@
     </row>
     <row r="1133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1133">
         <v>439111</v>
@@ -45048,7 +45005,7 @@
     </row>
     <row r="1134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1134">
         <v>439111</v>
@@ -45086,7 +45043,7 @@
     </row>
     <row r="1135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1135">
         <v>439111</v>
@@ -45124,7 +45081,7 @@
     </row>
     <row r="1136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1136">
         <v>439111</v>
@@ -45162,7 +45119,7 @@
     </row>
     <row r="1137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1137">
         <v>439111</v>
@@ -45200,7 +45157,7 @@
     </row>
     <row r="1138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1138">
         <v>439111</v>
@@ -45238,7 +45195,7 @@
     </row>
     <row r="1139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1139">
         <v>439111</v>
@@ -45276,7 +45233,7 @@
     </row>
     <row r="1140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1140">
         <v>439111</v>
@@ -45314,7 +45271,7 @@
     </row>
     <row r="1141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1141">
         <v>439111</v>
@@ -45352,7 +45309,7 @@
     </row>
     <row r="1142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1142">
         <v>439112</v>
@@ -45390,7 +45347,7 @@
     </row>
     <row r="1143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1143">
         <v>439112</v>
@@ -45428,7 +45385,7 @@
     </row>
     <row r="1144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1144">
         <v>439112</v>
@@ -45466,7 +45423,7 @@
     </row>
     <row r="1145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1145">
         <v>439112</v>
@@ -45504,7 +45461,7 @@
     </row>
     <row r="1146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1146">
         <v>439112</v>
@@ -45542,7 +45499,7 @@
     </row>
     <row r="1147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1147">
         <v>439112</v>
@@ -45580,7 +45537,7 @@
     </row>
     <row r="1148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1148">
         <v>439112</v>
@@ -45618,7 +45575,7 @@
     </row>
     <row r="1149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1149">
         <v>439112</v>
@@ -45656,7 +45613,7 @@
     </row>
     <row r="1150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1150">
         <v>439112</v>
@@ -45694,7 +45651,7 @@
     </row>
     <row r="1151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1151">
         <v>439112</v>
@@ -45732,7 +45689,7 @@
     </row>
     <row r="1152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1152">
         <v>439112</v>
@@ -45770,7 +45727,7 @@
     </row>
     <row r="1153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1153">
         <v>439111</v>
@@ -45808,7 +45765,7 @@
     </row>
     <row r="1154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1154">
         <v>439111</v>
@@ -45846,7 +45803,7 @@
     </row>
     <row r="1155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1155">
         <v>439111</v>
@@ -45884,7 +45841,7 @@
     </row>
     <row r="1156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1156">
         <v>439111</v>
@@ -45922,7 +45879,7 @@
     </row>
     <row r="1157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1157">
         <v>439111</v>
@@ -45960,7 +45917,7 @@
     </row>
     <row r="1158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1158">
         <v>439111</v>
@@ -45998,7 +45955,7 @@
     </row>
     <row r="1159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1159">
         <v>439111</v>
@@ -46036,7 +45993,7 @@
     </row>
     <row r="1160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1160">
         <v>439111</v>
@@ -46074,7 +46031,7 @@
     </row>
     <row r="1161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1161">
         <v>439111</v>
@@ -46112,7 +46069,7 @@
     </row>
     <row r="1162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1162">
         <v>439111</v>
@@ -46150,7 +46107,7 @@
     </row>
     <row r="1163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1163">
         <v>439111</v>
@@ -46188,7 +46145,7 @@
     </row>
     <row r="1164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1164">
         <v>439111</v>
@@ -46226,7 +46183,7 @@
     </row>
     <row r="1165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1165">
         <v>439112</v>
@@ -46264,7 +46221,7 @@
     </row>
     <row r="1166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1166">
         <v>439112</v>
@@ -46302,7 +46259,7 @@
     </row>
     <row r="1167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1167">
         <v>439112</v>
@@ -46340,7 +46297,7 @@
     </row>
     <row r="1168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1168">
         <v>439112</v>
@@ -46378,7 +46335,7 @@
     </row>
     <row r="1169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1169">
         <v>439112</v>
@@ -52264,7 +52221,7 @@
         <v>288</v>
       </c>
       <c r="G100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H100">
         <v>2260160</v>
@@ -52323,7 +52280,7 @@
         <v>4</v>
       </c>
       <c r="G101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H101">
         <v>2260173</v>
@@ -52382,7 +52339,7 @@
         <v>141</v>
       </c>
       <c r="G102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H102">
         <v>1100179</v>
@@ -52441,7 +52398,7 @@
         <v>139</v>
       </c>
       <c r="G103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H103">
         <v>1100176</v>
@@ -52500,7 +52457,7 @@
         <v>10</v>
       </c>
       <c r="G104" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H104">
         <v>2768293</v>
@@ -52559,7 +52516,7 @@
         <v>140</v>
       </c>
       <c r="G105" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H105">
         <v>14207</v>
@@ -52618,7 +52575,7 @@
         <v>44734</v>
       </c>
       <c r="G106" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H106">
         <v>1100175</v>
@@ -52677,7 +52634,7 @@
         <v>132</v>
       </c>
       <c r="G107" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H107">
         <v>2775848</v>
@@ -52736,7 +52693,7 @@
         <v>409</v>
       </c>
       <c r="G108" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H108">
         <v>76004</v>
@@ -52745,7 +52702,7 @@
         <v>10011425</v>
       </c>
       <c r="J108" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M108">
         <v>6720000</v>
@@ -52795,7 +52752,7 @@
         <v>22636</v>
       </c>
       <c r="G109" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H109">
         <v>2642953</v>
@@ -52854,7 +52811,7 @@
         <v>22667</v>
       </c>
       <c r="G110" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H110">
         <v>2642959</v>
@@ -52913,7 +52870,7 @@
         <v>22531</v>
       </c>
       <c r="G111" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H111">
         <v>833652</v>
@@ -52972,7 +52929,7 @@
         <v>469</v>
       </c>
       <c r="G112" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H112">
         <v>54807</v>
@@ -53031,7 +52988,7 @@
         <v>131</v>
       </c>
       <c r="G113" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H113">
         <v>2782021</v>
@@ -53090,7 +53047,7 @@
         <v>19</v>
       </c>
       <c r="G114" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H114">
         <v>2782030</v>
@@ -53149,7 +53106,7 @@
         <v>22675</v>
       </c>
       <c r="G115" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H115">
         <v>833653</v>
@@ -53208,7 +53165,7 @@
         <v>783</v>
       </c>
       <c r="G116" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H116">
         <v>100520261</v>
@@ -53267,7 +53224,7 @@
         <v>130</v>
       </c>
       <c r="G117" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H117">
         <v>2782212</v>
@@ -53326,7 +53283,7 @@
         <v>133</v>
       </c>
       <c r="G118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H118">
         <v>2782354</v>
@@ -53385,7 +53342,7 @@
         <v>23</v>
       </c>
       <c r="G119" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H119">
         <v>2783169</v>
@@ -53444,7 +53401,7 @@
         <v>67</v>
       </c>
       <c r="G120" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H120">
         <v>76008</v>
@@ -53503,7 +53460,7 @@
         <v>783</v>
       </c>
       <c r="G121" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H121">
         <v>100520262</v>
@@ -53562,7 +53519,7 @@
         <v>22661</v>
       </c>
       <c r="G122" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H122">
         <v>2642958</v>
@@ -53621,7 +53578,7 @@
         <v>22632</v>
       </c>
       <c r="G123" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H123">
         <v>2642957</v>
@@ -53680,7 +53637,7 @@
         <v>169</v>
       </c>
       <c r="G124" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H124">
         <v>775748</v>
@@ -53739,7 +53696,7 @@
         <v>783</v>
       </c>
       <c r="G125" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H125">
         <v>100520263</v>
@@ -53798,7 +53755,7 @@
         <v>666</v>
       </c>
       <c r="G126" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H126">
         <v>50272</v>
@@ -53857,7 +53814,7 @@
         <v>70</v>
       </c>
       <c r="G127" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H127">
         <v>2260159</v>
@@ -53916,7 +53873,7 @@
         <v>19</v>
       </c>
       <c r="G128" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H128">
         <v>2786136</v>
@@ -53975,7 +53932,7 @@
         <v>133</v>
       </c>
       <c r="G129" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H129">
         <v>2786608</v>
@@ -54034,7 +53991,7 @@
         <v>22663</v>
       </c>
       <c r="G130" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H130">
         <v>2642955</v>
@@ -54093,7 +54050,7 @@
         <v>169</v>
       </c>
       <c r="G131" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H131">
         <v>775838</v>
@@ -54152,7 +54109,7 @@
         <v>22636</v>
       </c>
       <c r="G132" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H132">
         <v>2642964</v>
@@ -54211,7 +54168,7 @@
         <v>23</v>
       </c>
       <c r="G133" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H133">
         <v>2787705</v>
@@ -54270,7 +54227,7 @@
         <v>386</v>
       </c>
       <c r="G134" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H134">
         <v>49291</v>
@@ -54483,18 +54440,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="43"/>
-      <c r="I1" s="44" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="34"/>
+      <c r="I1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="45">
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="36">
         <v>51</v>
       </c>
     </row>
@@ -54535,7 +54492,7 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="45"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -54725,7 +54682,7 @@
       </c>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="C10" s="24" t="s">
         <v>36</v>
@@ -54738,57 +54695,63 @@
       <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="38">
         <v>1326018</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="38">
         <v>10011503</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="40">
         <v>277800</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="40">
         <v>65900</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="40">
         <v>211900</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="41">
         <v>278800</v>
       </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="14">
+      <c r="J11" s="42">
+        <v>88700</v>
+      </c>
+      <c r="K11" s="43">
         <v>405</v>
       </c>
-      <c r="L11" s="32"/>
+      <c r="L11" s="44" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="45"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="34"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="49" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="30" t="s">
         <v>125</v>
       </c>
       <c r="B13" s="9">
@@ -54819,10 +54782,10 @@
       <c r="K13" s="14">
         <v>602</v>
       </c>
-      <c r="L13" s="36"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="13"/>
       <c r="C14" s="19" t="s">
         <v>26</v>
@@ -54835,107 +54798,119 @@
       <c r="I14" s="16"/>
       <c r="J14" s="13"/>
       <c r="K14" s="16"/>
-      <c r="L14" s="34"/>
+      <c r="L14" s="29"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="38">
         <v>1490615</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="38">
         <v>10011503</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="40">
         <v>193200</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="40">
         <v>66800</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="40">
         <v>126400</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="41">
         <v>192800</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="L15" s="36"/>
+      <c r="J15" s="42">
+        <v>65750</v>
+      </c>
+      <c r="K15" s="43">
+        <v>405</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="45"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="34"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="49" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="38">
         <v>1437341</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="38">
         <v>10011660</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="40">
         <v>284000</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="40">
         <v>68200</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="40">
         <v>215800</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="41">
         <v>285850</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="14">
+      <c r="J17" s="42">
+        <v>67850</v>
+      </c>
+      <c r="K17" s="43">
         <v>149</v>
       </c>
-      <c r="L17" s="36"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39" t="s">
+      <c r="L17" s="44" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="45"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="40"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="49" t="s">
+        <v>364</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341B42F7-1643-46BA-BD5D-C41D2924FCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF58F5C6-493F-4C70-951E-6EA5D2ED01D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="365">
   <si>
     <t>Date</t>
   </si>
@@ -1234,7 +1234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1441,50 +1441,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1494,7 +1450,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1553,14 +1509,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -54310,35 +54258,35 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>48</v>
+        <v>16350</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2">
+        <v>384</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>40.875</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E4">
         <f>SUM(E2:E2)</f>
-        <v>0</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="G4">
         <f>SUM(G2:G2)</f>
-        <v>0</v>
+        <v>40.875</v>
       </c>
     </row>
   </sheetData>
@@ -54440,18 +54388,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="I1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="36">
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="32">
         <v>51</v>
       </c>
     </row>
@@ -54492,7 +54440,7 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="36"/>
+      <c r="M2" s="32"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -54695,220 +54643,226 @@
       <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="34">
         <v>1326018</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="34">
         <v>10011503</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="36">
         <v>277800</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="36">
         <v>65900</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="36">
         <v>211900</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="37">
         <v>278800</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="38">
         <v>88700</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="39">
         <v>405</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="40" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
+      <c r="A12" s="41"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="49" t="s">
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="34">
         <v>1326015</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="34">
         <v>10011558</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="36">
         <v>273700</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="36">
         <v>65900</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="36">
         <v>207800</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="37">
         <v>274100</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="14">
+      <c r="J13" s="38">
+        <v>66250</v>
+      </c>
+      <c r="K13" s="39">
         <v>602</v>
       </c>
-      <c r="L13" s="31"/>
+      <c r="L13" s="40" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="19" t="s">
+      <c r="A14" s="41"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="29"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="34">
         <v>1490615</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="34">
         <v>10011503</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="36">
         <v>193200</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="36">
         <v>66800</v>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="36">
         <v>126400</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="37">
         <v>192800</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="38">
         <v>65750</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="39">
         <v>405</v>
       </c>
-      <c r="L15" s="44" t="s">
+      <c r="L15" s="40" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="47" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="49" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="34">
         <v>1437341</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="34">
         <v>10011660</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="36">
         <v>284000</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="36">
         <v>68200</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="36">
         <v>215800</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="37">
         <v>285850</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="38">
         <v>67850</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="39">
         <v>149</v>
       </c>
-      <c r="L17" s="44" t="s">
+      <c r="L17" s="40" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47" t="s">
+      <c r="A18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="49" t="s">
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="45" t="s">
         <v>364</v>
       </c>
     </row>

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF58F5C6-493F-4C70-951E-6EA5D2ED01D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C64A0FA-68F2-485D-8F08-D4145BA9332F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consumption" sheetId="25" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4552" uniqueCount="435">
   <si>
     <t>Date</t>
   </si>
@@ -1133,6 +1133,216 @@
   <si>
     <t>Empty 10/6</t>
   </si>
+  <si>
+    <t>032864/1</t>
+  </si>
+  <si>
+    <t>032864/2</t>
+  </si>
+  <si>
+    <t>032864/3</t>
+  </si>
+  <si>
+    <t>032864/4</t>
+  </si>
+  <si>
+    <t>032865/1</t>
+  </si>
+  <si>
+    <t>032865/2</t>
+  </si>
+  <si>
+    <t>032865/3</t>
+  </si>
+  <si>
+    <t>032865/4</t>
+  </si>
+  <si>
+    <t>032866/1</t>
+  </si>
+  <si>
+    <t>032866/2</t>
+  </si>
+  <si>
+    <t>032866/3</t>
+  </si>
+  <si>
+    <t>032866/4</t>
+  </si>
+  <si>
+    <t>032863/3</t>
+  </si>
+  <si>
+    <t>032870/1</t>
+  </si>
+  <si>
+    <t>032870/2</t>
+  </si>
+  <si>
+    <t>032871/3</t>
+  </si>
+  <si>
+    <t>032872/1</t>
+  </si>
+  <si>
+    <t>032872/2</t>
+  </si>
+  <si>
+    <t>032872/3</t>
+  </si>
+  <si>
+    <t>032874/1</t>
+  </si>
+  <si>
+    <t>032874/2</t>
+  </si>
+  <si>
+    <t>032874/3</t>
+  </si>
+  <si>
+    <t>032874/4</t>
+  </si>
+  <si>
+    <t>032875/1</t>
+  </si>
+  <si>
+    <t>032875/2</t>
+  </si>
+  <si>
+    <t>032875/3</t>
+  </si>
+  <si>
+    <t>032876/2</t>
+  </si>
+  <si>
+    <t>H146266</t>
+  </si>
+  <si>
+    <t>H146267</t>
+  </si>
+  <si>
+    <t>H146268</t>
+  </si>
+  <si>
+    <t>H146269</t>
+  </si>
+  <si>
+    <t>H146270</t>
+  </si>
+  <si>
+    <t>H146271</t>
+  </si>
+  <si>
+    <t>H146272</t>
+  </si>
+  <si>
+    <t>H146273</t>
+  </si>
+  <si>
+    <t>H146274</t>
+  </si>
+  <si>
+    <t>H146275</t>
+  </si>
+  <si>
+    <t>H146276</t>
+  </si>
+  <si>
+    <t>H146277</t>
+  </si>
+  <si>
+    <t>H146278</t>
+  </si>
+  <si>
+    <t>H146279</t>
+  </si>
+  <si>
+    <t>H146280</t>
+  </si>
+  <si>
+    <t>200lb deduction for dirt in load</t>
+  </si>
+  <si>
+    <t>Large amount of wood and mud in bottom of railcar</t>
+  </si>
+  <si>
+    <t>H146281</t>
+  </si>
+  <si>
+    <t>H146282</t>
+  </si>
+  <si>
+    <t>H146283</t>
+  </si>
+  <si>
+    <t>H146284</t>
+  </si>
+  <si>
+    <t>H146285</t>
+  </si>
+  <si>
+    <t>H146286</t>
+  </si>
+  <si>
+    <t>H146287</t>
+  </si>
+  <si>
+    <t>H146289</t>
+  </si>
+  <si>
+    <t>H146288</t>
+  </si>
+  <si>
+    <t>H146290</t>
+  </si>
+  <si>
+    <t>H146291</t>
+  </si>
+  <si>
+    <t>H146292</t>
+  </si>
+  <si>
+    <t>H146293</t>
+  </si>
+  <si>
+    <t>H146294</t>
+  </si>
+  <si>
+    <t>H146295</t>
+  </si>
+  <si>
+    <t>H146296</t>
+  </si>
+  <si>
+    <t>H146297</t>
+  </si>
+  <si>
+    <t>H146299</t>
+  </si>
+  <si>
+    <t>H146300</t>
+  </si>
+  <si>
+    <t>H146298</t>
+  </si>
+  <si>
+    <t>H146301</t>
+  </si>
+  <si>
+    <t>H146302</t>
+  </si>
+  <si>
+    <t>H146303</t>
+  </si>
+  <si>
+    <t>H146305</t>
+  </si>
+  <si>
+    <t>H146304</t>
+  </si>
+  <si>
+    <t>H146306</t>
+  </si>
 </sst>
 </file>
 
@@ -1509,21 +1719,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1555,6 +1750,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1894,7 +2104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77917A13-DEA9-4460-B065-B9D18D61784D}">
-  <dimension ref="A1:L1169"/>
+  <dimension ref="A1:L1324"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -46317,6 +46527,5896 @@
       </c>
       <c r="L1169" s="7">
         <v>0.98030092592592588</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1170" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1170">
+        <v>439111</v>
+      </c>
+      <c r="C1170">
+        <v>1</v>
+      </c>
+      <c r="D1170">
+        <v>23</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1170">
+        <v>149</v>
+      </c>
+      <c r="H1170">
+        <v>10011660</v>
+      </c>
+      <c r="I1170">
+        <v>25000</v>
+      </c>
+      <c r="J1170">
+        <v>4800</v>
+      </c>
+      <c r="K1170" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1170" s="7">
+        <v>0.3730324074074074</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1171" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1171">
+        <v>439112</v>
+      </c>
+      <c r="C1171">
+        <v>1</v>
+      </c>
+      <c r="D1171">
+        <v>15</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1171">
+        <v>286</v>
+      </c>
+      <c r="H1171">
+        <v>10011414</v>
+      </c>
+      <c r="I1171">
+        <v>19900</v>
+      </c>
+      <c r="J1171">
+        <v>19900</v>
+      </c>
+      <c r="K1171" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1171" s="7">
+        <v>8.3993055555555557E-2</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1172" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1172">
+        <v>439112</v>
+      </c>
+      <c r="C1172">
+        <v>1</v>
+      </c>
+      <c r="D1172">
+        <v>15</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1172" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1172">
+        <v>10011512</v>
+      </c>
+      <c r="I1172">
+        <v>8000</v>
+      </c>
+      <c r="J1172">
+        <v>7990</v>
+      </c>
+      <c r="K1172" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1172" s="7">
+        <v>3.6006944444444446E-2</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1173" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1173">
+        <v>439112</v>
+      </c>
+      <c r="C1173">
+        <v>1</v>
+      </c>
+      <c r="D1173">
+        <v>15</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1173">
+        <v>602</v>
+      </c>
+      <c r="H1173">
+        <v>10011558</v>
+      </c>
+      <c r="I1173">
+        <v>10000</v>
+      </c>
+      <c r="J1173">
+        <v>9950</v>
+      </c>
+      <c r="K1173" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1173" s="7">
+        <v>8.0127314814814818E-2</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1174" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1174">
+        <v>439112</v>
+      </c>
+      <c r="C1174">
+        <v>1</v>
+      </c>
+      <c r="D1174">
+        <v>15</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1174">
+        <v>448</v>
+      </c>
+      <c r="H1174">
+        <v>10012170</v>
+      </c>
+      <c r="I1174">
+        <v>27100</v>
+      </c>
+      <c r="J1174">
+        <v>27120</v>
+      </c>
+      <c r="K1174" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1174" s="7">
+        <v>1.4641203703703703E-2</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1175" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1175">
+        <v>439112</v>
+      </c>
+      <c r="C1175">
+        <v>1</v>
+      </c>
+      <c r="D1175">
+        <v>15</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1175">
+        <v>448</v>
+      </c>
+      <c r="H1175">
+        <v>10012170</v>
+      </c>
+      <c r="I1175">
+        <v>27100</v>
+      </c>
+      <c r="J1175">
+        <v>27130</v>
+      </c>
+      <c r="K1175" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1175" s="7">
+        <v>1.4733796296296297E-2</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1176" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1176">
+        <v>439112</v>
+      </c>
+      <c r="C1176">
+        <v>1</v>
+      </c>
+      <c r="D1176">
+        <v>15</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1176">
+        <v>525</v>
+      </c>
+      <c r="H1176">
+        <v>10012284</v>
+      </c>
+      <c r="I1176">
+        <v>1300</v>
+      </c>
+      <c r="J1176">
+        <v>1420</v>
+      </c>
+      <c r="K1176" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1176" s="7">
+        <v>3.650462962962963E-2</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1177" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1177">
+        <v>439116</v>
+      </c>
+      <c r="C1177">
+        <v>1</v>
+      </c>
+      <c r="D1177">
+        <v>13</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1177">
+        <v>281</v>
+      </c>
+      <c r="H1177">
+        <v>10011414</v>
+      </c>
+      <c r="I1177">
+        <v>50000</v>
+      </c>
+      <c r="J1177">
+        <v>49950</v>
+      </c>
+      <c r="K1177" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1177" s="7">
+        <v>1.1817129629629629E-2</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1178" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1178">
+        <v>439116</v>
+      </c>
+      <c r="C1178">
+        <v>1</v>
+      </c>
+      <c r="D1178">
+        <v>13</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1178">
+        <v>504</v>
+      </c>
+      <c r="H1178">
+        <v>10011509</v>
+      </c>
+      <c r="I1178">
+        <v>5000</v>
+      </c>
+      <c r="J1178">
+        <v>5500</v>
+      </c>
+      <c r="K1178" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1178" s="7">
+        <v>3.7152777777777778E-3</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1179" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1179">
+        <v>439116</v>
+      </c>
+      <c r="C1179">
+        <v>1</v>
+      </c>
+      <c r="D1179">
+        <v>13</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1179">
+        <v>149</v>
+      </c>
+      <c r="H1179">
+        <v>10011660</v>
+      </c>
+      <c r="I1179">
+        <v>19400</v>
+      </c>
+      <c r="J1179">
+        <v>19350</v>
+      </c>
+      <c r="K1179" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1179" s="7">
+        <v>7.5578703703703702E-3</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1180" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1180">
+        <v>439116</v>
+      </c>
+      <c r="C1180">
+        <v>1</v>
+      </c>
+      <c r="D1180">
+        <v>13</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1180">
+        <v>362</v>
+      </c>
+      <c r="H1180">
+        <v>10011667</v>
+      </c>
+      <c r="I1180">
+        <v>15000</v>
+      </c>
+      <c r="J1180">
+        <v>15600</v>
+      </c>
+      <c r="K1180" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1180" s="7">
+        <v>5.0231481481481481E-3</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1181" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1181">
+        <v>439117</v>
+      </c>
+      <c r="C1181">
+        <v>1</v>
+      </c>
+      <c r="D1181">
+        <v>18</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1181">
+        <v>281</v>
+      </c>
+      <c r="H1181">
+        <v>10011414</v>
+      </c>
+      <c r="I1181">
+        <v>19500</v>
+      </c>
+      <c r="J1181">
+        <v>19600</v>
+      </c>
+      <c r="K1181" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1181" s="7">
+        <v>9.7847222222222224E-2</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1182" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1182">
+        <v>439117</v>
+      </c>
+      <c r="C1182">
+        <v>1</v>
+      </c>
+      <c r="D1182">
+        <v>18</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1182">
+        <v>504</v>
+      </c>
+      <c r="H1182">
+        <v>10011509</v>
+      </c>
+      <c r="I1182">
+        <v>19500</v>
+      </c>
+      <c r="J1182">
+        <v>19450</v>
+      </c>
+      <c r="K1182" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1182" s="7">
+        <v>3.3506944444444443E-2</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1183" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1183">
+        <v>439117</v>
+      </c>
+      <c r="C1183">
+        <v>1</v>
+      </c>
+      <c r="D1183">
+        <v>18</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1183">
+        <v>448</v>
+      </c>
+      <c r="H1183">
+        <v>10012170</v>
+      </c>
+      <c r="I1183">
+        <v>27100</v>
+      </c>
+      <c r="J1183">
+        <v>27340</v>
+      </c>
+      <c r="K1183" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1183" s="7">
+        <v>8.3634259259259255E-2</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1184" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1184">
+        <v>439117</v>
+      </c>
+      <c r="C1184">
+        <v>1</v>
+      </c>
+      <c r="D1184">
+        <v>18</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1184">
+        <v>984</v>
+      </c>
+      <c r="H1184">
+        <v>10031006</v>
+      </c>
+      <c r="I1184">
+        <v>6350</v>
+      </c>
+      <c r="J1184">
+        <v>6340</v>
+      </c>
+      <c r="K1184" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1184" s="7">
+        <v>8.3460648148148145E-2</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1185" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1185">
+        <v>439117</v>
+      </c>
+      <c r="C1185">
+        <v>1</v>
+      </c>
+      <c r="D1185">
+        <v>18</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1185">
+        <v>864</v>
+      </c>
+      <c r="H1185">
+        <v>10031008</v>
+      </c>
+      <c r="I1185">
+        <v>5000</v>
+      </c>
+      <c r="J1185">
+        <v>4930</v>
+      </c>
+      <c r="K1185" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1185" s="7">
+        <v>8.3414351851851851E-2</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1186" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1186">
+        <v>439118</v>
+      </c>
+      <c r="C1186">
+        <v>1</v>
+      </c>
+      <c r="D1186">
+        <v>14</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1186">
+        <v>281</v>
+      </c>
+      <c r="H1186">
+        <v>10011414</v>
+      </c>
+      <c r="I1186">
+        <v>19400</v>
+      </c>
+      <c r="J1186">
+        <v>19450</v>
+      </c>
+      <c r="K1186" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1186" s="7">
+        <v>7.1886574074074075E-2</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1187" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1187">
+        <v>439118</v>
+      </c>
+      <c r="C1187">
+        <v>1</v>
+      </c>
+      <c r="D1187">
+        <v>14</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1187">
+        <v>10011512</v>
+      </c>
+      <c r="I1187">
+        <v>8000</v>
+      </c>
+      <c r="J1187">
+        <v>8000</v>
+      </c>
+      <c r="K1187" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1187" s="7">
+        <v>6.8692129629629631E-2</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1188" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1188">
+        <v>439118</v>
+      </c>
+      <c r="C1188">
+        <v>1</v>
+      </c>
+      <c r="D1188">
+        <v>14</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1188">
+        <v>602</v>
+      </c>
+      <c r="H1188">
+        <v>10011558</v>
+      </c>
+      <c r="I1188">
+        <v>10000</v>
+      </c>
+      <c r="J1188">
+        <v>9950</v>
+      </c>
+      <c r="K1188" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1188" s="7">
+        <v>3.1516203703703706E-2</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1189" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1189">
+        <v>439118</v>
+      </c>
+      <c r="C1189">
+        <v>1</v>
+      </c>
+      <c r="D1189">
+        <v>14</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1189">
+        <v>947</v>
+      </c>
+      <c r="H1189">
+        <v>10011657</v>
+      </c>
+      <c r="I1189">
+        <v>10000</v>
+      </c>
+      <c r="J1189">
+        <v>10200</v>
+      </c>
+      <c r="K1189" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1189" s="7">
+        <v>3.2696759259259259E-2</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1190" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1190">
+        <v>439118</v>
+      </c>
+      <c r="C1190">
+        <v>1</v>
+      </c>
+      <c r="D1190">
+        <v>14</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1190">
+        <v>448</v>
+      </c>
+      <c r="H1190">
+        <v>10012170</v>
+      </c>
+      <c r="I1190">
+        <v>27100</v>
+      </c>
+      <c r="J1190">
+        <v>27050</v>
+      </c>
+      <c r="K1190" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1190" s="7">
+        <v>6.2557870370370375E-2</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1191" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1191">
+        <v>439118</v>
+      </c>
+      <c r="C1191">
+        <v>1</v>
+      </c>
+      <c r="D1191">
+        <v>14</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1191">
+        <v>525</v>
+      </c>
+      <c r="H1191">
+        <v>10012284</v>
+      </c>
+      <c r="I1191">
+        <v>2500</v>
+      </c>
+      <c r="J1191">
+        <v>2400</v>
+      </c>
+      <c r="K1191" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1191" s="7">
+        <v>5.7118055555555554E-2</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1192" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1192">
+        <v>439118</v>
+      </c>
+      <c r="C1192">
+        <v>1</v>
+      </c>
+      <c r="D1192">
+        <v>14</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1192">
+        <v>984</v>
+      </c>
+      <c r="H1192">
+        <v>10031006</v>
+      </c>
+      <c r="I1192">
+        <v>6350</v>
+      </c>
+      <c r="J1192">
+        <v>6250</v>
+      </c>
+      <c r="K1192" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1192" s="7">
+        <v>5.4050925925925926E-2</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1193" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1193">
+        <v>439119</v>
+      </c>
+      <c r="C1193">
+        <v>1</v>
+      </c>
+      <c r="D1193">
+        <v>16</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1193">
+        <v>148</v>
+      </c>
+      <c r="H1193">
+        <v>10011660</v>
+      </c>
+      <c r="I1193">
+        <v>30000</v>
+      </c>
+      <c r="J1193">
+        <v>29950</v>
+      </c>
+      <c r="K1193" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1193" s="7">
+        <v>5.392361111111111E-2</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1194" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1194">
+        <v>439116</v>
+      </c>
+      <c r="C1194">
+        <v>1</v>
+      </c>
+      <c r="D1194">
+        <v>12</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1194">
+        <v>281</v>
+      </c>
+      <c r="H1194">
+        <v>10011414</v>
+      </c>
+      <c r="I1194">
+        <v>50000</v>
+      </c>
+      <c r="J1194">
+        <v>50050</v>
+      </c>
+      <c r="K1194" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1194" s="7">
+        <v>0.11480324074074075</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1195" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1195">
+        <v>439116</v>
+      </c>
+      <c r="C1195">
+        <v>1</v>
+      </c>
+      <c r="D1195">
+        <v>12</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1195">
+        <v>504</v>
+      </c>
+      <c r="H1195">
+        <v>10011509</v>
+      </c>
+      <c r="I1195">
+        <v>5000</v>
+      </c>
+      <c r="J1195">
+        <v>5100</v>
+      </c>
+      <c r="K1195" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1195" s="7">
+        <v>0.10622685185185185</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1196" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1196">
+        <v>439116</v>
+      </c>
+      <c r="C1196">
+        <v>1</v>
+      </c>
+      <c r="D1196">
+        <v>12</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1196">
+        <v>149</v>
+      </c>
+      <c r="H1196">
+        <v>10011660</v>
+      </c>
+      <c r="I1196">
+        <v>20000</v>
+      </c>
+      <c r="J1196">
+        <v>19900</v>
+      </c>
+      <c r="K1196" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1196" s="7">
+        <v>0.11085648148148149</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1197" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1197">
+        <v>439116</v>
+      </c>
+      <c r="C1197">
+        <v>1</v>
+      </c>
+      <c r="D1197">
+        <v>12</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1197">
+        <v>362</v>
+      </c>
+      <c r="H1197">
+        <v>10011667</v>
+      </c>
+      <c r="I1197">
+        <v>15000</v>
+      </c>
+      <c r="J1197">
+        <v>15150</v>
+      </c>
+      <c r="K1197" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1197" s="7">
+        <v>0.10748842592592593</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1198" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1198">
+        <v>439117</v>
+      </c>
+      <c r="C1198">
+        <v>1</v>
+      </c>
+      <c r="D1198">
+        <v>19</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1198">
+        <v>281</v>
+      </c>
+      <c r="H1198">
+        <v>10011414</v>
+      </c>
+      <c r="I1198">
+        <v>19500</v>
+      </c>
+      <c r="J1198">
+        <v>19650</v>
+      </c>
+      <c r="K1198" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1198" s="7">
+        <v>0.13218750000000001</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1199" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1199">
+        <v>439117</v>
+      </c>
+      <c r="C1199">
+        <v>1</v>
+      </c>
+      <c r="D1199">
+        <v>19</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1199">
+        <v>505</v>
+      </c>
+      <c r="H1199">
+        <v>10011509</v>
+      </c>
+      <c r="I1199">
+        <v>20000</v>
+      </c>
+      <c r="J1199">
+        <v>20000</v>
+      </c>
+      <c r="K1199" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1199" s="7">
+        <v>9.357638888888889E-2</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1200" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1200">
+        <v>439117</v>
+      </c>
+      <c r="C1200">
+        <v>1</v>
+      </c>
+      <c r="D1200">
+        <v>19</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1200">
+        <v>448</v>
+      </c>
+      <c r="H1200">
+        <v>10012170</v>
+      </c>
+      <c r="I1200">
+        <v>27100</v>
+      </c>
+      <c r="J1200">
+        <v>26950</v>
+      </c>
+      <c r="K1200" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1200" s="7">
+        <v>0.13024305555555554</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1201" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1201">
+        <v>439117</v>
+      </c>
+      <c r="C1201">
+        <v>1</v>
+      </c>
+      <c r="D1201">
+        <v>19</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1201">
+        <v>984</v>
+      </c>
+      <c r="H1201">
+        <v>10031006</v>
+      </c>
+      <c r="I1201">
+        <v>6350</v>
+      </c>
+      <c r="J1201">
+        <v>6250</v>
+      </c>
+      <c r="K1201" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1201" s="7">
+        <v>0.12474537037037037</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1202" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1202">
+        <v>439117</v>
+      </c>
+      <c r="C1202">
+        <v>1</v>
+      </c>
+      <c r="D1202">
+        <v>19</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1202">
+        <v>864</v>
+      </c>
+      <c r="H1202">
+        <v>10031008</v>
+      </c>
+      <c r="I1202">
+        <v>5000</v>
+      </c>
+      <c r="J1202">
+        <v>4930</v>
+      </c>
+      <c r="K1202" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1202" s="7">
+        <v>0.11614583333333334</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1203" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1203">
+        <v>439118</v>
+      </c>
+      <c r="C1203">
+        <v>1</v>
+      </c>
+      <c r="D1203">
+        <v>13</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1203">
+        <v>285</v>
+      </c>
+      <c r="H1203">
+        <v>10011414</v>
+      </c>
+      <c r="I1203">
+        <v>19400</v>
+      </c>
+      <c r="J1203">
+        <v>19400</v>
+      </c>
+      <c r="K1203" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1203" s="7">
+        <v>0.37531249999999999</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1204" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1204">
+        <v>439118</v>
+      </c>
+      <c r="C1204">
+        <v>1</v>
+      </c>
+      <c r="D1204">
+        <v>13</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1204">
+        <v>10011512</v>
+      </c>
+      <c r="I1204">
+        <v>8000</v>
+      </c>
+      <c r="J1204">
+        <v>7970</v>
+      </c>
+      <c r="K1204" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1204" s="7">
+        <v>0.34649305555555554</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1205" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1205">
+        <v>439118</v>
+      </c>
+      <c r="C1205">
+        <v>1</v>
+      </c>
+      <c r="D1205">
+        <v>13</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1205">
+        <v>602</v>
+      </c>
+      <c r="H1205">
+        <v>10011558</v>
+      </c>
+      <c r="I1205">
+        <v>10000</v>
+      </c>
+      <c r="J1205">
+        <v>10050</v>
+      </c>
+      <c r="K1205" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1205" s="7">
+        <v>0.24886574074074075</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1206" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1206">
+        <v>439118</v>
+      </c>
+      <c r="C1206">
+        <v>1</v>
+      </c>
+      <c r="D1206">
+        <v>13</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1206">
+        <v>947</v>
+      </c>
+      <c r="H1206">
+        <v>10011657</v>
+      </c>
+      <c r="I1206">
+        <v>10000</v>
+      </c>
+      <c r="J1206">
+        <v>10100</v>
+      </c>
+      <c r="K1206" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1206" s="7">
+        <v>0.25048611111111113</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1207" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1207">
+        <v>439118</v>
+      </c>
+      <c r="C1207">
+        <v>1</v>
+      </c>
+      <c r="D1207">
+        <v>13</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1207">
+        <v>448</v>
+      </c>
+      <c r="H1207">
+        <v>10012170</v>
+      </c>
+      <c r="I1207">
+        <v>27100</v>
+      </c>
+      <c r="J1207">
+        <v>27100</v>
+      </c>
+      <c r="K1207" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1207" s="7">
+        <v>0.34636574074074072</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1208" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1208">
+        <v>439118</v>
+      </c>
+      <c r="C1208">
+        <v>1</v>
+      </c>
+      <c r="D1208">
+        <v>13</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1208">
+        <v>525</v>
+      </c>
+      <c r="H1208">
+        <v>10012284</v>
+      </c>
+      <c r="I1208">
+        <v>2500</v>
+      </c>
+      <c r="J1208">
+        <v>2480</v>
+      </c>
+      <c r="K1208" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1208" s="7">
+        <v>0.2648726851851852</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1209" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1209">
+        <v>439118</v>
+      </c>
+      <c r="C1209">
+        <v>1</v>
+      </c>
+      <c r="D1209">
+        <v>13</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1209">
+        <v>984</v>
+      </c>
+      <c r="H1209">
+        <v>10031006</v>
+      </c>
+      <c r="I1209">
+        <v>6350</v>
+      </c>
+      <c r="J1209">
+        <v>6360</v>
+      </c>
+      <c r="K1209" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1209" s="7">
+        <v>0.26472222222222225</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1210" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1210">
+        <v>439119</v>
+      </c>
+      <c r="C1210">
+        <v>1</v>
+      </c>
+      <c r="D1210">
+        <v>18</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1210">
+        <v>149</v>
+      </c>
+      <c r="H1210">
+        <v>10011660</v>
+      </c>
+      <c r="I1210">
+        <v>30000</v>
+      </c>
+      <c r="J1210">
+        <v>29950</v>
+      </c>
+      <c r="K1210" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1210" s="7">
+        <v>0.25317129629629631</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1211" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1211">
+        <v>439116</v>
+      </c>
+      <c r="C1211">
+        <v>1</v>
+      </c>
+      <c r="D1211">
+        <v>14</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1211">
+        <v>281</v>
+      </c>
+      <c r="H1211">
+        <v>10011414</v>
+      </c>
+      <c r="I1211">
+        <v>50000</v>
+      </c>
+      <c r="J1211">
+        <v>50000</v>
+      </c>
+      <c r="K1211" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1211" s="7">
+        <v>0.35726851851851854</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1212" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1212">
+        <v>439116</v>
+      </c>
+      <c r="C1212">
+        <v>1</v>
+      </c>
+      <c r="D1212">
+        <v>14</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1212">
+        <v>504</v>
+      </c>
+      <c r="H1212">
+        <v>10011509</v>
+      </c>
+      <c r="I1212">
+        <v>5000</v>
+      </c>
+      <c r="J1212">
+        <v>4950</v>
+      </c>
+      <c r="K1212" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1212" s="7">
+        <v>0.33201388888888889</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1213" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1213">
+        <v>439116</v>
+      </c>
+      <c r="C1213">
+        <v>1</v>
+      </c>
+      <c r="D1213">
+        <v>14</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1213">
+        <v>149</v>
+      </c>
+      <c r="H1213">
+        <v>10011660</v>
+      </c>
+      <c r="I1213">
+        <v>19750</v>
+      </c>
+      <c r="J1213">
+        <v>19800</v>
+      </c>
+      <c r="K1213" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1213" s="7">
+        <v>0.34494212962962961</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1214" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1214">
+        <v>439116</v>
+      </c>
+      <c r="C1214">
+        <v>1</v>
+      </c>
+      <c r="D1214">
+        <v>14</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1214">
+        <v>362</v>
+      </c>
+      <c r="H1214">
+        <v>10011667</v>
+      </c>
+      <c r="I1214">
+        <v>15000</v>
+      </c>
+      <c r="J1214">
+        <v>15250</v>
+      </c>
+      <c r="K1214" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1214" s="7">
+        <v>0.33618055555555554</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1215" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1215">
+        <v>439117</v>
+      </c>
+      <c r="C1215">
+        <v>1</v>
+      </c>
+      <c r="D1215">
+        <v>16</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1215">
+        <v>286</v>
+      </c>
+      <c r="H1215">
+        <v>10011414</v>
+      </c>
+      <c r="I1215">
+        <v>19500</v>
+      </c>
+      <c r="J1215">
+        <v>19400</v>
+      </c>
+      <c r="K1215" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1215" s="7">
+        <v>0.39674768518518516</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1216" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1216">
+        <v>439117</v>
+      </c>
+      <c r="C1216">
+        <v>1</v>
+      </c>
+      <c r="D1216">
+        <v>16</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1216">
+        <v>505</v>
+      </c>
+      <c r="H1216">
+        <v>10011509</v>
+      </c>
+      <c r="I1216">
+        <v>20000</v>
+      </c>
+      <c r="J1216">
+        <v>20000</v>
+      </c>
+      <c r="K1216" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1216" s="7">
+        <v>0.35886574074074074</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1217" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1217">
+        <v>439117</v>
+      </c>
+      <c r="C1217">
+        <v>1</v>
+      </c>
+      <c r="D1217">
+        <v>16</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1217">
+        <v>448</v>
+      </c>
+      <c r="H1217">
+        <v>10012170</v>
+      </c>
+      <c r="I1217">
+        <v>27100</v>
+      </c>
+      <c r="J1217">
+        <v>27120</v>
+      </c>
+      <c r="K1217" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1217" s="7">
+        <v>0.38207175925925924</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1218" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1218">
+        <v>439117</v>
+      </c>
+      <c r="C1218">
+        <v>1</v>
+      </c>
+      <c r="D1218">
+        <v>16</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1218">
+        <v>984</v>
+      </c>
+      <c r="H1218">
+        <v>10031006</v>
+      </c>
+      <c r="I1218">
+        <v>6350</v>
+      </c>
+      <c r="J1218">
+        <v>6340</v>
+      </c>
+      <c r="K1218" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1218" s="7">
+        <v>0.38200231481481484</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1219" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1219">
+        <v>439117</v>
+      </c>
+      <c r="C1219">
+        <v>1</v>
+      </c>
+      <c r="D1219">
+        <v>16</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1219">
+        <v>864</v>
+      </c>
+      <c r="H1219">
+        <v>10031008</v>
+      </c>
+      <c r="I1219">
+        <v>5000</v>
+      </c>
+      <c r="J1219">
+        <v>4900</v>
+      </c>
+      <c r="K1219" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1219" s="7">
+        <v>0.38179398148148147</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1220" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1220">
+        <v>439118</v>
+      </c>
+      <c r="C1220">
+        <v>1</v>
+      </c>
+      <c r="D1220">
+        <v>19</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1220">
+        <v>286</v>
+      </c>
+      <c r="H1220">
+        <v>10011414</v>
+      </c>
+      <c r="I1220">
+        <v>19400</v>
+      </c>
+      <c r="J1220">
+        <v>19350</v>
+      </c>
+      <c r="K1220" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1220" s="7">
+        <v>0.60376157407407405</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1221" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1221">
+        <v>439118</v>
+      </c>
+      <c r="C1221">
+        <v>1</v>
+      </c>
+      <c r="D1221">
+        <v>19</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1221">
+        <v>10011512</v>
+      </c>
+      <c r="I1221">
+        <v>8000</v>
+      </c>
+      <c r="J1221">
+        <v>8030</v>
+      </c>
+      <c r="K1221" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1221" s="7">
+        <v>0.59616898148148145</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1222" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1222">
+        <v>439118</v>
+      </c>
+      <c r="C1222">
+        <v>1</v>
+      </c>
+      <c r="D1222">
+        <v>19</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1222">
+        <v>602</v>
+      </c>
+      <c r="H1222">
+        <v>10011558</v>
+      </c>
+      <c r="I1222">
+        <v>10000</v>
+      </c>
+      <c r="J1222">
+        <v>10150</v>
+      </c>
+      <c r="K1222" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1222" s="7">
+        <v>0.53913194444444446</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1223" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1223">
+        <v>439118</v>
+      </c>
+      <c r="C1223">
+        <v>1</v>
+      </c>
+      <c r="D1223">
+        <v>19</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1223">
+        <v>947</v>
+      </c>
+      <c r="H1223">
+        <v>10011657</v>
+      </c>
+      <c r="I1223">
+        <v>10000</v>
+      </c>
+      <c r="J1223">
+        <v>10200</v>
+      </c>
+      <c r="K1223" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1223" s="7">
+        <v>0.54546296296296293</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1224" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1224">
+        <v>439118</v>
+      </c>
+      <c r="C1224">
+        <v>1</v>
+      </c>
+      <c r="D1224">
+        <v>19</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1224">
+        <v>448</v>
+      </c>
+      <c r="H1224">
+        <v>10012170</v>
+      </c>
+      <c r="I1224">
+        <v>27100</v>
+      </c>
+      <c r="J1224">
+        <v>27090</v>
+      </c>
+      <c r="K1224" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1224" s="7">
+        <v>0.59612268518518519</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1225" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1225">
+        <v>439118</v>
+      </c>
+      <c r="C1225">
+        <v>1</v>
+      </c>
+      <c r="D1225">
+        <v>19</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1225">
+        <v>525</v>
+      </c>
+      <c r="H1225">
+        <v>10012284</v>
+      </c>
+      <c r="I1225">
+        <v>2500</v>
+      </c>
+      <c r="J1225">
+        <v>2550</v>
+      </c>
+      <c r="K1225" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1225" s="7">
+        <v>0.58128472222222227</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1226" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1226">
+        <v>439118</v>
+      </c>
+      <c r="C1226">
+        <v>1</v>
+      </c>
+      <c r="D1226">
+        <v>19</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1226">
+        <v>984</v>
+      </c>
+      <c r="H1226">
+        <v>10031006</v>
+      </c>
+      <c r="I1226">
+        <v>6350</v>
+      </c>
+      <c r="J1226">
+        <v>6340</v>
+      </c>
+      <c r="K1226" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1226" s="7">
+        <v>0.5534606481481481</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1227" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1227">
+        <v>439119</v>
+      </c>
+      <c r="C1227">
+        <v>1</v>
+      </c>
+      <c r="D1227">
+        <v>13</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1227">
+        <v>149</v>
+      </c>
+      <c r="H1227">
+        <v>10011660</v>
+      </c>
+      <c r="I1227">
+        <v>30000</v>
+      </c>
+      <c r="J1227">
+        <v>30050</v>
+      </c>
+      <c r="K1227" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1227" s="7">
+        <v>0.57839120370370367</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1228" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1228">
+        <v>439115</v>
+      </c>
+      <c r="C1228">
+        <v>1</v>
+      </c>
+      <c r="D1228">
+        <v>4</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1228">
+        <v>149</v>
+      </c>
+      <c r="H1228">
+        <v>10011660</v>
+      </c>
+      <c r="I1228">
+        <v>20000</v>
+      </c>
+      <c r="J1228">
+        <v>20000</v>
+      </c>
+      <c r="K1228" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1228" s="7">
+        <v>0.37268518518518517</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1229" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1229">
+        <v>439111</v>
+      </c>
+      <c r="C1229">
+        <v>1</v>
+      </c>
+      <c r="D1229">
+        <v>24</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1229">
+        <v>281</v>
+      </c>
+      <c r="H1229">
+        <v>10011414</v>
+      </c>
+      <c r="I1229">
+        <v>17000</v>
+      </c>
+      <c r="J1229">
+        <v>17300</v>
+      </c>
+      <c r="K1229" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1229" s="7">
+        <v>0.40452546296296299</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1230" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1230">
+        <v>439111</v>
+      </c>
+      <c r="C1230">
+        <v>1</v>
+      </c>
+      <c r="D1230">
+        <v>24</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1230">
+        <v>281</v>
+      </c>
+      <c r="H1230">
+        <v>10011414</v>
+      </c>
+      <c r="I1230">
+        <v>9700</v>
+      </c>
+      <c r="J1230">
+        <v>9700</v>
+      </c>
+      <c r="K1230" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1230" s="7">
+        <v>0.4195949074074074</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1231" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1231">
+        <v>439111</v>
+      </c>
+      <c r="C1231">
+        <v>1</v>
+      </c>
+      <c r="D1231">
+        <v>24</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1231">
+        <v>95</v>
+      </c>
+      <c r="H1231">
+        <v>10011446</v>
+      </c>
+      <c r="I1231">
+        <v>7000</v>
+      </c>
+      <c r="J1231">
+        <v>7050</v>
+      </c>
+      <c r="K1231" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1231" s="7">
+        <v>0.39976851851851852</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1232" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1232">
+        <v>439111</v>
+      </c>
+      <c r="C1232">
+        <v>1</v>
+      </c>
+      <c r="D1232">
+        <v>24</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1232">
+        <v>95</v>
+      </c>
+      <c r="H1232">
+        <v>10011446</v>
+      </c>
+      <c r="I1232">
+        <v>7000</v>
+      </c>
+      <c r="J1232">
+        <v>7250</v>
+      </c>
+      <c r="K1232" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1232" s="7">
+        <v>0.41728009259259258</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1233" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1233">
+        <v>439111</v>
+      </c>
+      <c r="C1233">
+        <v>1</v>
+      </c>
+      <c r="D1233">
+        <v>24</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1233">
+        <v>95</v>
+      </c>
+      <c r="H1233">
+        <v>10011446</v>
+      </c>
+      <c r="I1233">
+        <v>6750</v>
+      </c>
+      <c r="J1233">
+        <v>6700</v>
+      </c>
+      <c r="K1233" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1233" s="7">
+        <v>0.42746527777777776</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1234" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1234">
+        <v>439111</v>
+      </c>
+      <c r="C1234">
+        <v>1</v>
+      </c>
+      <c r="D1234">
+        <v>24</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1234">
+        <v>95</v>
+      </c>
+      <c r="H1234">
+        <v>10011446</v>
+      </c>
+      <c r="I1234">
+        <v>7000</v>
+      </c>
+      <c r="J1234">
+        <v>7200</v>
+      </c>
+      <c r="K1234" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1234" s="7">
+        <v>0.43817129629629631</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1235" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1235">
+        <v>439111</v>
+      </c>
+      <c r="C1235">
+        <v>1</v>
+      </c>
+      <c r="D1235">
+        <v>24</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1235">
+        <v>504</v>
+      </c>
+      <c r="H1235">
+        <v>10011509</v>
+      </c>
+      <c r="I1235">
+        <v>5000</v>
+      </c>
+      <c r="J1235">
+        <v>6350</v>
+      </c>
+      <c r="K1235" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1235" s="7">
+        <v>0.39225694444444442</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1236" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1236">
+        <v>439111</v>
+      </c>
+      <c r="C1236">
+        <v>1</v>
+      </c>
+      <c r="D1236">
+        <v>24</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1236">
+        <v>504</v>
+      </c>
+      <c r="H1236">
+        <v>10011509</v>
+      </c>
+      <c r="I1236">
+        <v>18650</v>
+      </c>
+      <c r="J1236">
+        <v>18550</v>
+      </c>
+      <c r="K1236" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1236" s="7">
+        <v>0.41560185185185183</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1237" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1237">
+        <v>439111</v>
+      </c>
+      <c r="C1237">
+        <v>1</v>
+      </c>
+      <c r="D1237">
+        <v>24</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1237">
+        <v>149</v>
+      </c>
+      <c r="H1237">
+        <v>10011660</v>
+      </c>
+      <c r="I1237">
+        <v>10200</v>
+      </c>
+      <c r="J1237">
+        <v>10150</v>
+      </c>
+      <c r="K1237" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1237" s="7">
+        <v>0.42487268518518517</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1238" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1238">
+        <v>439111</v>
+      </c>
+      <c r="C1238">
+        <v>1</v>
+      </c>
+      <c r="D1238">
+        <v>24</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1238">
+        <v>149</v>
+      </c>
+      <c r="H1238">
+        <v>10011660</v>
+      </c>
+      <c r="I1238">
+        <v>15000</v>
+      </c>
+      <c r="J1238">
+        <v>15000</v>
+      </c>
+      <c r="K1238" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1238" s="7">
+        <v>0.43634259259259262</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1239" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1239">
+        <v>439111</v>
+      </c>
+      <c r="C1239">
+        <v>1</v>
+      </c>
+      <c r="D1239">
+        <v>24</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1239">
+        <v>362</v>
+      </c>
+      <c r="H1239">
+        <v>10011667</v>
+      </c>
+      <c r="I1239">
+        <v>10000</v>
+      </c>
+      <c r="J1239">
+        <v>10100</v>
+      </c>
+      <c r="K1239" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1239" s="7">
+        <v>0.39718750000000003</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1240" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1240">
+        <v>439111</v>
+      </c>
+      <c r="C1240">
+        <v>1</v>
+      </c>
+      <c r="D1240">
+        <v>24</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1240">
+        <v>384</v>
+      </c>
+      <c r="H1240">
+        <v>10011669</v>
+      </c>
+      <c r="I1240">
+        <v>5000</v>
+      </c>
+      <c r="J1240">
+        <v>4700</v>
+      </c>
+      <c r="K1240" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1240" s="7">
+        <v>0.40768518518518521</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1241" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1241">
+        <v>439112</v>
+      </c>
+      <c r="C1241">
+        <v>1</v>
+      </c>
+      <c r="D1241">
+        <v>12</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1241">
+        <v>286</v>
+      </c>
+      <c r="H1241">
+        <v>10011414</v>
+      </c>
+      <c r="I1241">
+        <v>19900</v>
+      </c>
+      <c r="J1241">
+        <v>19950</v>
+      </c>
+      <c r="K1241" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1241" s="7">
+        <v>0.5690277777777778</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1242" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1242">
+        <v>439112</v>
+      </c>
+      <c r="C1242">
+        <v>1</v>
+      </c>
+      <c r="D1242">
+        <v>12</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1242">
+        <v>98</v>
+      </c>
+      <c r="H1242">
+        <v>10011446</v>
+      </c>
+      <c r="I1242">
+        <v>7000</v>
+      </c>
+      <c r="J1242">
+        <v>7000</v>
+      </c>
+      <c r="K1242" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1242" s="7">
+        <v>0.46656249999999999</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1243" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1243">
+        <v>439112</v>
+      </c>
+      <c r="C1243">
+        <v>1</v>
+      </c>
+      <c r="D1243">
+        <v>12</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1243">
+        <v>98</v>
+      </c>
+      <c r="H1243">
+        <v>10011446</v>
+      </c>
+      <c r="I1243">
+        <v>7000</v>
+      </c>
+      <c r="J1243">
+        <v>6950</v>
+      </c>
+      <c r="K1243" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1243" s="7">
+        <v>0.46929398148148149</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1244" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1244">
+        <v>439112</v>
+      </c>
+      <c r="C1244">
+        <v>1</v>
+      </c>
+      <c r="D1244">
+        <v>12</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1244">
+        <v>10011512</v>
+      </c>
+      <c r="I1244">
+        <v>8000</v>
+      </c>
+      <c r="J1244">
+        <v>8050</v>
+      </c>
+      <c r="K1244" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1244" s="7">
+        <v>0.54295138888888894</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1245" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1245">
+        <v>439112</v>
+      </c>
+      <c r="C1245">
+        <v>1</v>
+      </c>
+      <c r="D1245">
+        <v>12</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1245">
+        <v>602</v>
+      </c>
+      <c r="H1245">
+        <v>10011558</v>
+      </c>
+      <c r="I1245">
+        <v>10000</v>
+      </c>
+      <c r="J1245">
+        <v>9950</v>
+      </c>
+      <c r="K1245" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1245" s="7">
+        <v>0.56283564814814813</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1246" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1246">
+        <v>439112</v>
+      </c>
+      <c r="C1246">
+        <v>1</v>
+      </c>
+      <c r="D1246">
+        <v>12</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1246">
+        <v>947</v>
+      </c>
+      <c r="H1246">
+        <v>10011657</v>
+      </c>
+      <c r="I1246">
+        <v>10000</v>
+      </c>
+      <c r="J1246">
+        <v>10150</v>
+      </c>
+      <c r="K1246" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1246" s="7">
+        <v>0.46840277777777778</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1247" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1247">
+        <v>439112</v>
+      </c>
+      <c r="C1247">
+        <v>1</v>
+      </c>
+      <c r="D1247">
+        <v>12</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1247">
+        <v>448</v>
+      </c>
+      <c r="H1247">
+        <v>10012170</v>
+      </c>
+      <c r="I1247">
+        <v>27100</v>
+      </c>
+      <c r="J1247">
+        <v>27100</v>
+      </c>
+      <c r="K1247" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1247" s="7">
+        <v>0.52018518518518519</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1248" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1248">
+        <v>439112</v>
+      </c>
+      <c r="C1248">
+        <v>1</v>
+      </c>
+      <c r="D1248">
+        <v>12</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1248">
+        <v>448</v>
+      </c>
+      <c r="H1248">
+        <v>10012170</v>
+      </c>
+      <c r="I1248">
+        <v>27100</v>
+      </c>
+      <c r="J1248">
+        <v>27100</v>
+      </c>
+      <c r="K1248" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1248" s="7">
+        <v>0.5202430555555555</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1249" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1249">
+        <v>439112</v>
+      </c>
+      <c r="C1249">
+        <v>1</v>
+      </c>
+      <c r="D1249">
+        <v>12</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1249">
+        <v>525</v>
+      </c>
+      <c r="H1249">
+        <v>10012284</v>
+      </c>
+      <c r="I1249">
+        <v>1300</v>
+      </c>
+      <c r="J1249">
+        <v>1310</v>
+      </c>
+      <c r="K1249" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1249" s="7">
+        <v>0.54659722222222218</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1250" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1250">
+        <v>439112</v>
+      </c>
+      <c r="C1250">
+        <v>1</v>
+      </c>
+      <c r="D1250">
+        <v>12</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1250">
+        <v>984</v>
+      </c>
+      <c r="H1250">
+        <v>10031006</v>
+      </c>
+      <c r="I1250">
+        <v>11200</v>
+      </c>
+      <c r="J1250">
+        <v>11220</v>
+      </c>
+      <c r="K1250" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1250" s="7">
+        <v>0.49813657407407408</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1251" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1251">
+        <v>439112</v>
+      </c>
+      <c r="C1251">
+        <v>1</v>
+      </c>
+      <c r="D1251">
+        <v>12</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1251">
+        <v>864</v>
+      </c>
+      <c r="H1251">
+        <v>10031008</v>
+      </c>
+      <c r="I1251">
+        <v>5000</v>
+      </c>
+      <c r="J1251">
+        <v>4960</v>
+      </c>
+      <c r="K1251" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1251" s="7">
+        <v>0.49809027777777776</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1252" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1252">
+        <v>439115</v>
+      </c>
+      <c r="C1252">
+        <v>1</v>
+      </c>
+      <c r="D1252">
+        <v>17</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1252">
+        <v>148</v>
+      </c>
+      <c r="H1252">
+        <v>10011660</v>
+      </c>
+      <c r="I1252">
+        <v>25000</v>
+      </c>
+      <c r="J1252">
+        <v>25000</v>
+      </c>
+      <c r="K1252" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1252" s="7">
+        <v>0.67577546296296298</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1253" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1253">
+        <v>436131</v>
+      </c>
+      <c r="C1253">
+        <v>1</v>
+      </c>
+      <c r="D1253">
+        <v>23</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1253">
+        <v>286</v>
+      </c>
+      <c r="H1253">
+        <v>10011414</v>
+      </c>
+      <c r="I1253">
+        <v>7500</v>
+      </c>
+      <c r="J1253">
+        <v>7550</v>
+      </c>
+      <c r="K1253" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1253" s="7">
+        <v>0.71817129629629628</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1254" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1254">
+        <v>436131</v>
+      </c>
+      <c r="C1254">
+        <v>1</v>
+      </c>
+      <c r="D1254">
+        <v>23</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1254">
+        <v>286</v>
+      </c>
+      <c r="H1254">
+        <v>10011414</v>
+      </c>
+      <c r="I1254">
+        <v>7500</v>
+      </c>
+      <c r="J1254">
+        <v>7500</v>
+      </c>
+      <c r="K1254" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1254" s="7">
+        <v>0.72180555555555559</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1255" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1255">
+        <v>436131</v>
+      </c>
+      <c r="C1255">
+        <v>1</v>
+      </c>
+      <c r="D1255">
+        <v>23</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1255">
+        <v>98</v>
+      </c>
+      <c r="H1255">
+        <v>10011446</v>
+      </c>
+      <c r="I1255">
+        <v>7000</v>
+      </c>
+      <c r="J1255">
+        <v>7050</v>
+      </c>
+      <c r="K1255" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1255" s="7">
+        <v>0.71038194444444447</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1256" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1256">
+        <v>436131</v>
+      </c>
+      <c r="C1256">
+        <v>1</v>
+      </c>
+      <c r="D1256">
+        <v>23</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1256">
+        <v>98</v>
+      </c>
+      <c r="H1256">
+        <v>10011446</v>
+      </c>
+      <c r="I1256">
+        <v>7000</v>
+      </c>
+      <c r="J1256">
+        <v>7000</v>
+      </c>
+      <c r="K1256" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1256" s="7">
+        <v>0.71563657407407411</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1257" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1257">
+        <v>436131</v>
+      </c>
+      <c r="C1257">
+        <v>1</v>
+      </c>
+      <c r="D1257">
+        <v>23</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1257">
+        <v>98</v>
+      </c>
+      <c r="H1257">
+        <v>10011446</v>
+      </c>
+      <c r="I1257">
+        <v>7000</v>
+      </c>
+      <c r="J1257">
+        <v>6950</v>
+      </c>
+      <c r="K1257" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1257" s="7">
+        <v>0.71890046296296295</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1258" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1258">
+        <v>436131</v>
+      </c>
+      <c r="C1258">
+        <v>1</v>
+      </c>
+      <c r="D1258">
+        <v>23</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1258">
+        <v>98</v>
+      </c>
+      <c r="H1258">
+        <v>10011446</v>
+      </c>
+      <c r="I1258">
+        <v>7000</v>
+      </c>
+      <c r="J1258">
+        <v>7000</v>
+      </c>
+      <c r="K1258" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1258" s="7">
+        <v>0.72231481481481485</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1259" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1259">
+        <v>436131</v>
+      </c>
+      <c r="C1259">
+        <v>1</v>
+      </c>
+      <c r="D1259">
+        <v>23</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1259">
+        <v>505</v>
+      </c>
+      <c r="H1259">
+        <v>10011509</v>
+      </c>
+      <c r="I1259">
+        <v>5000</v>
+      </c>
+      <c r="J1259">
+        <v>4900</v>
+      </c>
+      <c r="K1259" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1259" s="7">
+        <v>0.705474537037037</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1260" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1260">
+        <v>436131</v>
+      </c>
+      <c r="C1260">
+        <v>1</v>
+      </c>
+      <c r="D1260">
+        <v>23</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1260">
+        <v>505</v>
+      </c>
+      <c r="H1260">
+        <v>10011509</v>
+      </c>
+      <c r="I1260">
+        <v>15000</v>
+      </c>
+      <c r="J1260">
+        <v>15100</v>
+      </c>
+      <c r="K1260" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1260" s="7">
+        <v>0.7125231481481481</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1261" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1261">
+        <v>436131</v>
+      </c>
+      <c r="C1261">
+        <v>1</v>
+      </c>
+      <c r="D1261">
+        <v>23</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1261">
+        <v>505</v>
+      </c>
+      <c r="H1261">
+        <v>10011509</v>
+      </c>
+      <c r="I1261">
+        <v>15000</v>
+      </c>
+      <c r="J1261">
+        <v>15150</v>
+      </c>
+      <c r="K1261" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1261" s="7">
+        <v>0.71728009259259262</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1262" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1262">
+        <v>436131</v>
+      </c>
+      <c r="C1262">
+        <v>1</v>
+      </c>
+      <c r="D1262">
+        <v>23</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1262">
+        <v>505</v>
+      </c>
+      <c r="H1262">
+        <v>10011509</v>
+      </c>
+      <c r="I1262">
+        <v>14850</v>
+      </c>
+      <c r="J1262">
+        <v>14900</v>
+      </c>
+      <c r="K1262" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1262" s="7">
+        <v>0.72103009259259254</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1263" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1263">
+        <v>436131</v>
+      </c>
+      <c r="C1263">
+        <v>1</v>
+      </c>
+      <c r="D1263">
+        <v>23</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1263">
+        <v>519</v>
+      </c>
+      <c r="H1263">
+        <v>10011529</v>
+      </c>
+      <c r="I1263">
+        <v>10000</v>
+      </c>
+      <c r="J1263">
+        <v>9900</v>
+      </c>
+      <c r="K1263" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1263" s="7">
+        <v>0.71497685185185189</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1264" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1264">
+        <v>436131</v>
+      </c>
+      <c r="C1264">
+        <v>1</v>
+      </c>
+      <c r="D1264">
+        <v>23</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1264">
+        <v>947</v>
+      </c>
+      <c r="H1264">
+        <v>10011657</v>
+      </c>
+      <c r="I1264">
+        <v>15000</v>
+      </c>
+      <c r="J1264">
+        <v>15000</v>
+      </c>
+      <c r="K1264" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1264" s="7">
+        <v>0.70966435185185184</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1265" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1265">
+        <v>436132</v>
+      </c>
+      <c r="C1265">
+        <v>1</v>
+      </c>
+      <c r="D1265">
+        <v>18</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1265">
+        <v>286</v>
+      </c>
+      <c r="H1265">
+        <v>10011414</v>
+      </c>
+      <c r="I1265">
+        <v>10800</v>
+      </c>
+      <c r="J1265">
+        <v>10750</v>
+      </c>
+      <c r="K1265" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1265" s="7">
+        <v>0.76107638888888884</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1266" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1266">
+        <v>436132</v>
+      </c>
+      <c r="C1266">
+        <v>1</v>
+      </c>
+      <c r="D1266">
+        <v>18</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1266">
+        <v>98</v>
+      </c>
+      <c r="H1266">
+        <v>10011446</v>
+      </c>
+      <c r="I1266">
+        <v>7000</v>
+      </c>
+      <c r="J1266">
+        <v>6900</v>
+      </c>
+      <c r="K1266" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1266" s="7">
+        <v>0.68949074074074079</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1267" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1267">
+        <v>436132</v>
+      </c>
+      <c r="C1267">
+        <v>1</v>
+      </c>
+      <c r="D1267">
+        <v>18</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1267">
+        <v>98</v>
+      </c>
+      <c r="H1267">
+        <v>10011446</v>
+      </c>
+      <c r="I1267">
+        <v>7000</v>
+      </c>
+      <c r="J1267">
+        <v>7050</v>
+      </c>
+      <c r="K1267" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1267" s="7">
+        <v>0.69112268518518516</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1268" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1268">
+        <v>436132</v>
+      </c>
+      <c r="C1268">
+        <v>1</v>
+      </c>
+      <c r="D1268">
+        <v>18</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1268">
+        <v>947</v>
+      </c>
+      <c r="H1268">
+        <v>10011657</v>
+      </c>
+      <c r="I1268">
+        <v>10000</v>
+      </c>
+      <c r="J1268">
+        <v>10300</v>
+      </c>
+      <c r="K1268" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1268" s="7">
+        <v>0.69047453703703698</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1269" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1269">
+        <v>436132</v>
+      </c>
+      <c r="C1269">
+        <v>1</v>
+      </c>
+      <c r="D1269">
+        <v>18</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1269">
+        <v>947</v>
+      </c>
+      <c r="H1269">
+        <v>10011657</v>
+      </c>
+      <c r="I1269">
+        <v>15000</v>
+      </c>
+      <c r="J1269">
+        <v>14900</v>
+      </c>
+      <c r="K1269" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1269" s="7">
+        <v>0.75988425925925929</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1270" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1270">
+        <v>436132</v>
+      </c>
+      <c r="C1270">
+        <v>1</v>
+      </c>
+      <c r="D1270">
+        <v>18</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1270">
+        <v>444</v>
+      </c>
+      <c r="H1270">
+        <v>10012170</v>
+      </c>
+      <c r="I1270">
+        <v>24100</v>
+      </c>
+      <c r="J1270">
+        <v>24110</v>
+      </c>
+      <c r="K1270" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1270" s="7">
+        <v>0.7329282407407407</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1271" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1271">
+        <v>436132</v>
+      </c>
+      <c r="C1271">
+        <v>1</v>
+      </c>
+      <c r="D1271">
+        <v>18</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1271">
+        <v>444</v>
+      </c>
+      <c r="H1271">
+        <v>10012170</v>
+      </c>
+      <c r="I1271">
+        <v>24100</v>
+      </c>
+      <c r="J1271">
+        <v>24060</v>
+      </c>
+      <c r="K1271" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1271" s="7">
+        <v>0.73296296296296293</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1272" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1272">
+        <v>436132</v>
+      </c>
+      <c r="C1272">
+        <v>1</v>
+      </c>
+      <c r="D1272">
+        <v>18</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1272">
+        <v>525</v>
+      </c>
+      <c r="H1272">
+        <v>10012284</v>
+      </c>
+      <c r="I1272">
+        <v>700</v>
+      </c>
+      <c r="J1272">
+        <v>670</v>
+      </c>
+      <c r="K1272" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1272" s="7">
+        <v>0.74199074074074078</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1273" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1273">
+        <v>436132</v>
+      </c>
+      <c r="C1273">
+        <v>1</v>
+      </c>
+      <c r="D1273">
+        <v>18</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1273">
+        <v>923</v>
+      </c>
+      <c r="H1273">
+        <v>10012360</v>
+      </c>
+      <c r="I1273">
+        <v>4500</v>
+      </c>
+      <c r="J1273">
+        <v>4700</v>
+      </c>
+      <c r="K1273" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1273" s="7">
+        <v>0.6922800925925926</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1274" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1274">
+        <v>436132</v>
+      </c>
+      <c r="C1274">
+        <v>1</v>
+      </c>
+      <c r="D1274">
+        <v>18</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1274">
+        <v>291</v>
+      </c>
+      <c r="H1274">
+        <v>10012420</v>
+      </c>
+      <c r="I1274">
+        <v>1500</v>
+      </c>
+      <c r="J1274">
+        <v>1490</v>
+      </c>
+      <c r="K1274" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1274" s="7">
+        <v>0.75694444444444442</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1275" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1275">
+        <v>436132</v>
+      </c>
+      <c r="C1275">
+        <v>1</v>
+      </c>
+      <c r="D1275">
+        <v>18</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1275">
+        <v>984</v>
+      </c>
+      <c r="H1275">
+        <v>10031006</v>
+      </c>
+      <c r="I1275">
+        <v>12000</v>
+      </c>
+      <c r="J1275">
+        <v>11990</v>
+      </c>
+      <c r="K1275" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1275" s="7">
+        <v>0.72362268518518513</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1276" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1276">
+        <v>436132</v>
+      </c>
+      <c r="C1276">
+        <v>1</v>
+      </c>
+      <c r="D1276">
+        <v>18</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1276">
+        <v>864</v>
+      </c>
+      <c r="H1276">
+        <v>10031008</v>
+      </c>
+      <c r="I1276">
+        <v>3800</v>
+      </c>
+      <c r="J1276">
+        <v>3720</v>
+      </c>
+      <c r="K1276" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1276" s="7">
+        <v>0.72357638888888887</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1277" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1277">
+        <v>436135</v>
+      </c>
+      <c r="C1277">
+        <v>1</v>
+      </c>
+      <c r="D1277">
+        <v>4</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1277">
+        <v>286</v>
+      </c>
+      <c r="H1277">
+        <v>10011414</v>
+      </c>
+      <c r="I1277">
+        <v>15000</v>
+      </c>
+      <c r="J1277">
+        <v>15050</v>
+      </c>
+      <c r="K1277" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1277" s="7">
+        <v>0.77995370370370365</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1278" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1278">
+        <v>436135</v>
+      </c>
+      <c r="C1278">
+        <v>1</v>
+      </c>
+      <c r="D1278">
+        <v>4</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1278">
+        <v>947</v>
+      </c>
+      <c r="H1278">
+        <v>10011657</v>
+      </c>
+      <c r="I1278">
+        <v>14700</v>
+      </c>
+      <c r="J1278">
+        <v>14650</v>
+      </c>
+      <c r="K1278" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1278" s="7">
+        <v>0.77731481481481479</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1279" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1279">
+        <v>436136</v>
+      </c>
+      <c r="C1279">
+        <v>1</v>
+      </c>
+      <c r="D1279">
+        <v>14</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1279">
+        <v>286</v>
+      </c>
+      <c r="H1279">
+        <v>10011414</v>
+      </c>
+      <c r="I1279">
+        <v>30800</v>
+      </c>
+      <c r="J1279">
+        <v>30800</v>
+      </c>
+      <c r="K1279" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1279" s="7">
+        <v>0.74496527777777777</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1280" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1280">
+        <v>436136</v>
+      </c>
+      <c r="C1280">
+        <v>1</v>
+      </c>
+      <c r="D1280">
+        <v>14</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1280">
+        <v>505</v>
+      </c>
+      <c r="H1280">
+        <v>10011509</v>
+      </c>
+      <c r="I1280">
+        <v>5000</v>
+      </c>
+      <c r="J1280">
+        <v>5500</v>
+      </c>
+      <c r="K1280" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1280" s="7">
+        <v>0.73126157407407411</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1281" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1281">
+        <v>436136</v>
+      </c>
+      <c r="C1281">
+        <v>1</v>
+      </c>
+      <c r="D1281">
+        <v>14</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1281">
+        <v>505</v>
+      </c>
+      <c r="H1281">
+        <v>10011509</v>
+      </c>
+      <c r="I1281">
+        <v>14500</v>
+      </c>
+      <c r="J1281">
+        <v>15500</v>
+      </c>
+      <c r="K1281" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1281" s="7">
+        <v>0.73686342592592591</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1282" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1282">
+        <v>436136</v>
+      </c>
+      <c r="C1282">
+        <v>1</v>
+      </c>
+      <c r="D1282">
+        <v>14</v>
+      </c>
+      <c r="E1282" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1282">
+        <v>505</v>
+      </c>
+      <c r="H1282">
+        <v>10011509</v>
+      </c>
+      <c r="I1282">
+        <v>13800</v>
+      </c>
+      <c r="J1282">
+        <v>13800</v>
+      </c>
+      <c r="K1282" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1282" s="7">
+        <v>0.74134259259259261</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1283" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1283">
+        <v>436136</v>
+      </c>
+      <c r="C1283">
+        <v>1</v>
+      </c>
+      <c r="D1283">
+        <v>14</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1283">
+        <v>519</v>
+      </c>
+      <c r="H1283">
+        <v>10011529</v>
+      </c>
+      <c r="I1283">
+        <v>10000</v>
+      </c>
+      <c r="J1283">
+        <v>10200</v>
+      </c>
+      <c r="K1283" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1283" s="7">
+        <v>0.73903935185185188</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1284" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1284">
+        <v>436136</v>
+      </c>
+      <c r="C1284">
+        <v>1</v>
+      </c>
+      <c r="D1284">
+        <v>14</v>
+      </c>
+      <c r="E1284" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1284">
+        <v>947</v>
+      </c>
+      <c r="H1284">
+        <v>10011657</v>
+      </c>
+      <c r="I1284">
+        <v>15000</v>
+      </c>
+      <c r="J1284">
+        <v>15000</v>
+      </c>
+      <c r="K1284" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1284" s="7">
+        <v>0.73537037037037034</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1285" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1285">
+        <v>436137</v>
+      </c>
+      <c r="C1285">
+        <v>1</v>
+      </c>
+      <c r="D1285">
+        <v>15</v>
+      </c>
+      <c r="E1285" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1285">
+        <v>281</v>
+      </c>
+      <c r="H1285">
+        <v>10011414</v>
+      </c>
+      <c r="I1285">
+        <v>17000</v>
+      </c>
+      <c r="J1285">
+        <v>16900</v>
+      </c>
+      <c r="K1285" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1285" s="7">
+        <v>0.79753472222222221</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1286" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1286">
+        <v>436137</v>
+      </c>
+      <c r="C1286">
+        <v>1</v>
+      </c>
+      <c r="D1286">
+        <v>15</v>
+      </c>
+      <c r="E1286" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1286">
+        <v>947</v>
+      </c>
+      <c r="H1286">
+        <v>10011657</v>
+      </c>
+      <c r="I1286">
+        <v>20000</v>
+      </c>
+      <c r="J1286">
+        <v>20150</v>
+      </c>
+      <c r="K1286" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1286" s="7">
+        <v>0.75271990740740746</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1287" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1287">
+        <v>436137</v>
+      </c>
+      <c r="C1287">
+        <v>1</v>
+      </c>
+      <c r="D1287">
+        <v>15</v>
+      </c>
+      <c r="E1287" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1287">
+        <v>444</v>
+      </c>
+      <c r="H1287">
+        <v>10012170</v>
+      </c>
+      <c r="I1287">
+        <v>24100</v>
+      </c>
+      <c r="J1287">
+        <v>24050</v>
+      </c>
+      <c r="K1287" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1287" s="7">
+        <v>0.77947916666666661</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1288" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1288">
+        <v>436137</v>
+      </c>
+      <c r="C1288">
+        <v>1</v>
+      </c>
+      <c r="D1288">
+        <v>15</v>
+      </c>
+      <c r="E1288" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1288">
+        <v>923</v>
+      </c>
+      <c r="H1288">
+        <v>10012360</v>
+      </c>
+      <c r="I1288">
+        <v>4500</v>
+      </c>
+      <c r="J1288">
+        <v>4750</v>
+      </c>
+      <c r="K1288" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1288" s="7">
+        <v>0.75442129629629628</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1289" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1289">
+        <v>436137</v>
+      </c>
+      <c r="C1289">
+        <v>1</v>
+      </c>
+      <c r="D1289">
+        <v>15</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1289">
+        <v>984</v>
+      </c>
+      <c r="H1289">
+        <v>10031006</v>
+      </c>
+      <c r="I1289">
+        <v>6750</v>
+      </c>
+      <c r="J1289">
+        <v>6750</v>
+      </c>
+      <c r="K1289" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1289" s="7">
+        <v>0.77940972222222227</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1290" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1290">
+        <v>436137</v>
+      </c>
+      <c r="C1290">
+        <v>1</v>
+      </c>
+      <c r="D1290">
+        <v>15</v>
+      </c>
+      <c r="E1290" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1290">
+        <v>864</v>
+      </c>
+      <c r="H1290">
+        <v>10031008</v>
+      </c>
+      <c r="I1290">
+        <v>3800</v>
+      </c>
+      <c r="J1290">
+        <v>3710</v>
+      </c>
+      <c r="K1290" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1290" s="7">
+        <v>0.76722222222222225</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1291" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1291">
+        <v>436138</v>
+      </c>
+      <c r="C1291">
+        <v>1</v>
+      </c>
+      <c r="D1291">
+        <v>16</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1291">
+        <v>281</v>
+      </c>
+      <c r="H1291">
+        <v>10011414</v>
+      </c>
+      <c r="I1291">
+        <v>25000</v>
+      </c>
+      <c r="J1291">
+        <v>24950</v>
+      </c>
+      <c r="K1291" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1291" s="7">
+        <v>0.85864583333333333</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1292" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1292">
+        <v>436138</v>
+      </c>
+      <c r="C1292">
+        <v>1</v>
+      </c>
+      <c r="D1292">
+        <v>16</v>
+      </c>
+      <c r="E1292" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1292">
+        <v>947</v>
+      </c>
+      <c r="H1292">
+        <v>10011657</v>
+      </c>
+      <c r="I1292">
+        <v>20000</v>
+      </c>
+      <c r="J1292">
+        <v>19750</v>
+      </c>
+      <c r="K1292" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1292" s="7">
+        <v>0.79660879629629633</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1293" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1293">
+        <v>436138</v>
+      </c>
+      <c r="C1293">
+        <v>1</v>
+      </c>
+      <c r="D1293">
+        <v>16</v>
+      </c>
+      <c r="E1293" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1293">
+        <v>444</v>
+      </c>
+      <c r="H1293">
+        <v>10012170</v>
+      </c>
+      <c r="I1293">
+        <v>24100</v>
+      </c>
+      <c r="J1293">
+        <v>24060</v>
+      </c>
+      <c r="K1293" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1293" s="7">
+        <v>0.83332175925925922</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1294" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1294">
+        <v>436138</v>
+      </c>
+      <c r="C1294">
+        <v>1</v>
+      </c>
+      <c r="D1294">
+        <v>16</v>
+      </c>
+      <c r="E1294" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1294">
+        <v>525</v>
+      </c>
+      <c r="H1294">
+        <v>10012284</v>
+      </c>
+      <c r="I1294">
+        <v>1900</v>
+      </c>
+      <c r="J1294">
+        <v>1870</v>
+      </c>
+      <c r="K1294" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1294" s="7">
+        <v>0.82693287037037033</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1295" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1295">
+        <v>436138</v>
+      </c>
+      <c r="C1295">
+        <v>1</v>
+      </c>
+      <c r="D1295">
+        <v>16</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1295">
+        <v>291</v>
+      </c>
+      <c r="H1295">
+        <v>10012420</v>
+      </c>
+      <c r="I1295">
+        <v>1500</v>
+      </c>
+      <c r="J1295">
+        <v>1500</v>
+      </c>
+      <c r="K1295" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1295" s="7">
+        <v>0.8489930555555556</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1296" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1296">
+        <v>436138</v>
+      </c>
+      <c r="C1296">
+        <v>1</v>
+      </c>
+      <c r="D1296">
+        <v>16</v>
+      </c>
+      <c r="E1296" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1296">
+        <v>984</v>
+      </c>
+      <c r="H1296">
+        <v>10031006</v>
+      </c>
+      <c r="I1296">
+        <v>6750</v>
+      </c>
+      <c r="J1296">
+        <v>6750</v>
+      </c>
+      <c r="K1296" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1296" s="7">
+        <v>0.82724537037037038</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1297" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1297">
+        <v>436139</v>
+      </c>
+      <c r="C1297">
+        <v>1</v>
+      </c>
+      <c r="D1297">
+        <v>13</v>
+      </c>
+      <c r="E1297" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1297">
+        <v>286</v>
+      </c>
+      <c r="H1297">
+        <v>10011414</v>
+      </c>
+      <c r="I1297">
+        <v>10000</v>
+      </c>
+      <c r="J1297">
+        <v>10000</v>
+      </c>
+      <c r="K1297" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1297" s="7">
+        <v>0.98341435185185189</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1298" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1298">
+        <v>436139</v>
+      </c>
+      <c r="C1298">
+        <v>1</v>
+      </c>
+      <c r="D1298">
+        <v>13</v>
+      </c>
+      <c r="E1298" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1298">
+        <v>505</v>
+      </c>
+      <c r="H1298">
+        <v>10011509</v>
+      </c>
+      <c r="I1298">
+        <v>15000</v>
+      </c>
+      <c r="J1298">
+        <v>15000</v>
+      </c>
+      <c r="K1298" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1298" s="7">
+        <v>0.98214120370370372</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1299" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1299">
+        <v>436133</v>
+      </c>
+      <c r="C1299">
+        <v>1</v>
+      </c>
+      <c r="D1299">
+        <v>24</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1299">
+        <v>286</v>
+      </c>
+      <c r="H1299">
+        <v>10011414</v>
+      </c>
+      <c r="I1299">
+        <v>15000</v>
+      </c>
+      <c r="J1299">
+        <v>15000</v>
+      </c>
+      <c r="K1299" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1299" s="7">
+        <v>0.85569444444444442</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1300" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1300">
+        <v>436133</v>
+      </c>
+      <c r="C1300">
+        <v>1</v>
+      </c>
+      <c r="D1300">
+        <v>24</v>
+      </c>
+      <c r="E1300" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1300">
+        <v>98</v>
+      </c>
+      <c r="H1300">
+        <v>10011446</v>
+      </c>
+      <c r="I1300">
+        <v>7000</v>
+      </c>
+      <c r="J1300">
+        <v>7000</v>
+      </c>
+      <c r="K1300" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1300" s="7">
+        <v>0.8453356481481481</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1301" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1301">
+        <v>436133</v>
+      </c>
+      <c r="C1301">
+        <v>1</v>
+      </c>
+      <c r="D1301">
+        <v>24</v>
+      </c>
+      <c r="E1301" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1301">
+        <v>98</v>
+      </c>
+      <c r="H1301">
+        <v>10011446</v>
+      </c>
+      <c r="I1301">
+        <v>7000</v>
+      </c>
+      <c r="J1301">
+        <v>6900</v>
+      </c>
+      <c r="K1301" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1301" s="7">
+        <v>0.84908564814814813</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1302" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1302">
+        <v>436133</v>
+      </c>
+      <c r="C1302">
+        <v>1</v>
+      </c>
+      <c r="D1302">
+        <v>24</v>
+      </c>
+      <c r="E1302" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1302">
+        <v>98</v>
+      </c>
+      <c r="H1302">
+        <v>10011446</v>
+      </c>
+      <c r="I1302">
+        <v>7000</v>
+      </c>
+      <c r="J1302">
+        <v>7050</v>
+      </c>
+      <c r="K1302" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1302" s="7">
+        <v>0.85206018518518523</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1303" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1303">
+        <v>436133</v>
+      </c>
+      <c r="C1303">
+        <v>1</v>
+      </c>
+      <c r="D1303">
+        <v>24</v>
+      </c>
+      <c r="E1303" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1303">
+        <v>98</v>
+      </c>
+      <c r="H1303">
+        <v>10011446</v>
+      </c>
+      <c r="I1303">
+        <v>7000</v>
+      </c>
+      <c r="J1303">
+        <v>7100</v>
+      </c>
+      <c r="K1303" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1303" s="7">
+        <v>0.85659722222222223</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1304" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1304">
+        <v>436133</v>
+      </c>
+      <c r="C1304">
+        <v>1</v>
+      </c>
+      <c r="D1304">
+        <v>24</v>
+      </c>
+      <c r="E1304" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1304">
+        <v>505</v>
+      </c>
+      <c r="H1304">
+        <v>10011509</v>
+      </c>
+      <c r="I1304">
+        <v>5000</v>
+      </c>
+      <c r="J1304">
+        <v>4950</v>
+      </c>
+      <c r="K1304" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1304" s="7">
+        <v>0.84064814814814814</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1305" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1305">
+        <v>436133</v>
+      </c>
+      <c r="C1305">
+        <v>1</v>
+      </c>
+      <c r="D1305">
+        <v>24</v>
+      </c>
+      <c r="E1305" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1305">
+        <v>505</v>
+      </c>
+      <c r="H1305">
+        <v>10011509</v>
+      </c>
+      <c r="I1305">
+        <v>10000</v>
+      </c>
+      <c r="J1305">
+        <v>11300</v>
+      </c>
+      <c r="K1305" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1305" s="7">
+        <v>0.84657407407407403</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1306" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1306">
+        <v>436133</v>
+      </c>
+      <c r="C1306">
+        <v>1</v>
+      </c>
+      <c r="D1306">
+        <v>24</v>
+      </c>
+      <c r="E1306" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1306">
+        <v>505</v>
+      </c>
+      <c r="H1306">
+        <v>10011509</v>
+      </c>
+      <c r="I1306">
+        <v>18800</v>
+      </c>
+      <c r="J1306">
+        <v>18750</v>
+      </c>
+      <c r="K1306" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1306" s="7">
+        <v>0.85127314814814814</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1307" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1307">
+        <v>436133</v>
+      </c>
+      <c r="C1307">
+        <v>1</v>
+      </c>
+      <c r="D1307">
+        <v>24</v>
+      </c>
+      <c r="E1307" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1307">
+        <v>505</v>
+      </c>
+      <c r="H1307">
+        <v>10011509</v>
+      </c>
+      <c r="I1307">
+        <v>15000</v>
+      </c>
+      <c r="J1307">
+        <v>15200</v>
+      </c>
+      <c r="K1307" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1307" s="7">
+        <v>0.85385416666666669</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1308" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1308">
+        <v>436133</v>
+      </c>
+      <c r="C1308">
+        <v>1</v>
+      </c>
+      <c r="D1308">
+        <v>24</v>
+      </c>
+      <c r="E1308" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1308">
+        <v>519</v>
+      </c>
+      <c r="H1308">
+        <v>10011529</v>
+      </c>
+      <c r="I1308">
+        <v>10000</v>
+      </c>
+      <c r="J1308">
+        <v>9950</v>
+      </c>
+      <c r="K1308" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1308" s="7">
+        <v>0.84811342592592598</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1309" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1309">
+        <v>436133</v>
+      </c>
+      <c r="C1309">
+        <v>1</v>
+      </c>
+      <c r="D1309">
+        <v>24</v>
+      </c>
+      <c r="E1309" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1309">
+        <v>947</v>
+      </c>
+      <c r="H1309">
+        <v>10011657</v>
+      </c>
+      <c r="I1309">
+        <v>15000</v>
+      </c>
+      <c r="J1309">
+        <v>14950</v>
+      </c>
+      <c r="K1309" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1309" s="7">
+        <v>0.84458333333333335</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1310" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1310">
+        <v>436134</v>
+      </c>
+      <c r="C1310">
+        <v>1</v>
+      </c>
+      <c r="D1310">
+        <v>19</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1310">
+        <v>286</v>
+      </c>
+      <c r="H1310">
+        <v>10011414</v>
+      </c>
+      <c r="I1310">
+        <v>10800</v>
+      </c>
+      <c r="J1310">
+        <v>10800</v>
+      </c>
+      <c r="K1310" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1310" s="7">
+        <v>0.9006481481481482</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1311" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1311">
+        <v>436134</v>
+      </c>
+      <c r="C1311">
+        <v>1</v>
+      </c>
+      <c r="D1311">
+        <v>19</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1311">
+        <v>98</v>
+      </c>
+      <c r="H1311">
+        <v>10011446</v>
+      </c>
+      <c r="I1311">
+        <v>7000</v>
+      </c>
+      <c r="J1311">
+        <v>6950</v>
+      </c>
+      <c r="K1311" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1311" s="7">
+        <v>0.82476851851851851</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1312" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1312">
+        <v>436134</v>
+      </c>
+      <c r="C1312">
+        <v>1</v>
+      </c>
+      <c r="D1312">
+        <v>19</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1312">
+        <v>98</v>
+      </c>
+      <c r="H1312">
+        <v>10011446</v>
+      </c>
+      <c r="I1312">
+        <v>7000</v>
+      </c>
+      <c r="J1312">
+        <v>7000</v>
+      </c>
+      <c r="K1312" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1312" s="7">
+        <v>0.82962962962962961</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1313" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1313">
+        <v>436134</v>
+      </c>
+      <c r="C1313">
+        <v>1</v>
+      </c>
+      <c r="D1313">
+        <v>19</v>
+      </c>
+      <c r="E1313" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1313">
+        <v>947</v>
+      </c>
+      <c r="H1313">
+        <v>10011657</v>
+      </c>
+      <c r="I1313">
+        <v>15000</v>
+      </c>
+      <c r="J1313">
+        <v>15300</v>
+      </c>
+      <c r="K1313" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1313" s="7">
+        <v>0.82900462962962962</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1314" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1314">
+        <v>436134</v>
+      </c>
+      <c r="C1314">
+        <v>1</v>
+      </c>
+      <c r="D1314">
+        <v>19</v>
+      </c>
+      <c r="E1314" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1314">
+        <v>947</v>
+      </c>
+      <c r="H1314">
+        <v>10011657</v>
+      </c>
+      <c r="I1314">
+        <v>9700</v>
+      </c>
+      <c r="J1314">
+        <v>9750</v>
+      </c>
+      <c r="K1314" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1314" s="7">
+        <v>0.89831018518518524</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1315" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1315">
+        <v>436134</v>
+      </c>
+      <c r="C1315">
+        <v>1</v>
+      </c>
+      <c r="D1315">
+        <v>19</v>
+      </c>
+      <c r="E1315" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1315">
+        <v>444</v>
+      </c>
+      <c r="H1315">
+        <v>10012170</v>
+      </c>
+      <c r="I1315">
+        <v>24100</v>
+      </c>
+      <c r="J1315">
+        <v>24110</v>
+      </c>
+      <c r="K1315" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1315" s="7">
+        <v>0.87570601851851848</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1316" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1316">
+        <v>436134</v>
+      </c>
+      <c r="C1316">
+        <v>1</v>
+      </c>
+      <c r="D1316">
+        <v>19</v>
+      </c>
+      <c r="E1316" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1316">
+        <v>444</v>
+      </c>
+      <c r="H1316">
+        <v>10012170</v>
+      </c>
+      <c r="I1316">
+        <v>24100</v>
+      </c>
+      <c r="J1316">
+        <v>24200</v>
+      </c>
+      <c r="K1316" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1316" s="7">
+        <v>0.87577546296296294</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1317" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1317">
+        <v>436134</v>
+      </c>
+      <c r="C1317">
+        <v>1</v>
+      </c>
+      <c r="D1317">
+        <v>19</v>
+      </c>
+      <c r="E1317" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1317">
+        <v>525</v>
+      </c>
+      <c r="H1317">
+        <v>10012284</v>
+      </c>
+      <c r="I1317">
+        <v>1200</v>
+      </c>
+      <c r="J1317">
+        <v>1260</v>
+      </c>
+      <c r="K1317" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1317" s="7">
+        <v>0.88043981481481481</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1318" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1318">
+        <v>436134</v>
+      </c>
+      <c r="C1318">
+        <v>1</v>
+      </c>
+      <c r="D1318">
+        <v>19</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1318" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1318">
+        <v>923</v>
+      </c>
+      <c r="H1318">
+        <v>10012360</v>
+      </c>
+      <c r="I1318">
+        <v>4500</v>
+      </c>
+      <c r="J1318">
+        <v>4800</v>
+      </c>
+      <c r="K1318" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1318" s="7">
+        <v>0.83240740740740737</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1319" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1319">
+        <v>436134</v>
+      </c>
+      <c r="C1319">
+        <v>1</v>
+      </c>
+      <c r="D1319">
+        <v>19</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1319">
+        <v>291</v>
+      </c>
+      <c r="H1319">
+        <v>10012420</v>
+      </c>
+      <c r="I1319">
+        <v>1500</v>
+      </c>
+      <c r="J1319">
+        <v>1460</v>
+      </c>
+      <c r="K1319" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1319" s="7">
+        <v>0.88355324074074071</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1320" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1320">
+        <v>436134</v>
+      </c>
+      <c r="C1320">
+        <v>1</v>
+      </c>
+      <c r="D1320">
+        <v>19</v>
+      </c>
+      <c r="E1320" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1320">
+        <v>984</v>
+      </c>
+      <c r="H1320">
+        <v>10031006</v>
+      </c>
+      <c r="I1320">
+        <v>13500</v>
+      </c>
+      <c r="J1320">
+        <v>13520</v>
+      </c>
+      <c r="K1320" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1320" s="7">
+        <v>0.86432870370370374</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1321" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1321">
+        <v>436134</v>
+      </c>
+      <c r="C1321">
+        <v>1</v>
+      </c>
+      <c r="D1321">
+        <v>19</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1321" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1321">
+        <v>864</v>
+      </c>
+      <c r="H1321">
+        <v>10031008</v>
+      </c>
+      <c r="I1321">
+        <v>3800</v>
+      </c>
+      <c r="J1321">
+        <v>3740</v>
+      </c>
+      <c r="K1321" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1321" s="7">
+        <v>0.86427083333333332</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1322" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1322">
+        <v>436135</v>
+      </c>
+      <c r="C1322">
+        <v>1</v>
+      </c>
+      <c r="D1322">
+        <v>12</v>
+      </c>
+      <c r="E1322" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1322">
+        <v>286</v>
+      </c>
+      <c r="H1322">
+        <v>10011414</v>
+      </c>
+      <c r="I1322">
+        <v>15000</v>
+      </c>
+      <c r="J1322">
+        <v>14950</v>
+      </c>
+      <c r="K1322" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1322" s="7">
+        <v>0.93699074074074074</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1323" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1323">
+        <v>436135</v>
+      </c>
+      <c r="C1323">
+        <v>1</v>
+      </c>
+      <c r="D1323">
+        <v>12</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1323" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1323">
+        <v>947</v>
+      </c>
+      <c r="H1323">
+        <v>10011657</v>
+      </c>
+      <c r="I1323">
+        <v>14700</v>
+      </c>
+      <c r="J1323">
+        <v>14650</v>
+      </c>
+      <c r="K1323" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1323" s="7">
+        <v>0.93530092592592595</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1324" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1324">
+        <v>436134</v>
+      </c>
+      <c r="C1324">
+        <v>1</v>
+      </c>
+      <c r="D1324">
+        <v>17</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1324" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1324">
+        <v>98</v>
+      </c>
+      <c r="H1324">
+        <v>10011446</v>
+      </c>
+      <c r="I1324">
+        <v>7000</v>
+      </c>
+      <c r="J1324">
+        <v>7100</v>
+      </c>
+      <c r="K1324" s="6">
+        <v>46301</v>
+      </c>
+      <c r="L1324" s="7">
+        <v>0.99912037037037038</v>
       </c>
     </row>
   </sheetData>
@@ -46326,7 +52426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0AFB269-D4B1-4043-8907-6E4F0CDB8B89}">
-  <dimension ref="A1:W134"/>
+  <dimension ref="A1:W179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -54218,6 +60318,2655 @@
       </c>
       <c r="W134">
         <v>71740</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>288</v>
+      </c>
+      <c r="B135">
+        <v>1679427</v>
+      </c>
+      <c r="E135" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" t="s">
+        <v>288</v>
+      </c>
+      <c r="G135" t="s">
+        <v>392</v>
+      </c>
+      <c r="H135">
+        <v>2260264</v>
+      </c>
+      <c r="I135">
+        <v>10031006</v>
+      </c>
+      <c r="J135">
+        <v>984</v>
+      </c>
+      <c r="M135">
+        <v>24000000</v>
+      </c>
+      <c r="N135" s="6">
+        <v>46300</v>
+      </c>
+      <c r="O135" s="7">
+        <v>0.99965277777777772</v>
+      </c>
+      <c r="P135">
+        <v>356922</v>
+      </c>
+      <c r="Q135" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R135" s="7">
+        <v>9.0046296296296298E-3</v>
+      </c>
+      <c r="S135">
+        <v>356923</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>77380</v>
+      </c>
+      <c r="V135">
+        <v>31600</v>
+      </c>
+      <c r="W135">
+        <v>45780</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136">
+        <v>1679427</v>
+      </c>
+      <c r="E136" t="s">
+        <v>41</v>
+      </c>
+      <c r="F136">
+        <v>4</v>
+      </c>
+      <c r="G136" t="s">
+        <v>393</v>
+      </c>
+      <c r="H136">
+        <v>2260273</v>
+      </c>
+      <c r="I136">
+        <v>10031006</v>
+      </c>
+      <c r="J136">
+        <v>984</v>
+      </c>
+      <c r="M136">
+        <v>24000000</v>
+      </c>
+      <c r="N136" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O136" s="7">
+        <v>0.17980324074074075</v>
+      </c>
+      <c r="P136">
+        <v>356924</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R136" s="7">
+        <v>0.19288194444444445</v>
+      </c>
+      <c r="S136">
+        <v>356925</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>78480</v>
+      </c>
+      <c r="V136">
+        <v>32240</v>
+      </c>
+      <c r="W136">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>47</v>
+      </c>
+      <c r="B137">
+        <v>1668373</v>
+      </c>
+      <c r="E137" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137">
+        <v>47</v>
+      </c>
+      <c r="G137" t="s">
+        <v>394</v>
+      </c>
+      <c r="H137">
+        <v>76010</v>
+      </c>
+      <c r="I137">
+        <v>10011503</v>
+      </c>
+      <c r="J137">
+        <v>405</v>
+      </c>
+      <c r="M137">
+        <v>3360000</v>
+      </c>
+      <c r="N137" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O137" s="7">
+        <v>0.29399305555555555</v>
+      </c>
+      <c r="P137">
+        <v>356926</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R137" s="7">
+        <v>0.30258101851851854</v>
+      </c>
+      <c r="S137">
+        <v>356929</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>78140</v>
+      </c>
+      <c r="V137">
+        <v>32680</v>
+      </c>
+      <c r="W137">
+        <v>45460</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>590</v>
+      </c>
+      <c r="B138">
+        <v>1325993</v>
+      </c>
+      <c r="E138" t="s">
+        <v>41</v>
+      </c>
+      <c r="F138">
+        <v>590</v>
+      </c>
+      <c r="G138" t="s">
+        <v>395</v>
+      </c>
+      <c r="H138">
+        <v>8466121</v>
+      </c>
+      <c r="I138">
+        <v>10011521</v>
+      </c>
+      <c r="J138">
+        <v>249</v>
+      </c>
+      <c r="M138">
+        <v>99999999</v>
+      </c>
+      <c r="N138" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O138" s="7">
+        <v>0.29655092592592591</v>
+      </c>
+      <c r="P138">
+        <v>356927</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R138" s="7">
+        <v>0.30872685185185184</v>
+      </c>
+      <c r="S138">
+        <v>356932</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>80260</v>
+      </c>
+      <c r="V138">
+        <v>34740</v>
+      </c>
+      <c r="W138">
+        <v>45520</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>132</v>
+      </c>
+      <c r="B139">
+        <v>1709881</v>
+      </c>
+      <c r="E139" t="s">
+        <v>41</v>
+      </c>
+      <c r="F139">
+        <v>132</v>
+      </c>
+      <c r="G139" t="s">
+        <v>396</v>
+      </c>
+      <c r="H139">
+        <v>2788944</v>
+      </c>
+      <c r="I139">
+        <v>10011414</v>
+      </c>
+      <c r="J139">
+        <v>286</v>
+      </c>
+      <c r="M139">
+        <v>5600000</v>
+      </c>
+      <c r="N139" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O139" s="7">
+        <v>0.30141203703703706</v>
+      </c>
+      <c r="P139">
+        <v>356928</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R139" s="7">
+        <v>0.31033564814814812</v>
+      </c>
+      <c r="S139">
+        <v>356933</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>79360</v>
+      </c>
+      <c r="V139">
+        <v>31940</v>
+      </c>
+      <c r="W139">
+        <v>47420</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>530</v>
+      </c>
+      <c r="B140">
+        <v>1326014</v>
+      </c>
+      <c r="E140" t="s">
+        <v>41</v>
+      </c>
+      <c r="F140">
+        <v>530</v>
+      </c>
+      <c r="G140" t="s">
+        <v>397</v>
+      </c>
+      <c r="H140">
+        <v>8466122</v>
+      </c>
+      <c r="I140">
+        <v>10011657</v>
+      </c>
+      <c r="J140">
+        <v>947</v>
+      </c>
+      <c r="M140">
+        <v>99999999</v>
+      </c>
+      <c r="N140" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O140" s="7">
+        <v>0.30439814814814814</v>
+      </c>
+      <c r="P140">
+        <v>356930</v>
+      </c>
+      <c r="Q140" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R140" s="7">
+        <v>0.31214120370370368</v>
+      </c>
+      <c r="S140">
+        <v>356935</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>99120</v>
+      </c>
+      <c r="V140">
+        <v>33380</v>
+      </c>
+      <c r="W140">
+        <v>65740</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>495</v>
+      </c>
+      <c r="B141">
+        <v>1325989</v>
+      </c>
+      <c r="E141" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141">
+        <v>495</v>
+      </c>
+      <c r="G141" t="s">
+        <v>398</v>
+      </c>
+      <c r="H141">
+        <v>8466123</v>
+      </c>
+      <c r="I141">
+        <v>10011509</v>
+      </c>
+      <c r="J141">
+        <v>505</v>
+      </c>
+      <c r="M141">
+        <v>99999999</v>
+      </c>
+      <c r="N141" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O141" s="7">
+        <v>0.30715277777777777</v>
+      </c>
+      <c r="P141">
+        <v>356931</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R141" s="7">
+        <v>0.31443287037037038</v>
+      </c>
+      <c r="S141">
+        <v>356937</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="U141">
+        <v>84440</v>
+      </c>
+      <c r="V141">
+        <v>34520</v>
+      </c>
+      <c r="W141">
+        <v>49920</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>131</v>
+      </c>
+      <c r="B142">
+        <v>1709881</v>
+      </c>
+      <c r="E142" t="s">
+        <v>41</v>
+      </c>
+      <c r="F142">
+        <v>131</v>
+      </c>
+      <c r="G142" t="s">
+        <v>399</v>
+      </c>
+      <c r="H142">
+        <v>2790238</v>
+      </c>
+      <c r="I142">
+        <v>10011414</v>
+      </c>
+      <c r="J142">
+        <v>286</v>
+      </c>
+      <c r="M142">
+        <v>5600000</v>
+      </c>
+      <c r="N142" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O142" s="7">
+        <v>0.31062499999999998</v>
+      </c>
+      <c r="P142">
+        <v>356934</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R142" s="7">
+        <v>0.31725694444444447</v>
+      </c>
+      <c r="S142">
+        <v>356940</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>95120</v>
+      </c>
+      <c r="V142">
+        <v>34100</v>
+      </c>
+      <c r="W142">
+        <v>61020</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>490</v>
+      </c>
+      <c r="B143">
+        <v>1325993</v>
+      </c>
+      <c r="E143" t="s">
+        <v>41</v>
+      </c>
+      <c r="F143">
+        <v>490</v>
+      </c>
+      <c r="G143" t="s">
+        <v>400</v>
+      </c>
+      <c r="H143">
+        <v>8466125</v>
+      </c>
+      <c r="I143">
+        <v>10011521</v>
+      </c>
+      <c r="J143">
+        <v>249</v>
+      </c>
+      <c r="M143">
+        <v>99999999</v>
+      </c>
+      <c r="N143" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O143" s="7">
+        <v>0.31369212962962961</v>
+      </c>
+      <c r="P143">
+        <v>356936</v>
+      </c>
+      <c r="Q143" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R143" s="7">
+        <v>0.32449074074074075</v>
+      </c>
+      <c r="S143">
+        <v>356943</v>
+      </c>
+      <c r="T143">
+        <v>0</v>
+      </c>
+      <c r="U143">
+        <v>99540</v>
+      </c>
+      <c r="V143">
+        <v>34200</v>
+      </c>
+      <c r="W143">
+        <v>65340</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>22636</v>
+      </c>
+      <c r="B144">
+        <v>1437764</v>
+      </c>
+      <c r="E144" t="s">
+        <v>41</v>
+      </c>
+      <c r="F144">
+        <v>22636</v>
+      </c>
+      <c r="G144" t="s">
+        <v>401</v>
+      </c>
+      <c r="H144">
+        <v>2642961</v>
+      </c>
+      <c r="I144">
+        <v>10011446</v>
+      </c>
+      <c r="J144">
+        <v>95</v>
+      </c>
+      <c r="M144">
+        <v>99999999</v>
+      </c>
+      <c r="N144" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O144" s="7">
+        <v>0.31619212962962961</v>
+      </c>
+      <c r="P144">
+        <v>356939</v>
+      </c>
+      <c r="Q144" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R144" s="7">
+        <v>0.32944444444444443</v>
+      </c>
+      <c r="S144">
+        <v>356944</v>
+      </c>
+      <c r="T144">
+        <v>0</v>
+      </c>
+      <c r="U144">
+        <v>116800</v>
+      </c>
+      <c r="V144">
+        <v>43340</v>
+      </c>
+      <c r="W144">
+        <v>73460</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>409</v>
+      </c>
+      <c r="B145">
+        <v>1668366</v>
+      </c>
+      <c r="E145" t="s">
+        <v>41</v>
+      </c>
+      <c r="F145">
+        <v>409</v>
+      </c>
+      <c r="G145" t="s">
+        <v>402</v>
+      </c>
+      <c r="H145">
+        <v>76015</v>
+      </c>
+      <c r="I145">
+        <v>10011425</v>
+      </c>
+      <c r="J145" t="s">
+        <v>336</v>
+      </c>
+      <c r="M145">
+        <v>6720000</v>
+      </c>
+      <c r="N145" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O145" s="7">
+        <v>0.31910879629629629</v>
+      </c>
+      <c r="P145">
+        <v>356941</v>
+      </c>
+      <c r="Q145" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R145" s="7">
+        <v>0.33325231481481482</v>
+      </c>
+      <c r="S145">
+        <v>356946</v>
+      </c>
+      <c r="T145">
+        <v>0</v>
+      </c>
+      <c r="U145">
+        <v>78820</v>
+      </c>
+      <c r="V145">
+        <v>35720</v>
+      </c>
+      <c r="W145">
+        <v>43100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>130</v>
+      </c>
+      <c r="B146">
+        <v>1709881</v>
+      </c>
+      <c r="E146" t="s">
+        <v>41</v>
+      </c>
+      <c r="F146">
+        <v>130</v>
+      </c>
+      <c r="G146" t="s">
+        <v>403</v>
+      </c>
+      <c r="H146">
+        <v>2791883</v>
+      </c>
+      <c r="I146">
+        <v>10011414</v>
+      </c>
+      <c r="J146">
+        <v>286</v>
+      </c>
+      <c r="M146">
+        <v>5600000</v>
+      </c>
+      <c r="N146" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O146" s="7">
+        <v>0.32269675925925928</v>
+      </c>
+      <c r="P146">
+        <v>356942</v>
+      </c>
+      <c r="Q146" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R146" s="7">
+        <v>0.33547453703703706</v>
+      </c>
+      <c r="S146">
+        <v>356947</v>
+      </c>
+      <c r="T146">
+        <v>0</v>
+      </c>
+      <c r="U146">
+        <v>80020</v>
+      </c>
+      <c r="V146">
+        <v>38000</v>
+      </c>
+      <c r="W146">
+        <v>42020</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>128</v>
+      </c>
+      <c r="B147">
+        <v>1437341</v>
+      </c>
+      <c r="E147" t="s">
+        <v>41</v>
+      </c>
+      <c r="F147" t="s">
+        <v>128</v>
+      </c>
+      <c r="G147" t="s">
+        <v>128</v>
+      </c>
+      <c r="I147">
+        <v>10011660</v>
+      </c>
+      <c r="J147">
+        <v>149</v>
+      </c>
+      <c r="M147">
+        <v>179200</v>
+      </c>
+      <c r="N147" s="6">
+        <v>46297</v>
+      </c>
+      <c r="O147" s="7">
+        <v>0.60424768518518523</v>
+      </c>
+      <c r="P147">
+        <v>356769</v>
+      </c>
+      <c r="Q147" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R147" s="7">
+        <v>0.34365740740740741</v>
+      </c>
+      <c r="S147">
+        <v>356948</v>
+      </c>
+      <c r="T147">
+        <v>0</v>
+      </c>
+      <c r="U147">
+        <v>285850</v>
+      </c>
+      <c r="V147">
+        <v>67850</v>
+      </c>
+      <c r="W147">
+        <v>218000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>107</v>
+      </c>
+      <c r="B148">
+        <v>1709886</v>
+      </c>
+      <c r="E148" t="s">
+        <v>41</v>
+      </c>
+      <c r="F148">
+        <v>107</v>
+      </c>
+      <c r="G148" t="s">
+        <v>404</v>
+      </c>
+      <c r="H148">
+        <v>161922</v>
+      </c>
+      <c r="I148">
+        <v>10011414</v>
+      </c>
+      <c r="J148">
+        <v>285</v>
+      </c>
+      <c r="M148">
+        <v>6720000</v>
+      </c>
+      <c r="N148" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O148" s="7">
+        <v>0.33304398148148145</v>
+      </c>
+      <c r="P148">
+        <v>356945</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R148" s="7">
+        <v>0.34621527777777777</v>
+      </c>
+      <c r="S148">
+        <v>356949</v>
+      </c>
+      <c r="T148">
+        <v>0</v>
+      </c>
+      <c r="U148">
+        <v>78940</v>
+      </c>
+      <c r="V148">
+        <v>32600</v>
+      </c>
+      <c r="W148">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>22675</v>
+      </c>
+      <c r="B149">
+        <v>1448549</v>
+      </c>
+      <c r="E149" t="s">
+        <v>41</v>
+      </c>
+      <c r="F149">
+        <v>22675</v>
+      </c>
+      <c r="G149" t="s">
+        <v>405</v>
+      </c>
+      <c r="H149">
+        <v>833655</v>
+      </c>
+      <c r="I149">
+        <v>10011660</v>
+      </c>
+      <c r="J149">
+        <v>148</v>
+      </c>
+      <c r="M149">
+        <v>1120000</v>
+      </c>
+      <c r="N149" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O149" s="7">
+        <v>0.35263888888888889</v>
+      </c>
+      <c r="P149">
+        <v>356950</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R149" s="7">
+        <v>0.36343750000000002</v>
+      </c>
+      <c r="S149">
+        <v>356951</v>
+      </c>
+      <c r="T149">
+        <v>0</v>
+      </c>
+      <c r="U149">
+        <v>95320</v>
+      </c>
+      <c r="V149">
+        <v>40940</v>
+      </c>
+      <c r="W149">
+        <v>54380</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>126</v>
+      </c>
+      <c r="B150">
+        <v>1490615</v>
+      </c>
+      <c r="E150" t="s">
+        <v>41</v>
+      </c>
+      <c r="F150" t="s">
+        <v>126</v>
+      </c>
+      <c r="G150" t="s">
+        <v>126</v>
+      </c>
+      <c r="I150">
+        <v>10011503</v>
+      </c>
+      <c r="J150">
+        <v>405</v>
+      </c>
+      <c r="M150">
+        <v>1120000</v>
+      </c>
+      <c r="N150" s="6">
+        <v>46300</v>
+      </c>
+      <c r="O150" s="7">
+        <v>0.33439814814814817</v>
+      </c>
+      <c r="P150">
+        <v>356846</v>
+      </c>
+      <c r="Q150" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R150" s="7">
+        <v>0.38067129629629631</v>
+      </c>
+      <c r="S150">
+        <v>356953</v>
+      </c>
+      <c r="T150">
+        <v>0</v>
+      </c>
+      <c r="U150">
+        <v>192800</v>
+      </c>
+      <c r="V150">
+        <v>65750</v>
+      </c>
+      <c r="W150">
+        <v>127050</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>44735</v>
+      </c>
+      <c r="B151">
+        <v>1707671</v>
+      </c>
+      <c r="E151" t="s">
+        <v>41</v>
+      </c>
+      <c r="F151">
+        <v>44735</v>
+      </c>
+      <c r="G151" t="s">
+        <v>406</v>
+      </c>
+      <c r="H151">
+        <v>1100189</v>
+      </c>
+      <c r="I151">
+        <v>10011503</v>
+      </c>
+      <c r="J151">
+        <v>405</v>
+      </c>
+      <c r="L151" t="s">
+        <v>407</v>
+      </c>
+      <c r="M151">
+        <v>400960</v>
+      </c>
+      <c r="N151" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O151" s="7">
+        <v>0.37638888888888888</v>
+      </c>
+      <c r="P151">
+        <v>356952</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R151" s="7">
+        <v>0.39372685185185186</v>
+      </c>
+      <c r="S151">
+        <v>356955</v>
+      </c>
+      <c r="T151">
+        <v>0</v>
+      </c>
+      <c r="U151">
+        <v>78920</v>
+      </c>
+      <c r="V151">
+        <v>37180</v>
+      </c>
+      <c r="W151">
+        <v>41740</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>124</v>
+      </c>
+      <c r="B152">
+        <v>1326018</v>
+      </c>
+      <c r="E152" t="s">
+        <v>41</v>
+      </c>
+      <c r="F152" t="s">
+        <v>124</v>
+      </c>
+      <c r="G152" t="s">
+        <v>124</v>
+      </c>
+      <c r="I152">
+        <v>10011503</v>
+      </c>
+      <c r="J152">
+        <v>405</v>
+      </c>
+      <c r="L152" t="s">
+        <v>408</v>
+      </c>
+      <c r="M152">
+        <v>99999999</v>
+      </c>
+      <c r="N152" s="6">
+        <v>46297</v>
+      </c>
+      <c r="O152" s="7">
+        <v>0.5927662037037037</v>
+      </c>
+      <c r="P152">
+        <v>356768</v>
+      </c>
+      <c r="Q152" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R152" s="7">
+        <v>0.39684027777777775</v>
+      </c>
+      <c r="S152">
+        <v>356957</v>
+      </c>
+      <c r="T152">
+        <v>0</v>
+      </c>
+      <c r="U152">
+        <v>278800</v>
+      </c>
+      <c r="V152">
+        <v>88700</v>
+      </c>
+      <c r="W152">
+        <v>190100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>130</v>
+      </c>
+      <c r="B153">
+        <v>1709886</v>
+      </c>
+      <c r="E153" t="s">
+        <v>41</v>
+      </c>
+      <c r="F153">
+        <v>130</v>
+      </c>
+      <c r="G153" t="s">
+        <v>409</v>
+      </c>
+      <c r="H153">
+        <v>161925</v>
+      </c>
+      <c r="I153">
+        <v>10011414</v>
+      </c>
+      <c r="J153">
+        <v>281</v>
+      </c>
+      <c r="M153">
+        <v>6720000</v>
+      </c>
+      <c r="N153" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O153" s="7">
+        <v>0.38234953703703706</v>
+      </c>
+      <c r="P153">
+        <v>356954</v>
+      </c>
+      <c r="Q153" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R153" s="7">
+        <v>0.39773148148148146</v>
+      </c>
+      <c r="S153">
+        <v>356958</v>
+      </c>
+      <c r="T153">
+        <v>0</v>
+      </c>
+      <c r="U153">
+        <v>116180</v>
+      </c>
+      <c r="V153">
+        <v>42220</v>
+      </c>
+      <c r="W153">
+        <v>73960</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>126</v>
+      </c>
+      <c r="B154">
+        <v>1709886</v>
+      </c>
+      <c r="E154" t="s">
+        <v>41</v>
+      </c>
+      <c r="F154">
+        <v>126</v>
+      </c>
+      <c r="G154" t="s">
+        <v>410</v>
+      </c>
+      <c r="H154">
+        <v>161926</v>
+      </c>
+      <c r="I154">
+        <v>10011414</v>
+      </c>
+      <c r="J154">
+        <v>285</v>
+      </c>
+      <c r="M154">
+        <v>6720000</v>
+      </c>
+      <c r="N154" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O154" s="7">
+        <v>0.39568287037037037</v>
+      </c>
+      <c r="P154">
+        <v>356956</v>
+      </c>
+      <c r="Q154" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R154" s="7">
+        <v>0.40361111111111109</v>
+      </c>
+      <c r="S154">
+        <v>356960</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154">
+        <v>105760</v>
+      </c>
+      <c r="V154">
+        <v>34340</v>
+      </c>
+      <c r="W154">
+        <v>71420</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>105</v>
+      </c>
+      <c r="B155">
+        <v>1709886</v>
+      </c>
+      <c r="E155" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155">
+        <v>105</v>
+      </c>
+      <c r="G155" t="s">
+        <v>411</v>
+      </c>
+      <c r="H155">
+        <v>161928</v>
+      </c>
+      <c r="I155">
+        <v>10011414</v>
+      </c>
+      <c r="J155">
+        <v>281</v>
+      </c>
+      <c r="M155">
+        <v>6720000</v>
+      </c>
+      <c r="N155" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O155" s="7">
+        <v>0.39967592592592593</v>
+      </c>
+      <c r="P155">
+        <v>356959</v>
+      </c>
+      <c r="Q155" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R155" s="7">
+        <v>0.40842592592592591</v>
+      </c>
+      <c r="S155">
+        <v>356961</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155">
+        <v>78840</v>
+      </c>
+      <c r="V155">
+        <v>38060</v>
+      </c>
+      <c r="W155">
+        <v>40780</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>133</v>
+      </c>
+      <c r="B156">
+        <v>1709881</v>
+      </c>
+      <c r="E156" t="s">
+        <v>41</v>
+      </c>
+      <c r="F156">
+        <v>133</v>
+      </c>
+      <c r="G156" t="s">
+        <v>412</v>
+      </c>
+      <c r="H156">
+        <v>2795904</v>
+      </c>
+      <c r="I156">
+        <v>10011414</v>
+      </c>
+      <c r="J156">
+        <v>281</v>
+      </c>
+      <c r="M156">
+        <v>5600000</v>
+      </c>
+      <c r="N156" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O156" s="7">
+        <v>0.42170138888888886</v>
+      </c>
+      <c r="P156">
+        <v>356962</v>
+      </c>
+      <c r="Q156" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R156" s="7">
+        <v>0.43094907407407407</v>
+      </c>
+      <c r="S156">
+        <v>356964</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>100160</v>
+      </c>
+      <c r="V156">
+        <v>33660</v>
+      </c>
+      <c r="W156">
+        <v>66500</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>128</v>
+      </c>
+      <c r="B157">
+        <v>1709886</v>
+      </c>
+      <c r="E157" t="s">
+        <v>41</v>
+      </c>
+      <c r="F157">
+        <v>128</v>
+      </c>
+      <c r="G157" t="s">
+        <v>413</v>
+      </c>
+      <c r="H157">
+        <v>161933</v>
+      </c>
+      <c r="I157">
+        <v>10011414</v>
+      </c>
+      <c r="J157">
+        <v>285</v>
+      </c>
+      <c r="M157">
+        <v>6720000</v>
+      </c>
+      <c r="N157" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O157" s="7">
+        <v>0.42871527777777779</v>
+      </c>
+      <c r="P157">
+        <v>356963</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R157" s="7">
+        <v>0.4387962962962963</v>
+      </c>
+      <c r="S157">
+        <v>356965</v>
+      </c>
+      <c r="T157">
+        <v>0</v>
+      </c>
+      <c r="U157">
+        <v>113720</v>
+      </c>
+      <c r="V157">
+        <v>36520</v>
+      </c>
+      <c r="W157">
+        <v>77200</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>23</v>
+      </c>
+      <c r="B158">
+        <v>1709881</v>
+      </c>
+      <c r="E158" t="s">
+        <v>41</v>
+      </c>
+      <c r="F158">
+        <v>23</v>
+      </c>
+      <c r="G158" t="s">
+        <v>414</v>
+      </c>
+      <c r="H158">
+        <v>2796032</v>
+      </c>
+      <c r="I158">
+        <v>10011414</v>
+      </c>
+      <c r="J158">
+        <v>280</v>
+      </c>
+      <c r="M158">
+        <v>5600000</v>
+      </c>
+      <c r="N158" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O158" s="7">
+        <v>0.44026620370370373</v>
+      </c>
+      <c r="P158">
+        <v>356966</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R158" s="7">
+        <v>0.4526736111111111</v>
+      </c>
+      <c r="S158">
+        <v>356967</v>
+      </c>
+      <c r="T158">
+        <v>0</v>
+      </c>
+      <c r="U158">
+        <v>92720</v>
+      </c>
+      <c r="V158">
+        <v>30480</v>
+      </c>
+      <c r="W158">
+        <v>62240</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>169</v>
+      </c>
+      <c r="B159">
+        <v>1437754</v>
+      </c>
+      <c r="E159" t="s">
+        <v>41</v>
+      </c>
+      <c r="F159">
+        <v>169</v>
+      </c>
+      <c r="G159" t="s">
+        <v>415</v>
+      </c>
+      <c r="H159">
+        <v>776047</v>
+      </c>
+      <c r="I159">
+        <v>10011660</v>
+      </c>
+      <c r="J159">
+        <v>149</v>
+      </c>
+      <c r="M159">
+        <v>5000000</v>
+      </c>
+      <c r="N159" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O159" s="7">
+        <v>0.45857638888888891</v>
+      </c>
+      <c r="P159">
+        <v>356968</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R159" s="7">
+        <v>0.47236111111111112</v>
+      </c>
+      <c r="S159">
+        <v>356972</v>
+      </c>
+      <c r="T159">
+        <v>0</v>
+      </c>
+      <c r="U159">
+        <v>80800</v>
+      </c>
+      <c r="V159">
+        <v>36360</v>
+      </c>
+      <c r="W159">
+        <v>44440</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>22531</v>
+      </c>
+      <c r="B160">
+        <v>1448549</v>
+      </c>
+      <c r="E160" t="s">
+        <v>41</v>
+      </c>
+      <c r="F160">
+        <v>22531</v>
+      </c>
+      <c r="G160" t="s">
+        <v>416</v>
+      </c>
+      <c r="H160">
+        <v>833654</v>
+      </c>
+      <c r="I160">
+        <v>10011660</v>
+      </c>
+      <c r="J160">
+        <v>149</v>
+      </c>
+      <c r="M160">
+        <v>1120000</v>
+      </c>
+      <c r="N160" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O160" s="7">
+        <v>0.4674537037037037</v>
+      </c>
+      <c r="P160">
+        <v>356970</v>
+      </c>
+      <c r="Q160" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R160" s="7">
+        <v>0.47768518518518521</v>
+      </c>
+      <c r="S160">
+        <v>356973</v>
+      </c>
+      <c r="T160">
+        <v>0</v>
+      </c>
+      <c r="U160">
+        <v>89460</v>
+      </c>
+      <c r="V160">
+        <v>41300</v>
+      </c>
+      <c r="W160">
+        <v>48160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>76</v>
+      </c>
+      <c r="B161">
+        <v>1710464</v>
+      </c>
+      <c r="E161" t="s">
+        <v>41</v>
+      </c>
+      <c r="F161">
+        <v>76</v>
+      </c>
+      <c r="G161" t="s">
+        <v>417</v>
+      </c>
+      <c r="H161">
+        <v>3006</v>
+      </c>
+      <c r="I161">
+        <v>10011513</v>
+      </c>
+      <c r="J161">
+        <v>431</v>
+      </c>
+      <c r="M161">
+        <v>250880</v>
+      </c>
+      <c r="N161" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O161" s="7">
+        <v>0.46425925925925926</v>
+      </c>
+      <c r="P161">
+        <v>356969</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R161" s="7">
+        <v>0.47965277777777776</v>
+      </c>
+      <c r="S161">
+        <v>356974</v>
+      </c>
+      <c r="T161">
+        <v>0</v>
+      </c>
+      <c r="U161">
+        <v>56720</v>
+      </c>
+      <c r="V161">
+        <v>30600</v>
+      </c>
+      <c r="W161">
+        <v>26120</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>77</v>
+      </c>
+      <c r="B162">
+        <v>1326013</v>
+      </c>
+      <c r="E162" t="s">
+        <v>41</v>
+      </c>
+      <c r="F162">
+        <v>77</v>
+      </c>
+      <c r="G162" t="s">
+        <v>418</v>
+      </c>
+      <c r="H162">
+        <v>100620261</v>
+      </c>
+      <c r="I162">
+        <v>10011669</v>
+      </c>
+      <c r="J162" t="s">
+        <v>113</v>
+      </c>
+      <c r="M162">
+        <v>99999999</v>
+      </c>
+      <c r="N162" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O162" s="7">
+        <v>0.48042824074074075</v>
+      </c>
+      <c r="P162">
+        <v>356975</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R162" s="7">
+        <v>0.50032407407407409</v>
+      </c>
+      <c r="S162">
+        <v>356979</v>
+      </c>
+      <c r="T162">
+        <v>0</v>
+      </c>
+      <c r="U162">
+        <v>61040</v>
+      </c>
+      <c r="V162">
+        <v>38800</v>
+      </c>
+      <c r="W162">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>169</v>
+      </c>
+      <c r="B163">
+        <v>1437754</v>
+      </c>
+      <c r="E163" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163">
+        <v>169</v>
+      </c>
+      <c r="G163" t="s">
+        <v>419</v>
+      </c>
+      <c r="H163">
+        <v>776087</v>
+      </c>
+      <c r="I163">
+        <v>10011660</v>
+      </c>
+      <c r="J163">
+        <v>149</v>
+      </c>
+      <c r="M163">
+        <v>5000000</v>
+      </c>
+      <c r="N163" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O163" s="7">
+        <v>0.50292824074074072</v>
+      </c>
+      <c r="P163">
+        <v>356980</v>
+      </c>
+      <c r="Q163" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R163" s="7">
+        <v>0.51503472222222224</v>
+      </c>
+      <c r="S163">
+        <v>356982</v>
+      </c>
+      <c r="T163">
+        <v>0</v>
+      </c>
+      <c r="U163">
+        <v>81600</v>
+      </c>
+      <c r="V163">
+        <v>36320</v>
+      </c>
+      <c r="W163">
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>101</v>
+      </c>
+      <c r="B164">
+        <v>1709886</v>
+      </c>
+      <c r="E164" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164">
+        <v>101</v>
+      </c>
+      <c r="G164" t="s">
+        <v>420</v>
+      </c>
+      <c r="H164">
+        <v>161936</v>
+      </c>
+      <c r="I164">
+        <v>10011414</v>
+      </c>
+      <c r="J164">
+        <v>286</v>
+      </c>
+      <c r="M164">
+        <v>6720000</v>
+      </c>
+      <c r="N164" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O164" s="7">
+        <v>0.5124305555555555</v>
+      </c>
+      <c r="P164">
+        <v>356981</v>
+      </c>
+      <c r="Q164" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R164" s="7">
+        <v>0.52119212962962957</v>
+      </c>
+      <c r="S164">
+        <v>356984</v>
+      </c>
+      <c r="T164">
+        <v>0</v>
+      </c>
+      <c r="U164">
+        <v>79280</v>
+      </c>
+      <c r="V164">
+        <v>37620</v>
+      </c>
+      <c r="W164">
+        <v>41660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>107</v>
+      </c>
+      <c r="B165">
+        <v>1709886</v>
+      </c>
+      <c r="E165" t="s">
+        <v>41</v>
+      </c>
+      <c r="F165">
+        <v>107</v>
+      </c>
+      <c r="G165" t="s">
+        <v>421</v>
+      </c>
+      <c r="H165">
+        <v>161937</v>
+      </c>
+      <c r="I165">
+        <v>10011414</v>
+      </c>
+      <c r="J165">
+        <v>286</v>
+      </c>
+      <c r="M165">
+        <v>6720000</v>
+      </c>
+      <c r="N165" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O165" s="7">
+        <v>0.51677083333333329</v>
+      </c>
+      <c r="P165">
+        <v>356983</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R165" s="7">
+        <v>0.54096064814814815</v>
+      </c>
+      <c r="S165">
+        <v>356987</v>
+      </c>
+      <c r="T165">
+        <v>0</v>
+      </c>
+      <c r="U165">
+        <v>78920</v>
+      </c>
+      <c r="V165">
+        <v>33200</v>
+      </c>
+      <c r="W165">
+        <v>45720</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>22661</v>
+      </c>
+      <c r="B166">
+        <v>1437764</v>
+      </c>
+      <c r="E166" t="s">
+        <v>41</v>
+      </c>
+      <c r="F166">
+        <v>22661</v>
+      </c>
+      <c r="G166" t="s">
+        <v>422</v>
+      </c>
+      <c r="H166">
+        <v>2642967</v>
+      </c>
+      <c r="I166">
+        <v>10011446</v>
+      </c>
+      <c r="J166">
+        <v>95</v>
+      </c>
+      <c r="M166">
+        <v>99999999</v>
+      </c>
+      <c r="N166" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O166" s="7">
+        <v>0.53575231481481478</v>
+      </c>
+      <c r="P166">
+        <v>356985</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R166" s="7">
+        <v>0.54475694444444445</v>
+      </c>
+      <c r="S166">
+        <v>356989</v>
+      </c>
+      <c r="T166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>115520</v>
+      </c>
+      <c r="V166">
+        <v>34960</v>
+      </c>
+      <c r="W166">
+        <v>80560</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>125</v>
+      </c>
+      <c r="B167">
+        <v>1326015</v>
+      </c>
+      <c r="E167" t="s">
+        <v>41</v>
+      </c>
+      <c r="F167" t="s">
+        <v>125</v>
+      </c>
+      <c r="G167" t="s">
+        <v>125</v>
+      </c>
+      <c r="I167">
+        <v>10011558</v>
+      </c>
+      <c r="J167">
+        <v>602</v>
+      </c>
+      <c r="M167">
+        <v>99999999</v>
+      </c>
+      <c r="N167" s="6">
+        <v>46300</v>
+      </c>
+      <c r="O167" s="7">
+        <v>0.35203703703703704</v>
+      </c>
+      <c r="P167">
+        <v>356852</v>
+      </c>
+      <c r="Q167" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R167" s="7">
+        <v>0.5494444444444444</v>
+      </c>
+      <c r="S167">
+        <v>356991</v>
+      </c>
+      <c r="T167">
+        <v>0</v>
+      </c>
+      <c r="U167">
+        <v>274100</v>
+      </c>
+      <c r="V167">
+        <v>66250</v>
+      </c>
+      <c r="W167">
+        <v>207850</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>130</v>
+      </c>
+      <c r="B168">
+        <v>1709886</v>
+      </c>
+      <c r="E168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168">
+        <v>130</v>
+      </c>
+      <c r="G168" t="s">
+        <v>423</v>
+      </c>
+      <c r="H168">
+        <v>106261</v>
+      </c>
+      <c r="I168">
+        <v>10011414</v>
+      </c>
+      <c r="J168">
+        <v>286</v>
+      </c>
+      <c r="M168">
+        <v>6720000</v>
+      </c>
+      <c r="N168" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O168" s="7">
+        <v>0.54059027777777779</v>
+      </c>
+      <c r="P168">
+        <v>356986</v>
+      </c>
+      <c r="Q168" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R168" s="7">
+        <v>0.55041666666666667</v>
+      </c>
+      <c r="S168">
+        <v>356992</v>
+      </c>
+      <c r="T168">
+        <v>0</v>
+      </c>
+      <c r="U168">
+        <v>117280</v>
+      </c>
+      <c r="V168">
+        <v>42020</v>
+      </c>
+      <c r="W168">
+        <v>75260</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>126</v>
+      </c>
+      <c r="B169">
+        <v>1709886</v>
+      </c>
+      <c r="E169" t="s">
+        <v>41</v>
+      </c>
+      <c r="F169">
+        <v>126</v>
+      </c>
+      <c r="G169" t="s">
+        <v>424</v>
+      </c>
+      <c r="H169">
+        <v>106262</v>
+      </c>
+      <c r="I169">
+        <v>10011414</v>
+      </c>
+      <c r="J169">
+        <v>286</v>
+      </c>
+      <c r="M169">
+        <v>6720000</v>
+      </c>
+      <c r="N169" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O169" s="7">
+        <v>0.54364583333333338</v>
+      </c>
+      <c r="P169">
+        <v>356988</v>
+      </c>
+      <c r="Q169" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R169" s="7">
+        <v>0.5529398148148148</v>
+      </c>
+      <c r="S169">
+        <v>356994</v>
+      </c>
+      <c r="T169">
+        <v>0</v>
+      </c>
+      <c r="U169">
+        <v>109200</v>
+      </c>
+      <c r="V169">
+        <v>34120</v>
+      </c>
+      <c r="W169">
+        <v>75080</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>22690</v>
+      </c>
+      <c r="B170">
+        <v>1437764</v>
+      </c>
+      <c r="E170" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170">
+        <v>22690</v>
+      </c>
+      <c r="G170" t="s">
+        <v>425</v>
+      </c>
+      <c r="H170">
+        <v>2642960</v>
+      </c>
+      <c r="I170">
+        <v>10011446</v>
+      </c>
+      <c r="J170">
+        <v>96</v>
+      </c>
+      <c r="M170">
+        <v>99999999</v>
+      </c>
+      <c r="N170" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O170" s="7">
+        <v>0.54765046296296294</v>
+      </c>
+      <c r="P170">
+        <v>356990</v>
+      </c>
+      <c r="Q170" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R170" s="7">
+        <v>0.5656944444444445</v>
+      </c>
+      <c r="S170">
+        <v>356997</v>
+      </c>
+      <c r="T170">
+        <v>0</v>
+      </c>
+      <c r="U170">
+        <v>117660</v>
+      </c>
+      <c r="V170">
+        <v>35340</v>
+      </c>
+      <c r="W170">
+        <v>82320</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>22663</v>
+      </c>
+      <c r="B171">
+        <v>1437764</v>
+      </c>
+      <c r="E171" t="s">
+        <v>41</v>
+      </c>
+      <c r="F171">
+        <v>22663</v>
+      </c>
+      <c r="G171" t="s">
+        <v>426</v>
+      </c>
+      <c r="H171">
+        <v>2642963</v>
+      </c>
+      <c r="I171">
+        <v>10011446</v>
+      </c>
+      <c r="J171">
+        <v>96</v>
+      </c>
+      <c r="M171">
+        <v>99999999</v>
+      </c>
+      <c r="N171" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O171" s="7">
+        <v>0.55899305555555556</v>
+      </c>
+      <c r="P171">
+        <v>356995</v>
+      </c>
+      <c r="Q171" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R171" s="7">
+        <v>0.5708333333333333</v>
+      </c>
+      <c r="S171">
+        <v>356998</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>116060</v>
+      </c>
+      <c r="V171">
+        <v>34460</v>
+      </c>
+      <c r="W171">
+        <v>81600</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>169</v>
+      </c>
+      <c r="B172">
+        <v>1437754</v>
+      </c>
+      <c r="E172" t="s">
+        <v>41</v>
+      </c>
+      <c r="F172">
+        <v>169</v>
+      </c>
+      <c r="G172" t="s">
+        <v>427</v>
+      </c>
+      <c r="H172">
+        <v>776133</v>
+      </c>
+      <c r="I172">
+        <v>10011660</v>
+      </c>
+      <c r="J172">
+        <v>149</v>
+      </c>
+      <c r="M172">
+        <v>5000000</v>
+      </c>
+      <c r="N172" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O172" s="7">
+        <v>0.56282407407407409</v>
+      </c>
+      <c r="P172">
+        <v>356996</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R172" s="7">
+        <v>0.57851851851851854</v>
+      </c>
+      <c r="S172">
+        <v>357000</v>
+      </c>
+      <c r="T172">
+        <v>0</v>
+      </c>
+      <c r="U172">
+        <v>81840</v>
+      </c>
+      <c r="V172">
+        <v>36340</v>
+      </c>
+      <c r="W172">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>22636</v>
+      </c>
+      <c r="B173">
+        <v>1437764</v>
+      </c>
+      <c r="E173" t="s">
+        <v>41</v>
+      </c>
+      <c r="F173">
+        <v>22636</v>
+      </c>
+      <c r="G173" t="s">
+        <v>428</v>
+      </c>
+      <c r="H173">
+        <v>2642962</v>
+      </c>
+      <c r="I173">
+        <v>10011446</v>
+      </c>
+      <c r="J173">
+        <v>94</v>
+      </c>
+      <c r="M173">
+        <v>99999999</v>
+      </c>
+      <c r="N173" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O173" s="7">
+        <v>0.55278935185185185</v>
+      </c>
+      <c r="P173">
+        <v>356993</v>
+      </c>
+      <c r="Q173" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R173" s="7">
+        <v>0.5848726851851852</v>
+      </c>
+      <c r="S173">
+        <v>357001</v>
+      </c>
+      <c r="T173">
+        <v>0</v>
+      </c>
+      <c r="U173">
+        <v>115820</v>
+      </c>
+      <c r="V173">
+        <v>43480</v>
+      </c>
+      <c r="W173">
+        <v>72340</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>22632</v>
+      </c>
+      <c r="B174">
+        <v>1437764</v>
+      </c>
+      <c r="E174" t="s">
+        <v>41</v>
+      </c>
+      <c r="F174">
+        <v>22632</v>
+      </c>
+      <c r="G174" t="s">
+        <v>429</v>
+      </c>
+      <c r="H174">
+        <v>2642968</v>
+      </c>
+      <c r="I174">
+        <v>10011446</v>
+      </c>
+      <c r="J174">
+        <v>96</v>
+      </c>
+      <c r="M174">
+        <v>99999999</v>
+      </c>
+      <c r="N174" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O174" s="7">
+        <v>0.57396990740740739</v>
+      </c>
+      <c r="P174">
+        <v>356999</v>
+      </c>
+      <c r="Q174" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R174" s="7">
+        <v>0.58684027777777781</v>
+      </c>
+      <c r="S174">
+        <v>357002</v>
+      </c>
+      <c r="T174">
+        <v>0</v>
+      </c>
+      <c r="U174">
+        <v>111940</v>
+      </c>
+      <c r="V174">
+        <v>35100</v>
+      </c>
+      <c r="W174">
+        <v>76840</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>22608</v>
+      </c>
+      <c r="B175">
+        <v>1437764</v>
+      </c>
+      <c r="E175" t="s">
+        <v>41</v>
+      </c>
+      <c r="F175">
+        <v>22608</v>
+      </c>
+      <c r="G175" t="s">
+        <v>430</v>
+      </c>
+      <c r="H175">
+        <v>2642964</v>
+      </c>
+      <c r="I175">
+        <v>10011446</v>
+      </c>
+      <c r="J175">
+        <v>91</v>
+      </c>
+      <c r="M175">
+        <v>99999999</v>
+      </c>
+      <c r="N175" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O175" s="7">
+        <v>0.59285879629629634</v>
+      </c>
+      <c r="P175">
+        <v>357003</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R175" s="7">
+        <v>0.60152777777777777</v>
+      </c>
+      <c r="S175">
+        <v>357005</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="U175">
+        <v>115920</v>
+      </c>
+      <c r="V175">
+        <v>35040</v>
+      </c>
+      <c r="W175">
+        <v>80880</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>18</v>
+      </c>
+      <c r="B176">
+        <v>1620675</v>
+      </c>
+      <c r="E176" t="s">
+        <v>41</v>
+      </c>
+      <c r="F176">
+        <v>18</v>
+      </c>
+      <c r="G176" t="s">
+        <v>431</v>
+      </c>
+      <c r="H176">
+        <v>776122</v>
+      </c>
+      <c r="I176">
+        <v>10011660</v>
+      </c>
+      <c r="J176">
+        <v>149</v>
+      </c>
+      <c r="M176">
+        <v>13000000</v>
+      </c>
+      <c r="N176" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O176" s="7">
+        <v>0.59787037037037039</v>
+      </c>
+      <c r="P176">
+        <v>357004</v>
+      </c>
+      <c r="Q176" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R176" s="7">
+        <v>0.61032407407407407</v>
+      </c>
+      <c r="S176">
+        <v>357007</v>
+      </c>
+      <c r="T176">
+        <v>0</v>
+      </c>
+      <c r="U176">
+        <v>79100</v>
+      </c>
+      <c r="V176">
+        <v>34880</v>
+      </c>
+      <c r="W176">
+        <v>44220</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>128</v>
+      </c>
+      <c r="B177">
+        <v>1709886</v>
+      </c>
+      <c r="E177" t="s">
+        <v>41</v>
+      </c>
+      <c r="F177">
+        <v>128</v>
+      </c>
+      <c r="G177" t="s">
+        <v>432</v>
+      </c>
+      <c r="H177">
+        <v>161952</v>
+      </c>
+      <c r="I177">
+        <v>10011414</v>
+      </c>
+      <c r="J177">
+        <v>286</v>
+      </c>
+      <c r="M177">
+        <v>6720000</v>
+      </c>
+      <c r="N177" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O177" s="7">
+        <v>0.6118055555555556</v>
+      </c>
+      <c r="P177">
+        <v>357008</v>
+      </c>
+      <c r="Q177" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R177" s="7">
+        <v>0.62528935185185186</v>
+      </c>
+      <c r="S177">
+        <v>357010</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+      <c r="U177">
+        <v>112500</v>
+      </c>
+      <c r="V177">
+        <v>36380</v>
+      </c>
+      <c r="W177">
+        <v>76120</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>22532</v>
+      </c>
+      <c r="B178">
+        <v>1437764</v>
+      </c>
+      <c r="E178" t="s">
+        <v>41</v>
+      </c>
+      <c r="F178">
+        <v>22532</v>
+      </c>
+      <c r="G178" t="s">
+        <v>433</v>
+      </c>
+      <c r="H178">
+        <v>2642965</v>
+      </c>
+      <c r="I178">
+        <v>10011446</v>
+      </c>
+      <c r="J178">
+        <v>94</v>
+      </c>
+      <c r="M178">
+        <v>99999999</v>
+      </c>
+      <c r="N178" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O178" s="7">
+        <v>0.60534722222222226</v>
+      </c>
+      <c r="P178">
+        <v>357006</v>
+      </c>
+      <c r="Q178" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R178" s="7">
+        <v>0.63665509259259256</v>
+      </c>
+      <c r="S178">
+        <v>357011</v>
+      </c>
+      <c r="T178">
+        <v>0</v>
+      </c>
+      <c r="U178">
+        <v>119000</v>
+      </c>
+      <c r="V178">
+        <v>36260</v>
+      </c>
+      <c r="W178">
+        <v>82740</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>23</v>
+      </c>
+      <c r="B179">
+        <v>1709881</v>
+      </c>
+      <c r="E179" t="s">
+        <v>41</v>
+      </c>
+      <c r="F179">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>434</v>
+      </c>
+      <c r="H179">
+        <v>2801187</v>
+      </c>
+      <c r="I179">
+        <v>10011414</v>
+      </c>
+      <c r="J179">
+        <v>286</v>
+      </c>
+      <c r="M179">
+        <v>5600000</v>
+      </c>
+      <c r="N179" s="6">
+        <v>46301</v>
+      </c>
+      <c r="O179" s="7">
+        <v>0.61685185185185187</v>
+      </c>
+      <c r="P179">
+        <v>357009</v>
+      </c>
+      <c r="Q179" s="6">
+        <v>46301</v>
+      </c>
+      <c r="R179" s="7">
+        <v>0.63799768518518518</v>
+      </c>
+      <c r="S179">
+        <v>357012</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+      <c r="U179">
+        <v>91180</v>
+      </c>
+      <c r="V179">
+        <v>30300</v>
+      </c>
+      <c r="W179">
+        <v>60880</v>
       </c>
     </row>
   </sheetData>
@@ -54388,18 +63137,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="I1" s="31" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="43"/>
+      <c r="I1" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32">
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="45">
         <v>51</v>
       </c>
     </row>
@@ -54440,7 +63189,7 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="32"/>
+      <c r="M2" s="45"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -54643,226 +63392,226 @@
       <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="29">
         <v>1326018</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="29">
         <v>10011503</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <v>277800</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="31">
         <v>65900</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="31">
         <v>211900</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="32">
         <v>278800</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="33">
         <v>88700</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="34">
         <v>405</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L11" s="35" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45" t="s">
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="40" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="29">
         <v>1326015</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="29">
         <v>10011558</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="31">
         <v>273700</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="31">
         <v>65900</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="31">
         <v>207800</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="32">
         <v>274100</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="33">
         <v>66250</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="34">
         <v>602</v>
       </c>
-      <c r="L13" s="40" t="s">
+      <c r="L13" s="35" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="41"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="40" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="29">
         <v>1490615</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="29">
         <v>10011503</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="31">
         <v>193200</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="31">
         <v>66800</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="31">
         <v>126400</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="32">
         <v>192800</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15" s="33">
         <v>65750</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="34">
         <v>405</v>
       </c>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="35" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="41"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43" t="s">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45" t="s">
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="40" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="29">
         <v>1437341</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="29">
         <v>10011660</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="31">
         <v>284000</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="31">
         <v>68200</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="31">
         <v>215800</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="32">
         <v>285850</v>
       </c>
-      <c r="J17" s="38">
+      <c r="J17" s="33">
         <v>67850</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="34">
         <v>149</v>
       </c>
-      <c r="L17" s="40" t="s">
+      <c r="L17" s="35" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="41"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43" t="s">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="45" t="s">
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="40" t="s">
         <v>364</v>
       </c>
     </row>

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D950429-8EBD-43A3-818E-3FDE38813192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAA6A5E-E623-444F-B7D6-A598456BE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6208" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6259" uniqueCount="656">
   <si>
     <t>Date</t>
   </si>
@@ -1931,6 +1931,81 @@
   <si>
     <t>Empty 10/9</t>
   </si>
+  <si>
+    <t>AEX19544</t>
+  </si>
+  <si>
+    <t>COHEN BROTHERS I</t>
+  </si>
+  <si>
+    <t>S 409 Aluminumized Scrap</t>
+  </si>
+  <si>
+    <t>Middletown</t>
+  </si>
+  <si>
+    <t>AEX19683</t>
+  </si>
+  <si>
+    <t>AEX26519</t>
+  </si>
+  <si>
+    <t>S 430 Scrap</t>
+  </si>
+  <si>
+    <t>AEX26547</t>
+  </si>
+  <si>
+    <t>AEX26559</t>
+  </si>
+  <si>
+    <t>AEX26583</t>
+  </si>
+  <si>
+    <t>S 436 St Scrap</t>
+  </si>
+  <si>
+    <t>CLVX807367</t>
+  </si>
+  <si>
+    <t>GNWR4052</t>
+  </si>
+  <si>
+    <t>ARVIN SANGO INC</t>
+  </si>
+  <si>
+    <t>Kroot</t>
+  </si>
+  <si>
+    <t>GNWR4057</t>
+  </si>
+  <si>
+    <t>AK TUBE LLC</t>
+  </si>
+  <si>
+    <t>OMNX102006</t>
+  </si>
+  <si>
+    <t>OMNISOURCE CORPO</t>
+  </si>
+  <si>
+    <t>Omnisource</t>
+  </si>
+  <si>
+    <t>OMNX2069</t>
+  </si>
+  <si>
+    <t>ZVBX6244</t>
+  </si>
+  <si>
+    <t>RG&gt;409Stainless</t>
+  </si>
+  <si>
+    <t>40Y/602</t>
+  </si>
+  <si>
+    <t>RG&gt;181Stainless</t>
+  </si>
 </sst>
 </file>
 
@@ -2218,7 +2293,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2237,6 +2312,34 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2269,6 +2372,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2283,6 +2390,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -87387,7 +87497,7 @@
       <c r="A2" s="6">
         <v>46296</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="C2">
@@ -87396,10 +87506,10 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -87427,7 +87537,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80722F43-7756-4701-9ABB-7A6774075D14}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -87444,18 +87554,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="I1" s="25" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="I1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26">
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40">
         <v>51</v>
       </c>
     </row>
@@ -87496,567 +87606,1149 @@
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="26"/>
+      <c r="M2" s="40"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="22">
         <v>1326018</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="22">
         <v>10011503</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="24">
         <v>277800</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="24">
         <v>65900</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="24">
         <v>211900</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="25">
         <v>278800</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="26">
         <v>88700</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="27">
         <v>405</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="33" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <v>1326015</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="22">
         <v>10011558</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="24">
         <v>273700</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="24">
         <v>65900</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="24">
         <v>207800</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="25">
         <v>274100</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="26">
         <v>66250</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="27">
         <v>602</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="21" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="33" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <v>1490615</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="22">
         <v>10011503</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="24">
         <v>193200</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="24">
         <v>66800</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="24">
         <v>126400</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="25">
         <v>192800</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="26">
         <v>65750</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="27">
         <v>405</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="33" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="22">
         <v>1437341</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="22">
         <v>10011660</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="24">
         <v>284000</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="24">
         <v>68200</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="24">
         <v>215800</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="25">
         <v>285850</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="26">
         <v>67850</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="27">
         <v>149</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L9" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="21" t="s">
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="33" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="22">
         <v>1326018</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="22">
         <v>10011503</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="24">
         <v>255200</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="24">
         <v>68900</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="24">
         <v>186300</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="25">
         <v>255750</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="26">
         <v>58050</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="27">
         <v>405</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="21" t="s">
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="33" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="22">
         <v>1326018</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="22">
         <v>10011503</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="24">
         <v>255200</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="24">
         <v>68900</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="24">
         <v>186300</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="25">
         <v>255750</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="26">
         <v>58050</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="27">
         <v>405</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L13" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19" t="s">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="21" t="s">
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="33" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="22">
         <v>1699514</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="22">
         <v>10011414</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="24">
         <v>283060</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="24">
         <v>72440</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="24">
         <v>210620</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="25">
         <v>280400</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="26">
         <v>72900</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="27">
         <v>286</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L15" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="21" t="s">
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="33" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="22">
         <v>1699514</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="22">
         <v>10011414</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="24">
         <v>263200</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="24">
         <v>68800</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="24">
         <v>194400</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="25">
         <v>261700</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="26">
         <v>67050</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="27">
         <v>286</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L17" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19" t="s">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="21" t="s">
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="33" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="22">
         <v>1699514</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="22">
         <v>10011414</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="24">
         <v>281400</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="24">
         <v>72780</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="24">
         <v>208620</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="25">
         <v>278750</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="26">
         <v>68800</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="27">
         <v>281</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L19" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21" t="s">
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="33" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="22">
         <v>1699514</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="22">
         <v>10011414</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="24">
         <v>285280</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="24">
         <v>79340</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="24">
         <v>205940</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="25">
         <v>283750</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="26">
         <v>75450</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="27">
         <v>285</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L21" s="28" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="21" t="s">
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="33" t="s">
         <v>630</v>
       </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1668369</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D23" s="9">
+        <v>10011502</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="F23" s="11">
+        <v>259360</v>
+      </c>
+      <c r="G23" s="11">
+        <v>69780</v>
+      </c>
+      <c r="H23" s="11">
+        <v>189580</v>
+      </c>
+      <c r="I23" s="18">
+        <v>259650</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="14">
+        <v>405</v>
+      </c>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="41">
+        <v>1668373</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1326018</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="9">
+        <v>10011503</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="11">
+        <v>262100</v>
+      </c>
+      <c r="G25" s="11">
+        <v>69500</v>
+      </c>
+      <c r="H25" s="11">
+        <v>192600</v>
+      </c>
+      <c r="I25" s="34"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="15"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="17"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B27" s="9">
+        <v>1668372</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D27" s="9">
+        <v>10011509</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F27" s="11">
+        <v>260180</v>
+      </c>
+      <c r="G27" s="11">
+        <v>60200</v>
+      </c>
+      <c r="H27" s="11">
+        <v>199980</v>
+      </c>
+      <c r="I27" s="34"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="15"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B29" s="9">
+        <v>1668372</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D29" s="9">
+        <v>10011509</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F29" s="11">
+        <v>259280</v>
+      </c>
+      <c r="G29" s="11">
+        <v>58840</v>
+      </c>
+      <c r="H29" s="11">
+        <v>200440</v>
+      </c>
+      <c r="I29" s="34"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="15"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1668369</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D31" s="9">
+        <v>10011502</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="F31" s="11">
+        <v>259620</v>
+      </c>
+      <c r="G31" s="11">
+        <v>56840</v>
+      </c>
+      <c r="H31" s="11">
+        <v>202780</v>
+      </c>
+      <c r="I31" s="34"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="15"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="17"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="B33" s="9">
+        <v>1326020</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="9">
+        <v>10011657</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="F33" s="11">
+        <v>234900</v>
+      </c>
+      <c r="G33" s="11">
+        <v>62600</v>
+      </c>
+      <c r="H33" s="11">
+        <v>172300</v>
+      </c>
+      <c r="I33" s="34"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="15"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="17"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B35" s="9">
+        <v>1668373</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D35" s="9">
+        <v>10011503</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="11">
+        <v>260660</v>
+      </c>
+      <c r="G35" s="11">
+        <v>80680</v>
+      </c>
+      <c r="H35" s="11">
+        <v>179980</v>
+      </c>
+      <c r="I35" s="34"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="15"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="17"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B37" s="9">
+        <v>1390356</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="D37" s="9">
+        <v>10011509</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F37" s="11">
+        <v>260450</v>
+      </c>
+      <c r="G37" s="11">
+        <v>59120</v>
+      </c>
+      <c r="H37" s="11">
+        <v>201330</v>
+      </c>
+      <c r="I37" s="18">
+        <v>260850</v>
+      </c>
+      <c r="J37" s="11"/>
+      <c r="K37" s="14">
+        <v>504</v>
+      </c>
+      <c r="L37" s="15"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="17"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="B39" s="9">
+        <v>1442707</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="D39" s="9">
+        <v>10011503</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="11">
+        <v>259250</v>
+      </c>
+      <c r="G39" s="11">
+        <v>59980</v>
+      </c>
+      <c r="H39" s="11">
+        <v>199270</v>
+      </c>
+      <c r="I39" s="18">
+        <v>259550</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="14">
+        <v>405</v>
+      </c>
+      <c r="L39" s="15"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="17"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="B41" s="9">
+        <v>1692202</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="D41" s="9">
+        <v>10011503</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="11">
+        <v>239334</v>
+      </c>
+      <c r="G41" s="11">
+        <v>78397</v>
+      </c>
+      <c r="H41" s="11">
+        <v>160937</v>
+      </c>
+      <c r="I41" s="18">
+        <v>240050</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="L41" s="15"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="35" t="s">
+        <v>655</v>
+      </c>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="17"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B43" s="9">
+        <v>1699696</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="D43" s="9">
+        <v>10011558</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" s="11">
+        <v>245066</v>
+      </c>
+      <c r="G43" s="11">
+        <v>72400</v>
+      </c>
+      <c r="H43" s="11">
+        <v>172666</v>
+      </c>
+      <c r="I43" s="18">
+        <v>244500</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="K43" s="14">
+        <v>602</v>
+      </c>
+      <c r="L43" s="15"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="17"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B45" s="9">
+        <v>1699514</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="9">
+        <v>10011414</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="F45" s="11">
+        <v>272950</v>
+      </c>
+      <c r="G45" s="11">
+        <v>76940</v>
+      </c>
+      <c r="H45" s="11">
+        <v>196010</v>
+      </c>
+      <c r="I45" s="18">
+        <v>271200</v>
+      </c>
+      <c r="J45" s="11"/>
+      <c r="K45" s="14">
+        <v>286</v>
+      </c>
+      <c r="L45" s="15"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Production.xlsx
+++ b/Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAA6A5E-E623-444F-B7D6-A598456BE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA8CAE3-FF2A-41AD-9653-16A365DEA8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6259" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6260" uniqueCount="657">
   <si>
     <t>Date</t>
   </si>
@@ -2006,6 +2006,9 @@
   <si>
     <t>RG&gt;181Stainless</t>
   </si>
+  <si>
+    <t>OldPO1668369</t>
+  </si>
 </sst>
 </file>
 
@@ -2391,7 +2394,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -88172,8 +88175,8 @@
       <c r="A23" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="B23" s="9">
-        <v>1668369</v>
+      <c r="B23" s="41">
+        <v>1668373</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>632</v>
@@ -88204,8 +88207,8 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="41">
-        <v>1668373</v>
+      <c r="B24" s="41" t="s">
+        <v>656</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>634</v>
